--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57880D57-2902-4D98-A84F-3434AF6B4908}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7511983A-E89F-F44A-A826-92796EF99FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16960" yWindow="780" windowWidth="19200" windowHeight="20880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -243,23 +243,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -272,7 +272,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -315,7 +315,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -336,27 +336,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -364,8 +364,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -646,18 +646,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y66"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y69"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -734,7 +734,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -803,7 +803,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -880,7 +880,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -957,7 +957,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -5729,6 +5729,174 @@
       </c>
       <c r="Y66" s="11">
         <v>5.5890000000000004</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25">
+      <c r="A67" s="12">
+        <v>46083</v>
+      </c>
+      <c r="B67" s="12">
+        <v>46083</v>
+      </c>
+      <c r="C67" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E67" s="11">
+        <v>51</v>
+      </c>
+      <c r="F67" s="11">
+        <v>25</v>
+      </c>
+      <c r="G67" s="11">
+        <v>39.332999999999998</v>
+      </c>
+      <c r="H67" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="I67" s="11">
+        <v>20</v>
+      </c>
+      <c r="J67" s="11">
+        <v>20.7</v>
+      </c>
+      <c r="K67" s="11">
+        <v>85</v>
+      </c>
+      <c r="L67" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="M67" s="11">
+        <v>78.090999999999994</v>
+      </c>
+      <c r="N67" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O67" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P67" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q67" s="11">
+        <v>48</v>
+      </c>
+      <c r="R67" s="11">
+        <v>11</v>
+      </c>
+      <c r="S67" s="11">
+        <v>33.020000000000003</v>
+      </c>
+      <c r="T67" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U67" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V67" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W67" s="11">
+        <v>5.9</v>
+      </c>
+      <c r="X67" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="Y67" s="11">
+        <v>5.5890000000000004</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25">
+      <c r="A68" s="12">
+        <v>46083</v>
+      </c>
+      <c r="B68" s="12">
+        <v>46083</v>
+      </c>
+      <c r="C68" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E68" s="11">
+        <v>51</v>
+      </c>
+      <c r="F68" s="11">
+        <v>25</v>
+      </c>
+      <c r="G68" s="11">
+        <v>39.332999999999998</v>
+      </c>
+      <c r="H68" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="I68" s="11">
+        <v>20</v>
+      </c>
+      <c r="J68" s="11">
+        <v>20.7</v>
+      </c>
+      <c r="K68" s="11">
+        <v>85</v>
+      </c>
+      <c r="L68" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="M68" s="11">
+        <v>78.090999999999994</v>
+      </c>
+      <c r="N68" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O68" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P68" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q68" s="11">
+        <v>48</v>
+      </c>
+      <c r="R68" s="11">
+        <v>11</v>
+      </c>
+      <c r="S68" s="11">
+        <v>33.020000000000003</v>
+      </c>
+      <c r="T68" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U68" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V68" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W68" s="11">
+        <v>5.9</v>
+      </c>
+      <c r="X68" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="Y68" s="11">
+        <v>5.5890000000000004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25">
+      <c r="A69" s="12">
+        <v>46083</v>
+      </c>
+      <c r="B69" s="12">
+        <v>46083</v>
+      </c>
+      <c r="C69" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -5747,17 +5915,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -5846,7 +6014,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -5927,7 +6095,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -6016,7 +6184,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -6105,7 +6273,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -6123,13 +6291,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
     <col min="7" max="7" width="9" style="11"/>
     <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
@@ -6140,11 +6308,11 @@
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:25" s="5" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
@@ -6193,9 +6361,9 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+    <row r="2" spans="1:25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="16"/>
       <c r="D2" s="17"/>
       <c r="E2" s="13" t="s">
@@ -6238,12 +6406,12 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:25">
+      <c r="A3" s="12">
         <v>46034</v>
       </c>
-      <c r="B3" s="6">
-        <v>46034</v>
+      <c r="B3" s="12">
+        <v>46048</v>
       </c>
       <c r="C3" s="8">
         <v>0.61111111111111105</v>
@@ -6291,12 +6459,12 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:25">
+      <c r="A4" s="12">
         <v>46048</v>
       </c>
-      <c r="B4" s="6">
-        <v>46048</v>
+      <c r="B4" s="12">
+        <v>46055</v>
       </c>
       <c r="C4" s="8">
         <v>0.61111111111111105</v>
@@ -6344,12 +6512,12 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:25">
+      <c r="A5" s="12">
         <v>46055</v>
       </c>
-      <c r="B5" s="6">
-        <v>46055</v>
+      <c r="B5" s="12">
+        <v>46062</v>
       </c>
       <c r="C5" s="8">
         <v>0.61111111111111105</v>
@@ -6385,12 +6553,12 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:25">
+      <c r="A6" s="12">
         <v>46062</v>
       </c>
-      <c r="B6" s="6">
-        <v>46062</v>
+      <c r="B6" s="12">
+        <v>46076</v>
       </c>
       <c r="C6" s="8">
         <v>0.61111111111111105</v>
@@ -6424,6 +6592,47 @@
       </c>
       <c r="M6" s="11">
         <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="12">
+        <v>46076</v>
+      </c>
+      <c r="B7" s="12">
+        <v>46083</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="14">
+        <v>259</v>
+      </c>
+      <c r="F7" s="14">
+        <v>230</v>
+      </c>
+      <c r="G7" s="11">
+        <v>245</v>
+      </c>
+      <c r="H7" s="14">
+        <v>970</v>
+      </c>
+      <c r="I7" s="14">
+        <v>800</v>
+      </c>
+      <c r="J7" s="11">
+        <v>890</v>
+      </c>
+      <c r="K7" s="14">
+        <v>148</v>
+      </c>
+      <c r="L7" s="14">
+        <v>105</v>
+      </c>
+      <c r="M7" s="11">
+        <v>122.667</v>
       </c>
     </row>
   </sheetData>
@@ -6440,19 +6649,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
-  <dimension ref="A1:Y6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -6499,7 +6708,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -6538,12 +6747,12 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="6">
+    <row r="3" spans="1:25">
+      <c r="A3" s="12">
         <v>46034</v>
       </c>
-      <c r="B3" s="6">
-        <v>46034</v>
+      <c r="B3" s="12">
+        <v>46048</v>
       </c>
       <c r="C3" s="8">
         <v>0.61111111111111105</v>
@@ -6585,12 +6794,12 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A4" s="6">
+    <row r="4" spans="1:25">
+      <c r="A4" s="12">
         <v>46048</v>
       </c>
-      <c r="B4" s="6">
-        <v>46048</v>
+      <c r="B4" s="12">
+        <v>46055</v>
       </c>
       <c r="C4" s="8">
         <v>0.61111111111111105</v>
@@ -6632,12 +6841,12 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="6">
+    <row r="5" spans="1:25">
+      <c r="A5" s="12">
         <v>46055</v>
       </c>
-      <c r="B5" s="6">
-        <v>46055</v>
+      <c r="B5" s="12">
+        <v>46062</v>
       </c>
       <c r="C5" s="8">
         <v>0.61111111111111105</v>
@@ -6664,18 +6873,18 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A6" s="6">
+    <row r="6" spans="1:25">
+      <c r="A6" s="12">
         <v>46062</v>
       </c>
-      <c r="B6" s="6">
-        <v>46062</v>
+      <c r="B6" s="12">
+        <v>46076</v>
       </c>
       <c r="C6" s="8">
         <v>0.61111111111111105</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E6" s="11">
         <v>15.5</v>
@@ -6694,6 +6903,38 @@
       </c>
       <c r="J6" s="11">
         <v>9.8650000000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="12">
+        <v>46076</v>
+      </c>
+      <c r="B7" s="12">
+        <v>46083</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="11">
+        <v>15.5</v>
+      </c>
+      <c r="F7" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="G7" s="11">
+        <v>10</v>
+      </c>
+      <c r="H7" s="11">
+        <v>16</v>
+      </c>
+      <c r="I7" s="11">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="J7" s="11">
+        <v>10.221</v>
       </c>
     </row>
   </sheetData>
@@ -6711,15 +6952,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -6730,7 +6971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -6744,7 +6985,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -6753,7 +6994,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -6762,7 +7003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -6771,7 +7012,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -6780,7 +7021,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -6789,7 +7030,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -6798,7 +7039,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -6807,49 +7048,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -6860,7 +7101,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -6869,7 +7110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -6878,7 +7119,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -6889,7 +7130,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -6898,7 +7139,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -6907,42 +7148,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -6951,35 +7192,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7511983A-E89F-F44A-A826-92796EF99FB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA78592-9D7D-4A2F-9E6B-3EA5F7F9C5A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16960" yWindow="780" windowWidth="19200" windowHeight="20880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16965" yWindow="780" windowWidth="19200" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -243,23 +243,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -272,7 +272,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -315,7 +315,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -336,27 +336,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -364,8 +364,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -646,18 +646,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y72"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -734,7 +734,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -803,7 +803,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -880,7 +880,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -957,7 +957,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -3190,7 +3190,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -3267,7 +3267,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -4422,7 +4422,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -4499,7 +4499,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -4730,7 +4730,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -4807,7 +4807,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -5346,7 +5346,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -5731,7 +5731,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -5808,7 +5808,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -5896,6 +5896,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D69" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E69" s="11">
+        <v>51</v>
+      </c>
+      <c r="F69" s="11">
+        <v>25</v>
+      </c>
+      <c r="G69" s="11">
+        <v>39.332999999999998</v>
+      </c>
+      <c r="H69" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="I69" s="11">
+        <v>20</v>
+      </c>
+      <c r="J69" s="11">
+        <v>20.7</v>
+      </c>
+      <c r="K69" s="11">
+        <v>85</v>
+      </c>
+      <c r="L69" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="M69" s="11">
+        <v>78.090999999999994</v>
+      </c>
+      <c r="N69" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O69" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P69" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q69" s="11">
+        <v>48</v>
+      </c>
+      <c r="R69" s="11">
+        <v>11</v>
+      </c>
+      <c r="S69" s="11">
+        <v>33.020000000000003</v>
+      </c>
+      <c r="T69" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U69" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V69" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W69" s="11">
+        <v>6.1</v>
+      </c>
+      <c r="X69" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="Y69" s="11">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A70" s="12">
+        <v>46084</v>
+      </c>
+      <c r="B70" s="12">
+        <v>46084</v>
+      </c>
+      <c r="C70" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E70" s="11">
+        <v>51</v>
+      </c>
+      <c r="F70" s="11">
+        <v>25</v>
+      </c>
+      <c r="G70" s="11">
+        <v>39.167000000000002</v>
+      </c>
+      <c r="H70" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="I70" s="11">
+        <v>20</v>
+      </c>
+      <c r="J70" s="11">
+        <v>20.7</v>
+      </c>
+      <c r="K70" s="11">
+        <v>84</v>
+      </c>
+      <c r="L70" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="M70" s="11">
+        <v>77.272999999999996</v>
+      </c>
+      <c r="N70" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O70" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P70" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q70" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R70" s="11">
+        <v>11</v>
+      </c>
+      <c r="S70" s="11">
+        <v>33.020000000000003</v>
+      </c>
+      <c r="T70" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U70" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V70" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W70" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="X70" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Y70" s="11">
+        <v>5.7590000000000003</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A71" s="12">
+        <v>46084</v>
+      </c>
+      <c r="B71" s="12">
+        <v>46084</v>
+      </c>
+      <c r="C71" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E71" s="11">
+        <v>51</v>
+      </c>
+      <c r="F71" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G71" s="11">
+        <v>39.167000000000002</v>
+      </c>
+      <c r="H71" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="I71" s="11">
+        <v>20</v>
+      </c>
+      <c r="J71" s="11">
+        <v>20.7</v>
+      </c>
+      <c r="K71" s="11">
+        <v>85</v>
+      </c>
+      <c r="L71" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M71" s="11">
+        <v>77.272999999999996</v>
+      </c>
+      <c r="N71" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O71" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P71" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q71" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R71" s="11">
+        <v>11</v>
+      </c>
+      <c r="S71" s="11">
+        <v>33.020000000000003</v>
+      </c>
+      <c r="T71" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U71" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V71" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W71" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="X71" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Y71" s="11">
+        <v>5.7889999999999997</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A72" s="12">
+        <v>46084</v>
+      </c>
+      <c r="B72" s="12">
+        <v>46084</v>
+      </c>
+      <c r="C72" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D72" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5915,17 +6146,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -6014,7 +6245,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -6095,7 +6326,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -6184,7 +6415,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -6273,7 +6504,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -6292,12 +6523,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
     <col min="7" max="7" width="9" style="11"/>
     <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
@@ -6308,7 +6539,7 @@
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -6361,7 +6592,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -6406,7 +6637,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -6459,7 +6690,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -6512,7 +6743,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -6553,7 +6784,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -6594,7 +6825,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -6650,18 +6881,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -6708,7 +6939,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -6747,7 +6978,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -6794,7 +7025,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -6841,7 +7072,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -6873,7 +7104,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -6905,7 +7136,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -6952,15 +7183,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -6971,7 +7202,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -6985,7 +7216,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -6994,7 +7225,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -7003,7 +7234,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -7012,7 +7243,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -7021,7 +7252,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -7030,7 +7261,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -7039,7 +7270,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -7048,49 +7279,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -7101,7 +7332,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -7110,7 +7341,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -7119,7 +7350,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -7130,7 +7361,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -7139,7 +7370,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -7148,42 +7379,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -7192,35 +7423,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA78592-9D7D-4A2F-9E6B-3EA5F7F9C5A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015C61C6-68AB-B746-8277-8F30F8357AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16965" yWindow="780" windowWidth="19200" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13580" yWindow="780" windowWidth="22420" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -19,17 +19,28 @@
     <sheet name="GDDR" sheetId="5" r:id="rId4"/>
     <sheet name="info" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -243,23 +254,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -272,7 +283,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -315,7 +326,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -336,27 +347,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -364,8 +375,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -646,18 +657,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y81"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -734,7 +745,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -803,7 +814,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -880,7 +891,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -957,7 +968,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -1034,7 +1045,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -1111,7 +1122,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -1188,7 +1199,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -1265,7 +1276,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -1342,7 +1353,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -1419,7 +1430,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -1496,7 +1507,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -1573,7 +1584,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -1650,7 +1661,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -1727,7 +1738,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -1804,7 +1815,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -1881,7 +1892,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -1958,7 +1969,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -2035,7 +2046,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -2112,7 +2123,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -2189,7 +2200,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -2266,7 +2277,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -2343,7 +2354,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -2420,7 +2431,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -2497,7 +2508,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -2574,7 +2585,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -2651,7 +2662,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -2728,7 +2739,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -2805,7 +2816,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -2882,7 +2893,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -2959,7 +2970,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -3036,7 +3047,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -3113,7 +3124,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -3190,7 +3201,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -3267,7 +3278,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -3344,7 +3355,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -3421,7 +3432,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -3498,7 +3509,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -3575,7 +3586,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -3652,7 +3663,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -3729,7 +3740,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -3806,7 +3817,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -3883,7 +3894,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -3960,7 +3971,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -4037,7 +4048,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -4114,7 +4125,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -4191,7 +4202,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -4268,7 +4279,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -4345,7 +4356,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -4499,7 +4510,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -4576,7 +4587,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -4653,7 +4664,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -4730,7 +4741,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -4807,7 +4818,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -4884,7 +4895,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -4961,7 +4972,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -5038,7 +5049,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -5115,7 +5126,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -5192,7 +5203,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -5269,7 +5280,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -5346,7 +5357,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -5423,7 +5434,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -5500,7 +5511,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -5577,7 +5588,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -5654,7 +5665,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -5731,7 +5742,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -5808,7 +5819,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -5885,7 +5896,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -5962,7 +5973,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -6039,7 +6050,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -6116,7 +6127,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -6127,6 +6138,573 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D72" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E72" s="11">
+        <v>51</v>
+      </c>
+      <c r="F72" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G72" s="11">
+        <v>39.167000000000002</v>
+      </c>
+      <c r="H72" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="I72" s="11">
+        <v>20</v>
+      </c>
+      <c r="J72" s="11">
+        <v>20.7</v>
+      </c>
+      <c r="K72" s="11">
+        <v>85</v>
+      </c>
+      <c r="L72" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M72" s="11">
+        <v>77.272999999999996</v>
+      </c>
+      <c r="N72" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O72" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P72" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q72" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R72" s="11">
+        <v>11</v>
+      </c>
+      <c r="S72" s="11">
+        <v>33.020000000000003</v>
+      </c>
+      <c r="T72" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U72" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V72" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W72" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="X72" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="Y72" s="11">
+        <v>5.7889999999999997</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25">
+      <c r="A73" s="12">
+        <v>46085</v>
+      </c>
+      <c r="B73" s="12">
+        <v>46085</v>
+      </c>
+      <c r="C73" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E73" s="11">
+        <v>51</v>
+      </c>
+      <c r="F73" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G73" s="11">
+        <v>39</v>
+      </c>
+      <c r="H73" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="I73" s="11">
+        <v>20</v>
+      </c>
+      <c r="J73" s="11">
+        <v>20.7</v>
+      </c>
+      <c r="K73" s="11">
+        <v>85</v>
+      </c>
+      <c r="L73" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M73" s="11">
+        <v>77.159000000000006</v>
+      </c>
+      <c r="N73" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O73" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P73" s="11">
+        <v>13.65</v>
+      </c>
+      <c r="Q73" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R73" s="11">
+        <v>11</v>
+      </c>
+      <c r="S73" s="11">
+        <v>32.979999999999997</v>
+      </c>
+      <c r="T73" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U73" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V73" s="11">
+        <v>6.9109999999999996</v>
+      </c>
+      <c r="W73" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="X73" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Y73" s="11">
+        <v>5.8390000000000004</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25">
+      <c r="A74" s="12">
+        <v>46085</v>
+      </c>
+      <c r="B74" s="12">
+        <v>46085</v>
+      </c>
+      <c r="C74" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E74" s="11">
+        <v>51</v>
+      </c>
+      <c r="F74" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G74" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="H74" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="I74" s="11">
+        <v>20</v>
+      </c>
+      <c r="J74" s="11">
+        <v>20.7</v>
+      </c>
+      <c r="K74" s="11">
+        <v>85</v>
+      </c>
+      <c r="L74" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M74" s="11">
+        <v>77.159000000000006</v>
+      </c>
+      <c r="N74" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O74" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P74" s="11">
+        <v>13.65</v>
+      </c>
+      <c r="Q74" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R74" s="11">
+        <v>11</v>
+      </c>
+      <c r="S74" s="11">
+        <v>32.979999999999997</v>
+      </c>
+      <c r="T74" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U74" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V74" s="11">
+        <v>6.9109999999999996</v>
+      </c>
+      <c r="W74" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="X74" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Y74" s="11">
+        <v>5.8620000000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25">
+      <c r="A75" s="12">
+        <v>46085</v>
+      </c>
+      <c r="B75" s="12">
+        <v>46085</v>
+      </c>
+      <c r="C75" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E75" s="11">
+        <v>51</v>
+      </c>
+      <c r="F75" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G75" s="11">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="H75" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="I75" s="11">
+        <v>20</v>
+      </c>
+      <c r="J75" s="11">
+        <v>20.7</v>
+      </c>
+      <c r="K75" s="11">
+        <v>85</v>
+      </c>
+      <c r="L75" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M75" s="11">
+        <v>77.159000000000006</v>
+      </c>
+      <c r="N75" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O75" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P75" s="11">
+        <v>13.65</v>
+      </c>
+      <c r="Q75" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R75" s="11">
+        <v>11</v>
+      </c>
+      <c r="S75" s="11">
+        <v>32.979999999999997</v>
+      </c>
+      <c r="T75" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U75" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V75" s="11">
+        <v>6.9109999999999996</v>
+      </c>
+      <c r="W75" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="X75" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Y75" s="11">
+        <v>5.8620000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25">
+      <c r="A76" s="12">
+        <v>46086</v>
+      </c>
+      <c r="B76" s="12">
+        <v>46086</v>
+      </c>
+      <c r="C76" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E76" s="11">
+        <v>51</v>
+      </c>
+      <c r="F76" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G76" s="11">
+        <v>39.332999999999998</v>
+      </c>
+      <c r="H76" s="11">
+        <v>23</v>
+      </c>
+      <c r="I76" s="11">
+        <v>20</v>
+      </c>
+      <c r="J76" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="K76" s="11">
+        <v>85</v>
+      </c>
+      <c r="L76" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M76" s="11">
+        <v>77.159000000000006</v>
+      </c>
+      <c r="N76" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O76" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P76" s="11">
+        <v>13.65</v>
+      </c>
+      <c r="Q76" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R76" s="11">
+        <v>11</v>
+      </c>
+      <c r="S76" s="11">
+        <v>32.979999999999997</v>
+      </c>
+      <c r="T76" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U76" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V76" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W76" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="X76" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y76" s="11">
+        <v>5.8979999999999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25">
+      <c r="A77" s="12">
+        <v>46086</v>
+      </c>
+      <c r="B77" s="12">
+        <v>46086</v>
+      </c>
+      <c r="C77" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E77" s="11">
+        <v>52</v>
+      </c>
+      <c r="F77" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G77" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="H77" s="11">
+        <v>23</v>
+      </c>
+      <c r="I77" s="11">
+        <v>20</v>
+      </c>
+      <c r="J77" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="K77" s="11">
+        <v>85</v>
+      </c>
+      <c r="L77" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M77" s="11">
+        <v>77.409000000000006</v>
+      </c>
+      <c r="N77" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O77" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P77" s="11">
+        <v>13.65</v>
+      </c>
+      <c r="Q77" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R77" s="11">
+        <v>11</v>
+      </c>
+      <c r="S77" s="11">
+        <v>32.82</v>
+      </c>
+      <c r="T77" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U77" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V77" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W77" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="X77" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y77" s="11">
+        <v>5.8979999999999997</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25">
+      <c r="A78" s="12">
+        <v>46086</v>
+      </c>
+      <c r="B78" s="12">
+        <v>46086</v>
+      </c>
+      <c r="C78" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E78" s="11">
+        <v>52</v>
+      </c>
+      <c r="F78" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G78" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="H78" s="11">
+        <v>23</v>
+      </c>
+      <c r="I78" s="11">
+        <v>20</v>
+      </c>
+      <c r="J78" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="K78" s="11">
+        <v>85</v>
+      </c>
+      <c r="L78" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M78" s="11">
+        <v>77.409000000000006</v>
+      </c>
+      <c r="N78" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O78" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="P78" s="11">
+        <v>13.65</v>
+      </c>
+      <c r="Q78" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R78" s="11">
+        <v>11</v>
+      </c>
+      <c r="S78" s="11">
+        <v>33.119999999999997</v>
+      </c>
+      <c r="T78" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U78" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V78" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W78" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="X78" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y78" s="11">
+        <v>5.9210000000000003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25">
+      <c r="A79" s="12">
+        <v>46087</v>
+      </c>
+      <c r="B79" s="12">
+        <v>46087</v>
+      </c>
+      <c r="C79" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25">
+      <c r="A80" s="12">
+        <v>46087</v>
+      </c>
+      <c r="B80" s="12">
+        <v>46087</v>
+      </c>
+      <c r="C80" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="12">
+        <v>46087</v>
+      </c>
+      <c r="B81" s="12">
+        <v>46087</v>
+      </c>
+      <c r="C81" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D81" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -6146,17 +6724,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -6245,7 +6823,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -6326,7 +6904,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -6415,7 +6993,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -6504,7 +7082,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -6523,12 +7101,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
     <col min="7" max="7" width="9" style="11"/>
     <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
@@ -6539,7 +7117,7 @@
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -6592,7 +7170,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -6637,7 +7215,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -6690,7 +7268,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -6743,7 +7321,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -6784,7 +7362,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -6825,7 +7403,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -6881,18 +7459,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -6939,7 +7517,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -6978,7 +7556,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -7025,7 +7603,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -7072,7 +7650,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -7104,7 +7682,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -7136,7 +7714,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -7183,15 +7761,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -7202,7 +7780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -7216,7 +7794,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -7225,7 +7803,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -7234,7 +7812,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -7243,7 +7821,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -7252,7 +7830,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -7261,7 +7839,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -7270,7 +7848,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -7279,49 +7857,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -7332,7 +7910,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -7341,7 +7919,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -7350,7 +7928,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -7361,7 +7939,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -7370,7 +7948,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -7379,42 +7957,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -7423,35 +8001,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{015C61C6-68AB-B746-8277-8F30F8357AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073AA71B-BD5C-BF4E-A5CE-3A27F1CF7425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13580" yWindow="780" windowWidth="22420" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13580" yWindow="780" windowWidth="22420" windowHeight="20680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -657,7 +657,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y81"/>
+  <dimension ref="A1:Y84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
@@ -6679,6 +6679,69 @@
       <c r="D79" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="E79" s="11">
+        <v>52</v>
+      </c>
+      <c r="F79" s="11">
+        <v>26</v>
+      </c>
+      <c r="G79" s="11">
+        <v>39.667000000000002</v>
+      </c>
+      <c r="H79" s="11">
+        <v>23</v>
+      </c>
+      <c r="I79" s="11">
+        <v>20</v>
+      </c>
+      <c r="J79" s="11">
+        <v>21</v>
+      </c>
+      <c r="K79" s="11">
+        <v>85</v>
+      </c>
+      <c r="L79" s="11">
+        <v>26</v>
+      </c>
+      <c r="M79" s="11">
+        <v>77.409000000000006</v>
+      </c>
+      <c r="N79" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O79" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P79" s="11">
+        <v>13.65</v>
+      </c>
+      <c r="Q79" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R79" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="S79" s="11">
+        <v>33.32</v>
+      </c>
+      <c r="T79" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U79" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V79" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W79" s="11">
+        <v>6.9</v>
+      </c>
+      <c r="X79" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y79" s="11">
+        <v>6.0380000000000003</v>
+      </c>
     </row>
     <row r="80" spans="1:25">
       <c r="A80" s="12">
@@ -6693,8 +6756,71 @@
       <c r="D80" s="7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="E80" s="11">
+        <v>52</v>
+      </c>
+      <c r="F80" s="11">
+        <v>26</v>
+      </c>
+      <c r="G80" s="11">
+        <v>39.667000000000002</v>
+      </c>
+      <c r="H80" s="11">
+        <v>23</v>
+      </c>
+      <c r="I80" s="11">
+        <v>20</v>
+      </c>
+      <c r="J80" s="11">
+        <v>21</v>
+      </c>
+      <c r="K80" s="11">
+        <v>85</v>
+      </c>
+      <c r="L80" s="11">
+        <v>26</v>
+      </c>
+      <c r="M80" s="11">
+        <v>77.409000000000006</v>
+      </c>
+      <c r="N80" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O80" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P80" s="11">
+        <v>13.65</v>
+      </c>
+      <c r="Q80" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R80" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="S80" s="11">
+        <v>33.32</v>
+      </c>
+      <c r="T80" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U80" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V80" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W80" s="11">
+        <v>6.9</v>
+      </c>
+      <c r="X80" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y80" s="11">
+        <v>6.0380000000000003</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -6705,6 +6831,174 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D81" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E81" s="11">
+        <v>52</v>
+      </c>
+      <c r="F81" s="11">
+        <v>26</v>
+      </c>
+      <c r="G81" s="11">
+        <v>39.667000000000002</v>
+      </c>
+      <c r="H81" s="11">
+        <v>23</v>
+      </c>
+      <c r="I81" s="11">
+        <v>20</v>
+      </c>
+      <c r="J81" s="11">
+        <v>21</v>
+      </c>
+      <c r="K81" s="11">
+        <v>85</v>
+      </c>
+      <c r="L81" s="11">
+        <v>26</v>
+      </c>
+      <c r="M81" s="11">
+        <v>77.436000000000007</v>
+      </c>
+      <c r="N81" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O81" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P81" s="11">
+        <v>13.65</v>
+      </c>
+      <c r="Q81" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R81" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="S81" s="11">
+        <v>33.32</v>
+      </c>
+      <c r="T81" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U81" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V81" s="11">
+        <v>6.9139999999999997</v>
+      </c>
+      <c r="W81" s="11">
+        <v>6.9</v>
+      </c>
+      <c r="X81" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="11">
+        <v>6.0380000000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25">
+      <c r="A82" s="12">
+        <v>46090</v>
+      </c>
+      <c r="B82" s="12">
+        <v>46090</v>
+      </c>
+      <c r="C82" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E82" s="11">
+        <v>52</v>
+      </c>
+      <c r="F82" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G82" s="11">
+        <v>39.683</v>
+      </c>
+      <c r="H82" s="11">
+        <v>23.1</v>
+      </c>
+      <c r="I82" s="11">
+        <v>20</v>
+      </c>
+      <c r="J82" s="11">
+        <v>21.1</v>
+      </c>
+      <c r="K82" s="11">
+        <v>85</v>
+      </c>
+      <c r="L82" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M82" s="11">
+        <v>77.409000000000006</v>
+      </c>
+      <c r="N82" s="11">
+        <v>14.6</v>
+      </c>
+      <c r="O82" s="11">
+        <v>13</v>
+      </c>
+      <c r="P82" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q82" s="11">
+        <v>48</v>
+      </c>
+      <c r="R82" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S82" s="11">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="T82" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U82" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V82" s="11">
+        <v>6.9169999999999998</v>
+      </c>
+      <c r="W82" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="X82" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y82" s="11">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25">
+      <c r="A83" s="12">
+        <v>46090</v>
+      </c>
+      <c r="B83" s="12">
+        <v>46090</v>
+      </c>
+      <c r="C83" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25">
+      <c r="A84" s="12">
+        <v>46090</v>
+      </c>
+      <c r="B84" s="12">
+        <v>46090</v>
+      </c>
+      <c r="C84" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D84" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073AA71B-BD5C-BF4E-A5CE-3A27F1CF7425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6E96DA-FDC0-5B46-9C2C-9B8EE9B2D04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13580" yWindow="780" windowWidth="22420" windowHeight="20680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -657,7 +657,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y84"/>
+  <dimension ref="A1:Y87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
@@ -6987,6 +6987,69 @@
       <c r="D83" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="E83" s="11">
+        <v>52</v>
+      </c>
+      <c r="F83" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G83" s="11">
+        <v>39.683</v>
+      </c>
+      <c r="H83" s="11">
+        <v>23.1</v>
+      </c>
+      <c r="I83" s="11">
+        <v>20</v>
+      </c>
+      <c r="J83" s="11">
+        <v>21.1</v>
+      </c>
+      <c r="K83" s="11">
+        <v>85</v>
+      </c>
+      <c r="L83" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M83" s="11">
+        <v>77.409000000000006</v>
+      </c>
+      <c r="N83" s="11">
+        <v>14.6</v>
+      </c>
+      <c r="O83" s="11">
+        <v>13</v>
+      </c>
+      <c r="P83" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q83" s="11">
+        <v>48</v>
+      </c>
+      <c r="R83" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S83" s="11">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="T83" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U83" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V83" s="11">
+        <v>6.9169999999999998</v>
+      </c>
+      <c r="W83" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="X83" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y83" s="11">
+        <v>6.11</v>
+      </c>
     </row>
     <row r="84" spans="1:25">
       <c r="A84" s="12">
@@ -6999,6 +7062,111 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D84" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E84" s="11">
+        <v>52</v>
+      </c>
+      <c r="F84" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G84" s="11">
+        <v>39.683</v>
+      </c>
+      <c r="H84" s="11">
+        <v>23.1</v>
+      </c>
+      <c r="I84" s="11">
+        <v>20</v>
+      </c>
+      <c r="J84" s="11">
+        <v>21.1</v>
+      </c>
+      <c r="K84" s="11">
+        <v>85</v>
+      </c>
+      <c r="L84" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M84" s="11">
+        <v>77.272999999999996</v>
+      </c>
+      <c r="N84" s="11">
+        <v>14.6</v>
+      </c>
+      <c r="O84" s="11">
+        <v>13</v>
+      </c>
+      <c r="P84" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q84" s="11">
+        <v>48</v>
+      </c>
+      <c r="R84" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S84" s="11">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="T84" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U84" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V84" s="11">
+        <v>6.9169999999999998</v>
+      </c>
+      <c r="W84" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="X84" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y84" s="11">
+        <v>6.11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25">
+      <c r="A85" s="12">
+        <v>46091</v>
+      </c>
+      <c r="B85" s="12">
+        <v>46091</v>
+      </c>
+      <c r="C85" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25">
+      <c r="A86" s="12">
+        <v>46091</v>
+      </c>
+      <c r="B86" s="12">
+        <v>46091</v>
+      </c>
+      <c r="C86" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25">
+      <c r="A87" s="12">
+        <v>46091</v>
+      </c>
+      <c r="B87" s="12">
+        <v>46091</v>
+      </c>
+      <c r="C87" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D87" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,46 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6E96DA-FDC0-5B46-9C2C-9B8EE9B2D04B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B1EDED-8B68-43F7-AAE1-3ADCD96C9E59}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13580" yWindow="780" windowWidth="22420" windowHeight="20680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
     <sheet name="DRAM Contract" sheetId="3" r:id="rId2"/>
     <sheet name="Module" sheetId="4" r:id="rId3"/>
     <sheet name="GDDR" sheetId="5" r:id="rId4"/>
-    <sheet name="info" sheetId="1" r:id="rId5"/>
+    <sheet name="fig" sheetId="6" r:id="rId5"/>
+    <sheet name="info" sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -254,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -283,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -326,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -347,27 +337,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -375,8 +365,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -389,6 +379,4851 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DRAM!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> DDR5 16G (2Gx8) 4800/5600 </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DRAM!$G$3:$G$87</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>36.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>36.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>36.6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>36.6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>36.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>36.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>36.533000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>36.533000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>36.533000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>36.533000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>36.433</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>37.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>37.966999999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>37.966999999999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>37.933</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>37.933</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>37.933</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>37.9</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>37.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>37.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>38.033000000000001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>38.033000000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>38.033000000000001</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>38.033000000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>38.033000000000001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>38.033000000000001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>38.067</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>38.067</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>38.067</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>39.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>39.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>39.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>39.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>39.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>39.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>39.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>39.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>39.683</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>39.683</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>39.683</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>39.683</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>39.683</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>39.683</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E818-4EE4-8F53-DB9B42941B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DRAM!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> DDR5 16Gb (2Gx8) eTT </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DRAM!$J$3:$J$87</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>19.3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>19.399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>19.8</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>19.8</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>19.8</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>19.8</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>19.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>19.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>19.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>19.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>20.2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>20.2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>20.2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>20.5</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>20.6</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>20.6</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>20.6</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>20.8</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>20.8</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>20.8</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>21.1</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>21.1</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>21.1</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>21.1</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>21.1</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>21.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E818-4EE4-8F53-DB9B42941B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DRAM!$M$1:$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> DDR4 16Gb (2Gx8)3200 </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DRAM!$M$3:$M$87</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>78.635999999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>78.635999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>78.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>78.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>78.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>78.75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>78.805000000000007</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>78.75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>78.75</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>78.75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>78.204999999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>78.204999999999998</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>78.204999999999998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>77.932000000000002</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>77.932000000000002</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>77.932000000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>77.932000000000002</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>77.704999999999998</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>77.704999999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>77.704999999999998</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>77.590999999999994</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>77.590999999999994</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>77.204999999999998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>77.204999999999998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>77.204999999999998</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>77.084000000000003</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>77.084000000000003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>77.084000000000003</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>76.948999999999998</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>76.948999999999998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>76.948999999999998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>76.831000000000003</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>76.965999999999994</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>76.965999999999994</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>76.847999999999999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>76.847999999999999</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>76.847999999999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>76.73</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>76.965999999999994</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>76.965999999999994</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>77.236000000000004</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>77.236000000000004</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>77.236000000000004</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>77.775000000000006</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>77.775000000000006</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>77.775000000000006</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>77.909000000000006</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>77.909000000000006</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>78.409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>78.409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>78.409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>78.409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>78.635999999999996</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>78.635999999999996</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>78.635999999999996</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>79.135999999999996</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>79.135999999999996</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>79.135999999999996</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>79.364000000000004</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>79.364000000000004</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>79.364000000000004</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>79.635999999999996</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>79.635999999999996</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>79.909000000000006</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>78.090999999999994</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>78.090999999999994</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>78.090999999999994</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>77.272999999999996</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>77.272999999999996</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>77.272999999999996</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>77.159000000000006</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>77.159000000000006</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>77.159000000000006</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>77.159000000000006</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>77.409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>77.409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>77.409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>77.409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>77.436000000000007</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>77.409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>77.409000000000006</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>77.272999999999996</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>77.227000000000004</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>77.090999999999994</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>77.090999999999994</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E818-4EE4-8F53-DB9B42941B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DRAM!$P$1:$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> DDR4 16Gb (2Gx8) eTT </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DRAM!$P$3:$P$87</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.775</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.775</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.775</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12.8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>13.05</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>13.05</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>13.125</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>13.175000000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>13.175000000000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>13.175000000000001</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>13.175000000000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>13.175000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>13.25</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>13.25</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>13.25</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>13.25</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>13.313000000000001</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>13.313000000000001</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>13.313000000000001</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>13.313000000000001</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>13.324999999999999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>13.324999999999999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>13.4</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>13.4</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>13.4</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>13.4</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>13.4</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>13.525</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>13.525</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>13.525</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>13.65</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>13.65</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>13.65</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>13.65</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>13.65</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>13.65</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>13.65</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>13.65</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>13.65</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E818-4EE4-8F53-DB9B42941B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DRAM!$S$1:$S$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> DDR4 8Gb (1Gx8) 3200 </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DRAM!$S$3:$S$87</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>30.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30.86</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30.86</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30.86</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>30.86</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>30.86</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>30.86</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>30.76</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>30.76</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>30.7</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>30.8</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>30.88</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>30.88</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>30.86</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>30.86</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>30.86</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>30.84</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30.84</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30.84</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>30.78</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>30.98</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>31.1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>31.1</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>31.1</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>31.3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>31.3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>31.34</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>31.34</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>31.34</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>31.34</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>31.34</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>31.4</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>31.4</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>31.7</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>32.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>32.340000000000003</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>32.340000000000003</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>32.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>32.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>32.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>32.9</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>32.9</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>32.9</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>33.020000000000003</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>33.020000000000003</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>33.020000000000003</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>33.020000000000003</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>33.020000000000003</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>33.020000000000003</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>32.979999999999997</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>32.979999999999997</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>32.979999999999997</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>32.979999999999997</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>32.82</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>33.119999999999997</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>33.32</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>33.32</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>33.32</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>33.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>33.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>33.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>33.28</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>33.28</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>33.28</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-E818-4EE4-8F53-DB9B42941B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1539939664"/>
+        <c:axId val="1468093408"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DRAM!$V$1:$V$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> DDR4 8Gb (1Gx8) eTT </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DRAM!$V$3:$V$87</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6.0289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.1890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.3140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6.3140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.3140000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.4640000000000004</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.4640000000000004</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.4640000000000004</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.5709999999999997</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.5709999999999997</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.5709999999999997</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.6360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.6360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.6360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6.6360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6.6360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6.6360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6.6360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6.6360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6.6550000000000002</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>6.6980000000000004</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6.7110000000000003</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>6.7859999999999996</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>6.7859999999999996</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>6.7859999999999996</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6.8929999999999998</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>6.8929999999999998</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6.8970000000000002</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6.8970000000000002</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6.8970000000000002</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>6.8970000000000002</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>6.9109999999999996</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>6.9109999999999996</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>6.9109999999999996</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>6.9139999999999997</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>6.9169999999999998</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>6.9169999999999998</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>6.9169999999999998</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>6.9059999999999997</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>6.9059999999999997</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>6.9059999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-E818-4EE4-8F53-DB9B42941B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DRAM!$Y$1:$Y$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v> DDR3 4Gb 512Mx8 1600/1866 </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>46044</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46045</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46049</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>46050</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>46051</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>46056</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>46057</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>46058</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>46059</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>46063</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46065</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>46066</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>46077</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46079</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>46084</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>46085</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>46086</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>46087</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>46091</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DRAM!$Y$3:$Y$87</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="85"/>
+                <c:pt idx="0">
+                  <c:v>4.9450000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.0250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.0250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.0250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.1479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.1479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.1479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.17</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.17</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.17</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.2089999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.2089999999999996</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.2089999999999996</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.3319999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.3319999999999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.3319999999999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5.4</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.468</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.468</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5.468</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5.48</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.48</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.48</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5.4950000000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5.4950000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.4950000000000001</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>5.5069999999999997</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>5.5069999999999997</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>5.5069999999999997</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5.5069999999999997</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5.5069999999999997</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>5.5069999999999997</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5.5229999999999997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>5.5229999999999997</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>5.5229999999999997</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>5.5449999999999999</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>5.5449999999999999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>5.5449999999999999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5.5449999999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>5.5449999999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>5.5449999999999999</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>5.5609999999999999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.5609999999999999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.5609999999999999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.5730000000000004</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5.5730000000000004</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5.5730000000000004</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5.5730000000000004</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.5730000000000004</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.5730000000000004</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.5890000000000004</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.5890000000000004</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.5890000000000004</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.5890000000000004</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>5.5890000000000004</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.5890000000000004</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>5.5890000000000004</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>5.5890000000000004</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>5.68</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>5.7590000000000003</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5.7889999999999997</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>5.7889999999999997</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>5.8390000000000004</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>5.8620000000000001</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5.8620000000000001</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5.8979999999999997</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5.8979999999999997</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5.9210000000000003</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>6.0380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>6.0380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>6.0380000000000003</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>6.11</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>6.11</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>6.11</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>6.157</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>6.181</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>6.181</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-E818-4EE4-8F53-DB9B42941B82}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1545832384"/>
+        <c:axId val="1583758912"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1539939664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46203"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy/mm;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1468093408"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="1"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1468093408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1539939664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1583758912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1545832384"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dateAx>
+        <c:axId val="1545832384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy\-mm\-dd;@" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1583758912"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>180974</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EEF2B9D-4A31-4EB2-BD81-0083F31E34F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -658,17 +5493,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y87"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -745,7 +5580,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -814,7 +5649,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -891,7 +5726,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -968,7 +5803,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -1045,7 +5880,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -1122,7 +5957,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -1199,7 +6034,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -1276,7 +6111,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -1353,7 +6188,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -1430,7 +6265,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -1507,7 +6342,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -1584,7 +6419,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -1661,7 +6496,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -1738,7 +6573,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -1815,7 +6650,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -1892,7 +6727,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -1969,7 +6804,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -2046,7 +6881,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -2123,7 +6958,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -2200,7 +7035,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -2277,7 +7112,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -2354,7 +7189,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -2431,7 +7266,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -2508,7 +7343,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -2585,7 +7420,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -2662,7 +7497,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -2739,7 +7574,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -2816,7 +7651,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -2893,7 +7728,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -2970,7 +7805,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -3047,7 +7882,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -3124,7 +7959,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -3201,7 +8036,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -3278,7 +8113,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -3355,7 +8190,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -3432,7 +8267,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -3509,7 +8344,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -3586,7 +8421,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -3663,7 +8498,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -3740,7 +8575,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -3817,7 +8652,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -3894,7 +8729,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -3971,7 +8806,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -4048,7 +8883,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -4125,7 +8960,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -4202,7 +9037,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -4279,7 +9114,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -4356,7 +9191,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -4433,7 +9268,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -4510,7 +9345,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -4587,7 +9422,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -4664,7 +9499,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -4741,7 +9576,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -4818,7 +9653,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -4895,7 +9730,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -4972,7 +9807,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -5049,7 +9884,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -5126,7 +9961,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -5203,7 +10038,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -5280,7 +10115,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -5357,7 +10192,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -5434,7 +10269,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -5511,7 +10346,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -5588,7 +10423,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -5665,7 +10500,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -5742,7 +10577,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -5819,7 +10654,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -5896,7 +10731,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -5973,7 +10808,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -6050,7 +10885,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -6127,7 +10962,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -6204,7 +11039,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -6281,7 +11116,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -6358,7 +11193,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -6435,7 +11270,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -6512,7 +11347,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -6589,7 +11424,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -6666,7 +11501,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -6743,7 +11578,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -6820,7 +11655,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -6897,7 +11732,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -6974,7 +11809,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -7051,7 +11886,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -7128,7 +11963,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -7141,8 +11976,71 @@
       <c r="D85" s="7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="86" spans="1:25">
+      <c r="E85" s="11">
+        <v>52</v>
+      </c>
+      <c r="F85" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G85" s="11">
+        <v>39.683</v>
+      </c>
+      <c r="H85" s="11">
+        <v>23.1</v>
+      </c>
+      <c r="I85" s="11">
+        <v>20</v>
+      </c>
+      <c r="J85" s="11">
+        <v>21.1</v>
+      </c>
+      <c r="K85" s="11">
+        <v>85</v>
+      </c>
+      <c r="L85" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M85" s="11">
+        <v>77.227000000000004</v>
+      </c>
+      <c r="N85" s="11">
+        <v>14.6</v>
+      </c>
+      <c r="O85" s="11">
+        <v>13</v>
+      </c>
+      <c r="P85" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q85" s="11">
+        <v>48</v>
+      </c>
+      <c r="R85" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S85" s="11">
+        <v>33.28</v>
+      </c>
+      <c r="T85" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U85" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V85" s="11">
+        <v>6.9059999999999997</v>
+      </c>
+      <c r="W85" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="X85" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y85" s="11">
+        <v>6.157</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -7155,8 +12053,71 @@
       <c r="D86" s="7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="87" spans="1:25">
+      <c r="E86" s="11">
+        <v>52</v>
+      </c>
+      <c r="F86" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G86" s="11">
+        <v>39.683</v>
+      </c>
+      <c r="H86" s="11">
+        <v>23.2</v>
+      </c>
+      <c r="I86" s="11">
+        <v>20</v>
+      </c>
+      <c r="J86" s="11">
+        <v>21.1</v>
+      </c>
+      <c r="K86" s="11">
+        <v>85</v>
+      </c>
+      <c r="L86" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M86" s="11">
+        <v>77.090999999999994</v>
+      </c>
+      <c r="N86" s="11">
+        <v>14.6</v>
+      </c>
+      <c r="O86" s="11">
+        <v>13</v>
+      </c>
+      <c r="P86" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q86" s="11">
+        <v>48</v>
+      </c>
+      <c r="R86" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S86" s="11">
+        <v>33.28</v>
+      </c>
+      <c r="T86" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U86" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V86" s="11">
+        <v>6.9059999999999997</v>
+      </c>
+      <c r="W86" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="X86" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y86" s="11">
+        <v>6.181</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -7168,6 +12129,69 @@
       </c>
       <c r="D87" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E87" s="11">
+        <v>52</v>
+      </c>
+      <c r="F87" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G87" s="11">
+        <v>39.683</v>
+      </c>
+      <c r="H87" s="11">
+        <v>23.2</v>
+      </c>
+      <c r="I87" s="11">
+        <v>20</v>
+      </c>
+      <c r="J87" s="11">
+        <v>21.1</v>
+      </c>
+      <c r="K87" s="11">
+        <v>85</v>
+      </c>
+      <c r="L87" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M87" s="11">
+        <v>77.090999999999994</v>
+      </c>
+      <c r="N87" s="11">
+        <v>14.6</v>
+      </c>
+      <c r="O87" s="11">
+        <v>13</v>
+      </c>
+      <c r="P87" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q87" s="11">
+        <v>48</v>
+      </c>
+      <c r="R87" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S87" s="11">
+        <v>33.28</v>
+      </c>
+      <c r="T87" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U87" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V87" s="11">
+        <v>6.9059999999999997</v>
+      </c>
+      <c r="W87" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="X87" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y87" s="11">
+        <v>6.181</v>
       </c>
     </row>
   </sheetData>
@@ -7186,17 +12210,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -7285,7 +12309,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -7366,7 +12390,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -7455,7 +12479,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -7544,7 +12568,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -7562,13 +12586,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
     <col min="7" max="7" width="9" style="11"/>
     <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
@@ -7579,7 +12603,7 @@
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -7632,7 +12656,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -7677,7 +12701,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -7730,7 +12754,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -7783,7 +12807,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -7824,7 +12848,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -7865,7 +12889,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -7904,6 +12928,47 @@
       </c>
       <c r="M7" s="11">
         <v>122.667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" s="12">
+        <v>46083</v>
+      </c>
+      <c r="B8" s="12">
+        <v>46090</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="14">
+        <v>250</v>
+      </c>
+      <c r="F8" s="14">
+        <v>200</v>
+      </c>
+      <c r="G8" s="11">
+        <v>240</v>
+      </c>
+      <c r="H8" s="14">
+        <v>980</v>
+      </c>
+      <c r="I8" s="14">
+        <v>830</v>
+      </c>
+      <c r="J8" s="11">
+        <v>900</v>
+      </c>
+      <c r="K8" s="14">
+        <v>145</v>
+      </c>
+      <c r="L8" s="14">
+        <v>107</v>
+      </c>
+      <c r="M8" s="11">
+        <v>123.333</v>
       </c>
     </row>
   </sheetData>
@@ -7915,24 +12980,25 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -7979,7 +13045,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -8018,7 +13084,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -8065,7 +13131,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -8112,7 +13178,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -8144,7 +13210,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -8176,7 +13242,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -8206,6 +13272,38 @@
       </c>
       <c r="J7" s="11">
         <v>10.221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
+        <v>46083</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46090</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="11">
+        <v>16</v>
+      </c>
+      <c r="F8" s="11">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G8" s="11">
+        <v>10.455</v>
+      </c>
+      <c r="H8" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="I8" s="11">
+        <v>9</v>
+      </c>
+      <c r="J8" s="11">
+        <v>10.721</v>
       </c>
     </row>
   </sheetData>
@@ -8221,17 +13319,31 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -8242,7 +13354,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -8256,7 +13368,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -8265,7 +13377,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -8274,7 +13386,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -8283,7 +13395,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -8292,7 +13404,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -8301,7 +13413,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -8310,7 +13422,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -8319,49 +13431,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -8372,7 +13484,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -8381,7 +13493,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -8390,7 +13502,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -8401,7 +13513,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -8410,7 +13522,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -8419,42 +13531,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -8463,35 +13575,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B1EDED-8B68-43F7-AAE1-3ADCD96C9E59}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD421C0E-CC23-4F33-AD4F-495B7CC97BE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -432,10 +432,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:f>DRAM!$B$3:$B$1187</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>46044</c:v>
                 </c:pt>
@@ -690,16 +690,25 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DRAM!$G$3:$G$87</c:f>
+              <c:f>DRAM!$G$3:$G$1187</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>36.667000000000002</c:v>
                 </c:pt>
@@ -954,6 +963,15 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>39.683</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>39.75</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>39.75</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>39.567</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -996,10 +1014,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:f>DRAM!$B$3:$B$1187</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>46044</c:v>
                 </c:pt>
@@ -1254,16 +1272,25 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DRAM!$J$3:$J$87</c:f>
+              <c:f>DRAM!$J$3:$J$1187</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>19.2</c:v>
                 </c:pt>
@@ -1518,6 +1545,15 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>21.1</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>21.15</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>21.15</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>21.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1560,10 +1596,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:f>DRAM!$B$3:$B$1187</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>46044</c:v>
                 </c:pt>
@@ -1818,16 +1854,25 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DRAM!$M$3:$M$87</c:f>
+              <c:f>DRAM!$M$3:$M$1187</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>78.635999999999996</c:v>
                 </c:pt>
@@ -2082,6 +2127,15 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>77.090999999999994</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>77.317999999999998</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>77.317999999999998</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>77.317999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2124,10 +2178,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:f>DRAM!$B$3:$B$1187</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>46044</c:v>
                 </c:pt>
@@ -2382,16 +2436,25 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DRAM!$P$3:$P$87</c:f>
+              <c:f>DRAM!$P$3:$P$1187</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>12.7</c:v>
                 </c:pt>
@@ -2646,6 +2709,15 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>13.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2688,10 +2760,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:f>DRAM!$B$3:$B$1187</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>46044</c:v>
                 </c:pt>
@@ -2946,16 +3018,25 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DRAM!$S$3:$S$87</c:f>
+              <c:f>DRAM!$S$3:$S$1187</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>30.3</c:v>
                 </c:pt>
@@ -3210,6 +3291,15 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>33.28</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>33.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3268,10 +3358,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:f>DRAM!$B$3:$B$1187</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>46044</c:v>
                 </c:pt>
@@ -3526,16 +3616,25 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DRAM!$V$3:$V$87</c:f>
+              <c:f>DRAM!$V$3:$V$1187</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>6.0289999999999999</c:v>
                 </c:pt>
@@ -3789,6 +3888,15 @@
                   <c:v>6.9059999999999997</c:v>
                 </c:pt>
                 <c:pt idx="84">
+                  <c:v>6.9059999999999997</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>6.9059999999999997</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>6.9059999999999997</c:v>
+                </c:pt>
+                <c:pt idx="87">
                   <c:v>6.9059999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -3834,10 +3942,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>DRAM!$B$3:$B$87</c:f>
+              <c:f>DRAM!$B$3:$B$1187</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>46044</c:v>
                 </c:pt>
@@ -4092,16 +4200,25 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>46091</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>46092</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>46092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DRAM!$Y$3:$Y$87</c:f>
+              <c:f>DRAM!$Y$3:$Y$1187</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="1185"/>
                 <c:pt idx="0">
                   <c:v>4.9450000000000003</c:v>
                 </c:pt>
@@ -4356,6 +4473,15 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>6.181</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>6.2430000000000003</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>6.29</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>6.3049999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5492,7 +5618,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y87"/>
+  <dimension ref="A1:Y90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -12192,6 +12318,237 @@
       </c>
       <c r="Y87" s="11">
         <v>6.181</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A88" s="12">
+        <v>46092</v>
+      </c>
+      <c r="B88" s="12">
+        <v>46092</v>
+      </c>
+      <c r="C88" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E88" s="11">
+        <v>52</v>
+      </c>
+      <c r="F88" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G88" s="11">
+        <v>39.75</v>
+      </c>
+      <c r="H88" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I88" s="11">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="J88" s="11">
+        <v>21.15</v>
+      </c>
+      <c r="K88" s="11">
+        <v>87</v>
+      </c>
+      <c r="L88" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M88" s="11">
+        <v>77.317999999999998</v>
+      </c>
+      <c r="N88" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O88" s="11">
+        <v>13</v>
+      </c>
+      <c r="P88" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q88" s="11">
+        <v>48</v>
+      </c>
+      <c r="R88" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S88" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T88" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U88" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V88" s="11">
+        <v>6.9059999999999997</v>
+      </c>
+      <c r="W88" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="X88" s="11">
+        <v>5.25</v>
+      </c>
+      <c r="Y88" s="11">
+        <v>6.2430000000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A89" s="12">
+        <v>46092</v>
+      </c>
+      <c r="B89" s="12">
+        <v>46092</v>
+      </c>
+      <c r="C89" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E89" s="11">
+        <v>52</v>
+      </c>
+      <c r="F89" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G89" s="11">
+        <v>39.75</v>
+      </c>
+      <c r="H89" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I89" s="11">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="J89" s="11">
+        <v>21.15</v>
+      </c>
+      <c r="K89" s="11">
+        <v>87</v>
+      </c>
+      <c r="L89" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M89" s="11">
+        <v>77.317999999999998</v>
+      </c>
+      <c r="N89" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O89" s="11">
+        <v>13</v>
+      </c>
+      <c r="P89" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q89" s="11">
+        <v>48</v>
+      </c>
+      <c r="R89" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S89" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T89" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U89" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V89" s="11">
+        <v>6.9059999999999997</v>
+      </c>
+      <c r="W89" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="X89" s="11">
+        <v>5.25</v>
+      </c>
+      <c r="Y89" s="11">
+        <v>6.29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A90" s="12">
+        <v>46092</v>
+      </c>
+      <c r="B90" s="12">
+        <v>46092</v>
+      </c>
+      <c r="C90" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E90" s="11">
+        <v>52</v>
+      </c>
+      <c r="F90" s="11">
+        <v>26</v>
+      </c>
+      <c r="G90" s="11">
+        <v>39.567</v>
+      </c>
+      <c r="H90" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I90" s="11">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="J90" s="11">
+        <v>21.15</v>
+      </c>
+      <c r="K90" s="11">
+        <v>87</v>
+      </c>
+      <c r="L90" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M90" s="11">
+        <v>77.317999999999998</v>
+      </c>
+      <c r="N90" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O90" s="11">
+        <v>13</v>
+      </c>
+      <c r="P90" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q90" s="11">
+        <v>48</v>
+      </c>
+      <c r="R90" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S90" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T90" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U90" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V90" s="11">
+        <v>6.9059999999999997</v>
+      </c>
+      <c r="W90" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="X90" s="11">
+        <v>5.25</v>
+      </c>
+      <c r="Y90" s="11">
+        <v>6.3049999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD421C0E-CC23-4F33-AD4F-495B7CC97BE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572932D9-E658-4474-B153-70CABC1A9673}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -700,6 +700,15 @@
                 <c:pt idx="87">
                   <c:v>46092</c:v>
                 </c:pt>
+                <c:pt idx="88">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>46093</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -972,6 +981,12 @@
                 </c:pt>
                 <c:pt idx="87">
                   <c:v>39.567</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>39.4</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>39.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1282,6 +1297,15 @@
                 <c:pt idx="87">
                   <c:v>46092</c:v>
                 </c:pt>
+                <c:pt idx="88">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>46093</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1553,6 +1577,12 @@
                   <c:v>21.15</c:v>
                 </c:pt>
                 <c:pt idx="87">
+                  <c:v>21.15</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>21.15</c:v>
+                </c:pt>
+                <c:pt idx="89">
                   <c:v>21.15</c:v>
                 </c:pt>
               </c:numCache>
@@ -1864,6 +1894,15 @@
                 <c:pt idx="87">
                   <c:v>46092</c:v>
                 </c:pt>
+                <c:pt idx="88">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>46093</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2135,6 +2174,12 @@
                   <c:v>77.317999999999998</c:v>
                 </c:pt>
                 <c:pt idx="87">
+                  <c:v>77.317999999999998</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>77.317999999999998</c:v>
+                </c:pt>
+                <c:pt idx="89">
                   <c:v>77.317999999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -2446,6 +2491,15 @@
                 <c:pt idx="87">
                   <c:v>46092</c:v>
                 </c:pt>
+                <c:pt idx="88">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>46093</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2717,6 +2771,12 @@
                   <c:v>13.75</c:v>
                 </c:pt>
                 <c:pt idx="87">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="89">
                   <c:v>13.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3028,6 +3088,15 @@
                 <c:pt idx="87">
                   <c:v>46092</c:v>
                 </c:pt>
+                <c:pt idx="88">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>46093</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3300,6 +3369,12 @@
                 </c:pt>
                 <c:pt idx="87">
                   <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>33.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3626,6 +3701,15 @@
                 <c:pt idx="87">
                   <c:v>46092</c:v>
                 </c:pt>
+                <c:pt idx="88">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>46093</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3897,6 +3981,12 @@
                   <c:v>6.9059999999999997</c:v>
                 </c:pt>
                 <c:pt idx="87">
+                  <c:v>6.9059999999999997</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>6.9059999999999997</c:v>
+                </c:pt>
+                <c:pt idx="89">
                   <c:v>6.9059999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -4210,6 +4300,15 @@
                 <c:pt idx="87">
                   <c:v>46092</c:v>
                 </c:pt>
+                <c:pt idx="88">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>46093</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>46093</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4482,6 +4581,12 @@
                 </c:pt>
                 <c:pt idx="87">
                   <c:v>6.3049999999999997</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>6.3810000000000002</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>6.3810000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5618,7 +5723,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y90"/>
+  <dimension ref="A1:Y93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -12549,6 +12654,174 @@
       </c>
       <c r="Y90" s="11">
         <v>6.3049999999999997</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A91" s="12">
+        <v>46093</v>
+      </c>
+      <c r="B91" s="12">
+        <v>46093</v>
+      </c>
+      <c r="C91" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E91" s="11">
+        <v>52</v>
+      </c>
+      <c r="F91" s="11">
+        <v>26</v>
+      </c>
+      <c r="G91" s="11">
+        <v>39.4</v>
+      </c>
+      <c r="H91" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I91" s="11">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="J91" s="11">
+        <v>21.15</v>
+      </c>
+      <c r="K91" s="11">
+        <v>87</v>
+      </c>
+      <c r="L91" s="11">
+        <v>26</v>
+      </c>
+      <c r="M91" s="11">
+        <v>77.317999999999998</v>
+      </c>
+      <c r="N91" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O91" s="11">
+        <v>13</v>
+      </c>
+      <c r="P91" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q91" s="11">
+        <v>48</v>
+      </c>
+      <c r="R91" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="S91" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T91" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U91" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V91" s="11">
+        <v>6.9059999999999997</v>
+      </c>
+      <c r="W91" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="X91" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y91" s="11">
+        <v>6.3810000000000002</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A92" s="12">
+        <v>46093</v>
+      </c>
+      <c r="B92" s="12">
+        <v>46093</v>
+      </c>
+      <c r="C92" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E92" s="11">
+        <v>52</v>
+      </c>
+      <c r="F92" s="11">
+        <v>26</v>
+      </c>
+      <c r="G92" s="11">
+        <v>39.4</v>
+      </c>
+      <c r="H92" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I92" s="11">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="J92" s="11">
+        <v>21.15</v>
+      </c>
+      <c r="K92" s="11">
+        <v>87</v>
+      </c>
+      <c r="L92" s="11">
+        <v>26</v>
+      </c>
+      <c r="M92" s="11">
+        <v>77.317999999999998</v>
+      </c>
+      <c r="N92" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O92" s="11">
+        <v>13</v>
+      </c>
+      <c r="P92" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q92" s="11">
+        <v>48</v>
+      </c>
+      <c r="R92" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="S92" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T92" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U92" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V92" s="11">
+        <v>6.9059999999999997</v>
+      </c>
+      <c r="W92" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="X92" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y92" s="11">
+        <v>6.3810000000000002</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A93" s="12">
+        <v>46093</v>
+      </c>
+      <c r="B93" s="12">
+        <v>46093</v>
+      </c>
+      <c r="C93" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572932D9-E658-4474-B153-70CABC1A9673}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A077CFCF-E3AE-4E20-94CD-A757B9E07D82}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -709,6 +709,24 @@
                 <c:pt idx="90">
                   <c:v>46093</c:v>
                 </c:pt>
+                <c:pt idx="91">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46097</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -987,6 +1005,24 @@
                 </c:pt>
                 <c:pt idx="89">
                   <c:v>39.4</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>39.4</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>39.332999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1306,6 +1342,24 @@
                 <c:pt idx="90">
                   <c:v>46093</c:v>
                 </c:pt>
+                <c:pt idx="91">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46097</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1584,6 +1638,24 @@
                 </c:pt>
                 <c:pt idx="89">
                   <c:v>21.15</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>21.15</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>21.15</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>21.15</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>21.15</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>21.2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>21.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1903,6 +1975,24 @@
                 <c:pt idx="90">
                   <c:v>46093</c:v>
                 </c:pt>
+                <c:pt idx="91">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46097</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2181,6 +2271,24 @@
                 </c:pt>
                 <c:pt idx="89">
                   <c:v>77.317999999999998</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>77.317999999999998</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>77.25</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>77.25</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>77.25</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>77.227000000000004</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>77.227000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2500,6 +2608,24 @@
                 <c:pt idx="90">
                   <c:v>46093</c:v>
                 </c:pt>
+                <c:pt idx="91">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46097</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2777,6 +2903,24 @@
                   <c:v>13.75</c:v>
                 </c:pt>
                 <c:pt idx="89">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>13.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3097,6 +3241,24 @@
                 <c:pt idx="90">
                   <c:v>46093</c:v>
                 </c:pt>
+                <c:pt idx="91">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46097</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3375,6 +3537,24 @@
                 </c:pt>
                 <c:pt idx="89">
                   <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>33.58</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>33.58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3710,6 +3890,24 @@
                 <c:pt idx="90">
                   <c:v>46093</c:v>
                 </c:pt>
+                <c:pt idx="91">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46097</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3988,6 +4186,24 @@
                 </c:pt>
                 <c:pt idx="89">
                   <c:v>6.9059999999999997</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>6.9059999999999997</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>6.899</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>6.899</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>6.899</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>6.8940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>6.8940000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4309,6 +4525,24 @@
                 <c:pt idx="90">
                   <c:v>46093</c:v>
                 </c:pt>
+                <c:pt idx="91">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46094</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46097</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4587,6 +4821,24 @@
                 </c:pt>
                 <c:pt idx="89">
                   <c:v>6.3810000000000002</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>6.3810000000000002</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>6.4379999999999997</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>6.4379999999999997</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>6.4379999999999997</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>6.5330000000000004</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>6.5119999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4858,7 +5110,1006 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Module!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>DDR5 UDIMM 16GB 4800/5600</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Module!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Module!$G$3:$G$9</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>177.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>230</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C247-486A-B615-212EDB24F1C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Module!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>DDR5 RDIMM 32GB 4800/5600</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Module!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Module!$J$3:$J$9</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>545</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>885</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>910</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-C247-486A-B615-212EDB24F1C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Module!$M$1:$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>DDR4 UDIMM 16GB 3200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Module!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Module!$M$3:$M$9</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>118.333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>122.667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>123.333</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>126.667</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C247-486A-B615-212EDB24F1C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1526098480"/>
+        <c:axId val="1427473968"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1526098480"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46203"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy/mm/dd;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1427473968"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="1"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1427473968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1526098480"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>GDDR!$G$1:$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>GDDR5 8Gb</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>GDDR!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="m/d/yyyy">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>GDDR!$G$3:$G$9</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>7.0910000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.6820000000000004</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.4090000000000007</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.6359999999999992</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.455</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11.182</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B192-400F-A953-98DEBDB0B8C6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>GDDR!$J$1:$J$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>GDDR6 8Gb</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>GDDR!$B$3:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="m/d/yyyy">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>GDDR!$J$3:$J$9</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>7.1539999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.8650000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.6539999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.8650000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.221</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10.721</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11.462</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B192-400F-A953-98DEBDB0B8C6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1668066848"/>
+        <c:axId val="1382523328"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1668066848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46203"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy\-mm\-dd;@" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1382523328"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="1"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1382523328"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="6"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1668066848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5414,18 +6665,1050 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>685799</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>180974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>600076</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
@@ -5449,6 +7732,82 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="차트 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49C124B6-8D35-4B98-ACF3-0FDC84D173C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="차트 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7307BB6A-9BE9-4A84-9024-9D535B409D3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5723,7 +8082,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y93"/>
+  <dimension ref="A1:Y99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -12821,6 +15180,468 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D93" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E93" s="11">
+        <v>52</v>
+      </c>
+      <c r="F93" s="11">
+        <v>26</v>
+      </c>
+      <c r="G93" s="11">
+        <v>39.4</v>
+      </c>
+      <c r="H93" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I93" s="11">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="J93" s="11">
+        <v>21.15</v>
+      </c>
+      <c r="K93" s="11">
+        <v>87</v>
+      </c>
+      <c r="L93" s="11">
+        <v>26</v>
+      </c>
+      <c r="M93" s="11">
+        <v>77.317999999999998</v>
+      </c>
+      <c r="N93" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O93" s="11">
+        <v>13</v>
+      </c>
+      <c r="P93" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q93" s="11">
+        <v>48</v>
+      </c>
+      <c r="R93" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="S93" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T93" s="11">
+        <v>8.1</v>
+      </c>
+      <c r="U93" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V93" s="11">
+        <v>6.9059999999999997</v>
+      </c>
+      <c r="W93" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="X93" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y93" s="11">
+        <v>6.3810000000000002</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A94" s="12">
+        <v>46094</v>
+      </c>
+      <c r="B94" s="12">
+        <v>46094</v>
+      </c>
+      <c r="C94" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E94" s="11">
+        <v>51</v>
+      </c>
+      <c r="F94" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="G94" s="11">
+        <v>39</v>
+      </c>
+      <c r="H94" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I94" s="11">
+        <v>20</v>
+      </c>
+      <c r="J94" s="11">
+        <v>21.15</v>
+      </c>
+      <c r="K94" s="11">
+        <v>88</v>
+      </c>
+      <c r="L94" s="11">
+        <v>26</v>
+      </c>
+      <c r="M94" s="11">
+        <v>77.25</v>
+      </c>
+      <c r="N94" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O94" s="11">
+        <v>13</v>
+      </c>
+      <c r="P94" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q94" s="11">
+        <v>48</v>
+      </c>
+      <c r="R94" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="S94" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T94" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U94" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V94" s="11">
+        <v>6.899</v>
+      </c>
+      <c r="W94" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="X94" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y94" s="11">
+        <v>6.4379999999999997</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A95" s="12">
+        <v>46094</v>
+      </c>
+      <c r="B95" s="12">
+        <v>46094</v>
+      </c>
+      <c r="C95" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E95" s="11">
+        <v>51</v>
+      </c>
+      <c r="F95" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="G95" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H95" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I95" s="11">
+        <v>20</v>
+      </c>
+      <c r="J95" s="11">
+        <v>21.15</v>
+      </c>
+      <c r="K95" s="11">
+        <v>88</v>
+      </c>
+      <c r="L95" s="11">
+        <v>26</v>
+      </c>
+      <c r="M95" s="11">
+        <v>77.25</v>
+      </c>
+      <c r="N95" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O95" s="11">
+        <v>13</v>
+      </c>
+      <c r="P95" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q95" s="11">
+        <v>48</v>
+      </c>
+      <c r="R95" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="S95" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T95" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U95" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V95" s="11">
+        <v>6.899</v>
+      </c>
+      <c r="W95" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="X95" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y95" s="11">
+        <v>6.4379999999999997</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A96" s="12">
+        <v>46094</v>
+      </c>
+      <c r="B96" s="12">
+        <v>46094</v>
+      </c>
+      <c r="C96" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E96" s="11">
+        <v>51</v>
+      </c>
+      <c r="F96" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="G96" s="11">
+        <v>39.332999999999998</v>
+      </c>
+      <c r="H96" s="11">
+        <v>23.3</v>
+      </c>
+      <c r="I96" s="11">
+        <v>20</v>
+      </c>
+      <c r="J96" s="11">
+        <v>21.15</v>
+      </c>
+      <c r="K96" s="11">
+        <v>88</v>
+      </c>
+      <c r="L96" s="11">
+        <v>26</v>
+      </c>
+      <c r="M96" s="11">
+        <v>77.25</v>
+      </c>
+      <c r="N96" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O96" s="11">
+        <v>13</v>
+      </c>
+      <c r="P96" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q96" s="11">
+        <v>48</v>
+      </c>
+      <c r="R96" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="S96" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T96" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U96" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V96" s="11">
+        <v>6.899</v>
+      </c>
+      <c r="W96" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="X96" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y96" s="11">
+        <v>6.4379999999999997</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A97" s="12">
+        <v>46097</v>
+      </c>
+      <c r="B97" s="12">
+        <v>46097</v>
+      </c>
+      <c r="C97" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E97" s="11">
+        <v>51</v>
+      </c>
+      <c r="F97" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="G97" s="11">
+        <v>39.332999999999998</v>
+      </c>
+      <c r="H97" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I97" s="11">
+        <v>20</v>
+      </c>
+      <c r="J97" s="11">
+        <v>21.2</v>
+      </c>
+      <c r="K97" s="11">
+        <v>88</v>
+      </c>
+      <c r="L97" s="11">
+        <v>26</v>
+      </c>
+      <c r="M97" s="11">
+        <v>77.227000000000004</v>
+      </c>
+      <c r="N97" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O97" s="11">
+        <v>13</v>
+      </c>
+      <c r="P97" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q97" s="11">
+        <v>48</v>
+      </c>
+      <c r="R97" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="S97" s="11">
+        <v>33.58</v>
+      </c>
+      <c r="T97" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U97" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V97" s="11">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="W97" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="X97" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y97" s="11">
+        <v>6.5330000000000004</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A98" s="12">
+        <v>46097</v>
+      </c>
+      <c r="B98" s="12">
+        <v>46097</v>
+      </c>
+      <c r="C98" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E98" s="11">
+        <v>51</v>
+      </c>
+      <c r="F98" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="G98" s="11">
+        <v>39.332999999999998</v>
+      </c>
+      <c r="H98" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I98" s="11">
+        <v>20</v>
+      </c>
+      <c r="J98" s="11">
+        <v>21.2</v>
+      </c>
+      <c r="K98" s="11">
+        <v>88</v>
+      </c>
+      <c r="L98" s="11">
+        <v>26</v>
+      </c>
+      <c r="M98" s="11">
+        <v>77.227000000000004</v>
+      </c>
+      <c r="N98" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O98" s="11">
+        <v>13</v>
+      </c>
+      <c r="P98" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q98" s="11">
+        <v>48</v>
+      </c>
+      <c r="R98" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="S98" s="11">
+        <v>33.58</v>
+      </c>
+      <c r="T98" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U98" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V98" s="11">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="W98" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="X98" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y98" s="11">
+        <v>6.5119999999999996</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A99" s="12">
+        <v>46097</v>
+      </c>
+      <c r="B99" s="12">
+        <v>46097</v>
+      </c>
+      <c r="C99" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D99" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -13216,7 +16037,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -13601,6 +16422,47 @@
         <v>123.333</v>
       </c>
     </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" s="12">
+        <v>46090</v>
+      </c>
+      <c r="B9" s="12">
+        <v>46097</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="14">
+        <v>240</v>
+      </c>
+      <c r="F9" s="14">
+        <v>200</v>
+      </c>
+      <c r="G9" s="11">
+        <v>230</v>
+      </c>
+      <c r="H9" s="14">
+        <v>990</v>
+      </c>
+      <c r="I9" s="14">
+        <v>850</v>
+      </c>
+      <c r="J9" s="11">
+        <v>910</v>
+      </c>
+      <c r="K9" s="14">
+        <v>160</v>
+      </c>
+      <c r="L9" s="14">
+        <v>115</v>
+      </c>
+      <c r="M9" s="11">
+        <v>126.667</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -13616,7 +16478,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
@@ -13934,6 +16796,38 @@
       </c>
       <c r="J8" s="11">
         <v>10.721</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" s="12">
+        <v>46090</v>
+      </c>
+      <c r="B9" s="12">
+        <v>46097</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="11">
+        <v>17</v>
+      </c>
+      <c r="F9" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G9" s="11">
+        <v>11.182</v>
+      </c>
+      <c r="H9" s="11">
+        <v>18</v>
+      </c>
+      <c r="I9" s="11">
+        <v>10</v>
+      </c>
+      <c r="J9" s="11">
+        <v>11.462</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A077CFCF-E3AE-4E20-94CD-A757B9E07D82}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18DC94A-2E38-4341-86D5-C7EA38862E92}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -727,6 +727,15 @@
                 <c:pt idx="96">
                   <c:v>46097</c:v>
                 </c:pt>
+                <c:pt idx="97">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46098</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1023,6 +1032,15 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>39.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>39.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>39.667000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1360,6 +1378,15 @@
                 <c:pt idx="96">
                   <c:v>46097</c:v>
                 </c:pt>
+                <c:pt idx="97">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46098</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1656,6 +1683,15 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>21.2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>21.2</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>21.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1993,6 +2029,15 @@
                 <c:pt idx="96">
                   <c:v>46097</c:v>
                 </c:pt>
+                <c:pt idx="97">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46098</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2289,6 +2334,15 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>77.227000000000004</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>77.227000000000004</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>77.364000000000004</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>77.364000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2626,6 +2680,15 @@
                 <c:pt idx="96">
                   <c:v>46097</c:v>
                 </c:pt>
+                <c:pt idx="97">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46098</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2921,6 +2984,15 @@
                   <c:v>13.75</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="98">
                   <c:v>13.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3259,6 +3331,15 @@
                 <c:pt idx="96">
                   <c:v>46097</c:v>
                 </c:pt>
+                <c:pt idx="97">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46098</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3555,6 +3636,15 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>33.58</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>33.58</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>33.68</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>33.880000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3908,6 +3998,15 @@
                 <c:pt idx="96">
                   <c:v>46097</c:v>
                 </c:pt>
+                <c:pt idx="97">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46098</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4203,6 +4302,15 @@
                   <c:v>6.8940000000000001</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>6.8940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6.8940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6.8940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="98">
                   <c:v>6.8940000000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -4543,6 +4651,15 @@
                 <c:pt idx="96">
                   <c:v>46097</c:v>
                 </c:pt>
+                <c:pt idx="97">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46098</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>46098</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4839,6 +4956,15 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>6.5119999999999996</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>6.5119999999999996</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>6.6189999999999998</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>6.6189999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8082,7 +8208,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y99"/>
+  <dimension ref="A1:Y102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -15642,6 +15768,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D99" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E99" s="11">
+        <v>51</v>
+      </c>
+      <c r="F99" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="G99" s="11">
+        <v>39.332999999999998</v>
+      </c>
+      <c r="H99" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I99" s="11">
+        <v>20</v>
+      </c>
+      <c r="J99" s="11">
+        <v>21.2</v>
+      </c>
+      <c r="K99" s="11">
+        <v>88</v>
+      </c>
+      <c r="L99" s="11">
+        <v>26</v>
+      </c>
+      <c r="M99" s="11">
+        <v>77.227000000000004</v>
+      </c>
+      <c r="N99" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O99" s="11">
+        <v>13</v>
+      </c>
+      <c r="P99" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q99" s="11">
+        <v>48</v>
+      </c>
+      <c r="R99" s="11">
+        <v>11.75</v>
+      </c>
+      <c r="S99" s="11">
+        <v>33.58</v>
+      </c>
+      <c r="T99" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U99" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V99" s="11">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="W99" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="X99" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y99" s="11">
+        <v>6.5119999999999996</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A100" s="12">
+        <v>46098</v>
+      </c>
+      <c r="B100" s="12">
+        <v>46098</v>
+      </c>
+      <c r="C100" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E100" s="11">
+        <v>51</v>
+      </c>
+      <c r="F100" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G100" s="11">
+        <v>39.667000000000002</v>
+      </c>
+      <c r="H100" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I100" s="11">
+        <v>20</v>
+      </c>
+      <c r="J100" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K100" s="11">
+        <v>88</v>
+      </c>
+      <c r="L100" s="11">
+        <v>26</v>
+      </c>
+      <c r="M100" s="11">
+        <v>77.364000000000004</v>
+      </c>
+      <c r="N100" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O100" s="11">
+        <v>13</v>
+      </c>
+      <c r="P100" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q100" s="11">
+        <v>48</v>
+      </c>
+      <c r="R100" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S100" s="11">
+        <v>33.68</v>
+      </c>
+      <c r="T100" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U100" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V100" s="11">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="W100" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="X100" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y100" s="11">
+        <v>6.6189999999999998</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A101" s="12">
+        <v>46098</v>
+      </c>
+      <c r="B101" s="12">
+        <v>46098</v>
+      </c>
+      <c r="C101" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E101" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F101" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G101" s="11">
+        <v>39.667000000000002</v>
+      </c>
+      <c r="H101" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I101" s="11">
+        <v>20</v>
+      </c>
+      <c r="J101" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K101" s="11">
+        <v>88</v>
+      </c>
+      <c r="L101" s="11">
+        <v>26</v>
+      </c>
+      <c r="M101" s="11">
+        <v>77.364000000000004</v>
+      </c>
+      <c r="N101" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O101" s="11">
+        <v>13</v>
+      </c>
+      <c r="P101" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q101" s="11">
+        <v>48</v>
+      </c>
+      <c r="R101" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S101" s="11">
+        <v>33.880000000000003</v>
+      </c>
+      <c r="T101" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U101" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V101" s="11">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="W101" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="X101" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y101" s="11">
+        <v>6.6189999999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A102" s="12">
+        <v>46098</v>
+      </c>
+      <c r="B102" s="12">
+        <v>46098</v>
+      </c>
+      <c r="C102" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D102" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18DC94A-2E38-4341-86D5-C7EA38862E92}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378BF811-37CE-4730-B07C-0E2F239F2E32}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -736,6 +736,15 @@
                 <c:pt idx="99">
                   <c:v>46098</c:v>
                 </c:pt>
+                <c:pt idx="100">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>46099</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1041,6 +1050,18 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>39.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>39.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>39.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>39.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>39.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1387,6 +1408,15 @@
                 <c:pt idx="99">
                   <c:v>46098</c:v>
                 </c:pt>
+                <c:pt idx="100">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>46099</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1691,6 +1721,18 @@
                   <c:v>21.5</c:v>
                 </c:pt>
                 <c:pt idx="98">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="102">
                   <c:v>21.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2038,6 +2080,15 @@
                 <c:pt idx="99">
                   <c:v>46098</c:v>
                 </c:pt>
+                <c:pt idx="100">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>46099</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2343,6 +2394,18 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>77.364000000000004</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>77.364000000000004</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>77.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2689,6 +2752,15 @@
                 <c:pt idx="99">
                   <c:v>46098</c:v>
                 </c:pt>
+                <c:pt idx="100">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>46099</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2993,6 +3065,18 @@
                   <c:v>13.75</c:v>
                 </c:pt>
                 <c:pt idx="98">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="102">
                   <c:v>13.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3340,6 +3424,15 @@
                 <c:pt idx="99">
                   <c:v>46098</c:v>
                 </c:pt>
+                <c:pt idx="100">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>46099</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3645,6 +3738,18 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>33.880000000000003</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>33.880000000000003</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>33.9</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>33.9</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>34.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4007,6 +4112,15 @@
                 <c:pt idx="99">
                   <c:v>46098</c:v>
                 </c:pt>
+                <c:pt idx="100">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>46099</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4312,6 +4426,18 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>6.8940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>6.8940000000000001</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6.8879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>6.8879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>6.8879999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4660,6 +4786,15 @@
                 <c:pt idx="99">
                   <c:v>46098</c:v>
                 </c:pt>
+                <c:pt idx="100">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>46099</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>46099</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4965,6 +5100,18 @@
                 </c:pt>
                 <c:pt idx="98">
                   <c:v>6.6189999999999998</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>6.6189999999999998</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>6.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8208,7 +8355,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y102"/>
+  <dimension ref="A1:Y105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -16000,6 +16147,300 @@
       </c>
       <c r="D102" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E102" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F102" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G102" s="11">
+        <v>39.667000000000002</v>
+      </c>
+      <c r="H102" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I102" s="11">
+        <v>20</v>
+      </c>
+      <c r="J102" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K102" s="11">
+        <v>88</v>
+      </c>
+      <c r="L102" s="11">
+        <v>26</v>
+      </c>
+      <c r="M102" s="11">
+        <v>77.364000000000004</v>
+      </c>
+      <c r="N102" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O102" s="11">
+        <v>13</v>
+      </c>
+      <c r="P102" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q102" s="11">
+        <v>48</v>
+      </c>
+      <c r="R102" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S102" s="11">
+        <v>33.880000000000003</v>
+      </c>
+      <c r="T102" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U102" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V102" s="11">
+        <v>6.8940000000000001</v>
+      </c>
+      <c r="W102" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="X102" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="Y102" s="11">
+        <v>6.6189999999999998</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A103" s="12">
+        <v>46099</v>
+      </c>
+      <c r="B103" s="12">
+        <v>46099</v>
+      </c>
+      <c r="C103" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E103" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F103" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G103" s="11">
+        <v>39.832999999999998</v>
+      </c>
+      <c r="H103" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I103" s="11">
+        <v>20</v>
+      </c>
+      <c r="J103" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K103" s="11">
+        <v>88</v>
+      </c>
+      <c r="L103" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M103" s="11">
+        <v>77.5</v>
+      </c>
+      <c r="N103" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O103" s="11">
+        <v>13</v>
+      </c>
+      <c r="P103" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q103" s="11">
+        <v>48</v>
+      </c>
+      <c r="R103" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S103" s="11">
+        <v>33.9</v>
+      </c>
+      <c r="T103" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U103" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V103" s="11">
+        <v>6.8879999999999999</v>
+      </c>
+      <c r="W103" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="X103" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="Y103" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A104" s="12">
+        <v>46099</v>
+      </c>
+      <c r="B104" s="12">
+        <v>46099</v>
+      </c>
+      <c r="C104" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E104" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F104" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G104" s="11">
+        <v>39.832999999999998</v>
+      </c>
+      <c r="H104" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I104" s="11">
+        <v>20</v>
+      </c>
+      <c r="J104" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K104" s="11">
+        <v>88</v>
+      </c>
+      <c r="L104" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M104" s="11">
+        <v>77.5</v>
+      </c>
+      <c r="N104" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O104" s="11">
+        <v>13</v>
+      </c>
+      <c r="P104" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q104" s="11">
+        <v>48</v>
+      </c>
+      <c r="R104" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S104" s="11">
+        <v>33.9</v>
+      </c>
+      <c r="T104" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U104" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V104" s="11">
+        <v>6.8879999999999999</v>
+      </c>
+      <c r="W104" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="X104" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="Y104" s="11">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A105" s="12">
+        <v>46099</v>
+      </c>
+      <c r="B105" s="12">
+        <v>46099</v>
+      </c>
+      <c r="C105" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E105" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F105" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G105" s="11">
+        <v>39.832999999999998</v>
+      </c>
+      <c r="H105" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I105" s="11">
+        <v>20</v>
+      </c>
+      <c r="J105" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K105" s="11">
+        <v>88</v>
+      </c>
+      <c r="L105" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M105" s="11">
+        <v>77.5</v>
+      </c>
+      <c r="N105" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O105" s="11">
+        <v>13</v>
+      </c>
+      <c r="P105" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q105" s="11">
+        <v>48</v>
+      </c>
+      <c r="R105" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S105" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T105" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U105" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V105" s="11">
+        <v>6.8879999999999999</v>
+      </c>
+      <c r="W105" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="X105" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="Y105" s="11">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378BF811-37CE-4730-B07C-0E2F239F2E32}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BDC592-89D1-4281-A731-63A61366E3DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -745,6 +745,15 @@
                 <c:pt idx="102">
                   <c:v>46099</c:v>
                 </c:pt>
+                <c:pt idx="103">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46100</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1061,6 +1070,12 @@
                   <c:v>39.832999999999998</c:v>
                 </c:pt>
                 <c:pt idx="102">
+                  <c:v>39.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>39.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>39.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -1417,6 +1432,15 @@
                 <c:pt idx="102">
                   <c:v>46099</c:v>
                 </c:pt>
+                <c:pt idx="103">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46100</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1733,6 +1757,12 @@
                   <c:v>21.5</c:v>
                 </c:pt>
                 <c:pt idx="102">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>21.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2089,6 +2119,15 @@
                 <c:pt idx="102">
                   <c:v>46099</c:v>
                 </c:pt>
+                <c:pt idx="103">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46100</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2405,6 +2444,12 @@
                   <c:v>77.5</c:v>
                 </c:pt>
                 <c:pt idx="102">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>77.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2761,6 +2806,15 @@
                 <c:pt idx="102">
                   <c:v>46099</c:v>
                 </c:pt>
+                <c:pt idx="103">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46100</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3077,6 +3131,12 @@
                   <c:v>13.75</c:v>
                 </c:pt>
                 <c:pt idx="102">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>13.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3433,6 +3493,15 @@
                 <c:pt idx="102">
                   <c:v>46099</c:v>
                 </c:pt>
+                <c:pt idx="103">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46100</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3749,6 +3818,12 @@
                   <c:v>33.9</c:v>
                 </c:pt>
                 <c:pt idx="102">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>34.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -4121,6 +4196,15 @@
                 <c:pt idx="102">
                   <c:v>46099</c:v>
                 </c:pt>
+                <c:pt idx="103">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46100</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4437,6 +4521,12 @@
                   <c:v>6.8879999999999999</c:v>
                 </c:pt>
                 <c:pt idx="102">
+                  <c:v>6.8879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>6.8879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="104">
                   <c:v>6.8879999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -4795,6 +4885,15 @@
                 <c:pt idx="102">
                   <c:v>46099</c:v>
                 </c:pt>
+                <c:pt idx="103">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46100</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46100</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5112,6 +5211,12 @@
                 </c:pt>
                 <c:pt idx="102">
                   <c:v>6.7</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>6.75</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>6.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5492,7 +5597,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-C247-486A-B615-212EDB24F1C8}"/>
@@ -5588,7 +5693,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-C247-486A-B615-212EDB24F1C8}"/>
@@ -5684,7 +5789,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-C247-486A-B615-212EDB24F1C8}"/>
@@ -5999,7 +6104,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-B192-400F-A953-98DEBDB0B8C6}"/>
@@ -6095,7 +6200,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-B192-400F-A953-98DEBDB0B8C6}"/>
@@ -8355,7 +8460,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y105"/>
+  <dimension ref="A1:Y108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -16441,6 +16546,174 @@
       </c>
       <c r="Y105" s="11">
         <v>6.7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A106" s="12">
+        <v>46100</v>
+      </c>
+      <c r="B106" s="12">
+        <v>46100</v>
+      </c>
+      <c r="C106" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E106" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F106" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G106" s="11">
+        <v>39.832999999999998</v>
+      </c>
+      <c r="H106" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I106" s="11">
+        <v>20</v>
+      </c>
+      <c r="J106" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K106" s="11">
+        <v>88</v>
+      </c>
+      <c r="L106" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M106" s="11">
+        <v>77.5</v>
+      </c>
+      <c r="N106" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O106" s="11">
+        <v>13</v>
+      </c>
+      <c r="P106" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q106" s="11">
+        <v>48</v>
+      </c>
+      <c r="R106" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S106" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T106" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U106" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V106" s="11">
+        <v>6.8879999999999999</v>
+      </c>
+      <c r="W106" s="11">
+        <v>8</v>
+      </c>
+      <c r="X106" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y106" s="11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A107" s="12">
+        <v>46100</v>
+      </c>
+      <c r="B107" s="12">
+        <v>46100</v>
+      </c>
+      <c r="C107" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E107" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F107" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G107" s="11">
+        <v>39.832999999999998</v>
+      </c>
+      <c r="H107" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I107" s="11">
+        <v>20</v>
+      </c>
+      <c r="J107" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K107" s="11">
+        <v>88</v>
+      </c>
+      <c r="L107" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M107" s="11">
+        <v>77.5</v>
+      </c>
+      <c r="N107" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O107" s="11">
+        <v>13</v>
+      </c>
+      <c r="P107" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q107" s="11">
+        <v>48</v>
+      </c>
+      <c r="R107" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S107" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T107" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U107" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V107" s="11">
+        <v>6.8879999999999999</v>
+      </c>
+      <c r="W107" s="11">
+        <v>8</v>
+      </c>
+      <c r="X107" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y107" s="11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A108" s="12">
+        <v>46100</v>
+      </c>
+      <c r="B108" s="12">
+        <v>46100</v>
+      </c>
+      <c r="C108" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BDC592-89D1-4281-A731-63A61366E3DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68A60C9-61BB-4D73-A21A-E8FD8F2823D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -754,6 +754,15 @@
                 <c:pt idx="105">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46101</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1077,6 +1086,18 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>39.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>39.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>39.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>39.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>39.167000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1441,6 +1462,15 @@
                 <c:pt idx="105">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46101</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1763,6 +1793,18 @@
                   <c:v>21.5</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>21.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2128,6 +2170,15 @@
                 <c:pt idx="105">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46101</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2450,6 +2501,18 @@
                   <c:v>77.5</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>77.5</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>77.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -2815,6 +2878,15 @@
                 <c:pt idx="105">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46101</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3137,6 +3209,18 @@
                   <c:v>13.75</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>13.75</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>13.75</c:v>
                 </c:pt>
               </c:numCache>
@@ -3502,6 +3586,15 @@
                 <c:pt idx="105">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46101</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3824,6 +3917,18 @@
                   <c:v>34.1</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>34.1</c:v>
                 </c:pt>
               </c:numCache>
@@ -4205,6 +4310,15 @@
                 <c:pt idx="105">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46101</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4528,6 +4642,18 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>6.8879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>6.8879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>6.8769999999999998</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>6.8769999999999998</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6.8769999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4894,6 +5020,15 @@
                 <c:pt idx="105">
                   <c:v>46100</c:v>
                 </c:pt>
+                <c:pt idx="106">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46101</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5217,6 +5352,18 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>6.75</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>6.75</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>6.8879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>6.8879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>6.8879999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8460,7 +8607,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y108"/>
+  <dimension ref="A1:Y111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -16714,6 +16861,300 @@
       </c>
       <c r="D108" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E108" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F108" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G108" s="11">
+        <v>39.832999999999998</v>
+      </c>
+      <c r="H108" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I108" s="11">
+        <v>20</v>
+      </c>
+      <c r="J108" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K108" s="11">
+        <v>88</v>
+      </c>
+      <c r="L108" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M108" s="11">
+        <v>77.5</v>
+      </c>
+      <c r="N108" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O108" s="11">
+        <v>13</v>
+      </c>
+      <c r="P108" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q108" s="11">
+        <v>48</v>
+      </c>
+      <c r="R108" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S108" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T108" s="11">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="U108" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V108" s="11">
+        <v>6.8879999999999999</v>
+      </c>
+      <c r="W108" s="11">
+        <v>8</v>
+      </c>
+      <c r="X108" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y108" s="11">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A109" s="12">
+        <v>46101</v>
+      </c>
+      <c r="B109" s="12">
+        <v>46101</v>
+      </c>
+      <c r="C109" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E109" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F109" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G109" s="11">
+        <v>39.832999999999998</v>
+      </c>
+      <c r="H109" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I109" s="11">
+        <v>20</v>
+      </c>
+      <c r="J109" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K109" s="11">
+        <v>88</v>
+      </c>
+      <c r="L109" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M109" s="11">
+        <v>77.5</v>
+      </c>
+      <c r="N109" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O109" s="11">
+        <v>13</v>
+      </c>
+      <c r="P109" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q109" s="11">
+        <v>48</v>
+      </c>
+      <c r="R109" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S109" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T109" s="11">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="U109" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V109" s="11">
+        <v>6.8769999999999998</v>
+      </c>
+      <c r="W109" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="X109" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y109" s="11">
+        <v>6.8879999999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A110" s="12">
+        <v>46101</v>
+      </c>
+      <c r="B110" s="12">
+        <v>46101</v>
+      </c>
+      <c r="C110" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E110" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F110" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G110" s="11">
+        <v>39.167000000000002</v>
+      </c>
+      <c r="H110" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I110" s="11">
+        <v>20</v>
+      </c>
+      <c r="J110" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K110" s="11">
+        <v>88</v>
+      </c>
+      <c r="L110" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M110" s="11">
+        <v>77.5</v>
+      </c>
+      <c r="N110" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O110" s="11">
+        <v>13</v>
+      </c>
+      <c r="P110" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q110" s="11">
+        <v>48</v>
+      </c>
+      <c r="R110" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S110" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T110" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="U110" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V110" s="11">
+        <v>6.8769999999999998</v>
+      </c>
+      <c r="W110" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="X110" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y110" s="11">
+        <v>6.8879999999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A111" s="12">
+        <v>46101</v>
+      </c>
+      <c r="B111" s="12">
+        <v>46101</v>
+      </c>
+      <c r="C111" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E111" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="F111" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="G111" s="11">
+        <v>39.167000000000002</v>
+      </c>
+      <c r="H111" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="I111" s="11">
+        <v>20</v>
+      </c>
+      <c r="J111" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K111" s="11">
+        <v>88</v>
+      </c>
+      <c r="L111" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="M111" s="11">
+        <v>77.5</v>
+      </c>
+      <c r="N111" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="O111" s="11">
+        <v>13</v>
+      </c>
+      <c r="P111" s="11">
+        <v>13.75</v>
+      </c>
+      <c r="Q111" s="11">
+        <v>48</v>
+      </c>
+      <c r="R111" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="S111" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T111" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="U111" s="11">
+        <v>5.75</v>
+      </c>
+      <c r="V111" s="11">
+        <v>6.8769999999999998</v>
+      </c>
+      <c r="W111" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="X111" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y111" s="11">
+        <v>6.8879999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C68A60C9-61BB-4D73-A21A-E8FD8F2823D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7037A6FB-E481-E048-84C8-A5721F4EEE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13580" yWindow="780" windowWidth="22420" windowHeight="20680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -244,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,27 +337,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -365,8 +365,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +384,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -763,6 +763,15 @@
                 <c:pt idx="108">
                   <c:v>46101</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46104</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1471,6 +1480,15 @@
                 <c:pt idx="108">
                   <c:v>46101</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46104</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2179,6 +2197,15 @@
                 <c:pt idx="108">
                   <c:v>46101</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46104</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2887,6 +2914,15 @@
                 <c:pt idx="108">
                   <c:v>46101</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46104</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3594,6 +3630,15 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4319,6 +4364,15 @@
                 <c:pt idx="108">
                   <c:v>46101</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46104</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5028,6 +5082,15 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46101</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46104</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5598,6 +5661,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5605,7 +5669,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5638,7 +5701,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6105,6 +6168,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6112,7 +6176,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6145,7 +6208,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6212,7 +6275,7 @@
                 <c:pt idx="4">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="m/d/yyyy">
+                <c:pt idx="5" formatCode="m/d/yy">
                   <c:v>46090</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -6308,7 +6371,7 @@
                 <c:pt idx="4">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="m/d/yyyy">
+                <c:pt idx="5" formatCode="m/d/yy">
                   <c:v>46090</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -6517,6 +6580,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6524,7 +6588,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8607,18 +8670,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y111"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y114"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -8695,7 +8758,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -8764,7 +8827,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -8841,7 +8904,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -8918,7 +8981,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -8995,7 +9058,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -9072,7 +9135,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -9149,7 +9212,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -9226,7 +9289,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -9303,7 +9366,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -9380,7 +9443,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -9457,7 +9520,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -9534,7 +9597,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -9611,7 +9674,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -9688,7 +9751,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -9765,7 +9828,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -9842,7 +9905,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -9919,7 +9982,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -9996,7 +10059,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -10073,7 +10136,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -10150,7 +10213,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -10227,7 +10290,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -10304,7 +10367,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -10381,7 +10444,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -10458,7 +10521,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -10535,7 +10598,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -10612,7 +10675,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -10689,7 +10752,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -10766,7 +10829,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -10843,7 +10906,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -10920,7 +10983,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -10997,7 +11060,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -11074,7 +11137,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -11151,7 +11214,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -11228,7 +11291,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -11305,7 +11368,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -11382,7 +11445,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -11459,7 +11522,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -11536,7 +11599,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -11613,7 +11676,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -11690,7 +11753,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -11767,7 +11830,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -11844,7 +11907,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -11921,7 +11984,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -11998,7 +12061,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -12075,7 +12138,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -12152,7 +12215,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -12229,7 +12292,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -12306,7 +12369,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -12383,7 +12446,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -12460,7 +12523,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -12537,7 +12600,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -12614,7 +12677,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -12691,7 +12754,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -12768,7 +12831,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -12845,7 +12908,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -12922,7 +12985,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -12999,7 +13062,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -13076,7 +13139,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -13153,7 +13216,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -13230,7 +13293,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -13307,7 +13370,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -13384,7 +13447,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -13461,7 +13524,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -13538,7 +13601,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -13615,7 +13678,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -13692,7 +13755,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -13769,7 +13832,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -13846,7 +13909,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -13923,7 +13986,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -14000,7 +14063,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -14077,7 +14140,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -14154,7 +14217,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -14231,7 +14294,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -14308,7 +14371,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -14385,7 +14448,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -14462,7 +14525,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -14539,7 +14602,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -14616,7 +14679,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -14693,7 +14756,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -14770,7 +14833,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -14847,7 +14910,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -14924,7 +14987,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -15001,7 +15064,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -15078,7 +15141,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -15155,7 +15218,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -15232,7 +15295,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -15309,7 +15372,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -15386,7 +15449,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -15463,7 +15526,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -15540,7 +15603,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -15617,7 +15680,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -15694,7 +15757,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -15771,7 +15834,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -15848,7 +15911,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -15925,7 +15988,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -16002,7 +16065,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -16079,7 +16142,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -16156,7 +16219,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -16233,7 +16296,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -16310,7 +16373,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -16387,7 +16450,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -16464,7 +16527,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -16541,7 +16604,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -16618,7 +16681,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -16695,7 +16758,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -16772,7 +16835,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -16849,7 +16912,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -16926,7 +16989,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -17003,7 +17066,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -17080,7 +17143,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -17155,6 +17218,48 @@
       </c>
       <c r="Y111" s="11">
         <v>6.8879999999999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25">
+      <c r="A112" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B112" s="12">
+        <v>46104</v>
+      </c>
+      <c r="C112" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B113" s="12">
+        <v>46104</v>
+      </c>
+      <c r="C113" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B114" s="12">
+        <v>46104</v>
+      </c>
+      <c r="C114" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -17173,17 +17278,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -17272,7 +17377,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -17353,7 +17458,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -17442,7 +17547,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -17531,7 +17636,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -17550,12 +17655,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
     <col min="7" max="7" width="9" style="11"/>
     <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
@@ -17566,7 +17671,7 @@
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -17619,7 +17724,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -17664,7 +17769,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -17717,7 +17822,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -17770,7 +17875,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -17811,7 +17916,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -17852,7 +17957,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -17893,7 +17998,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -17934,7 +18039,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -17991,18 +18096,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -18049,7 +18154,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -18088,7 +18193,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -18135,7 +18240,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -18182,7 +18287,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -18214,7 +18319,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -18246,7 +18351,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -18278,7 +18383,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="6">
         <v>46083</v>
       </c>
@@ -18310,7 +18415,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -18357,7 +18462,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -18371,15 +18476,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -18390,7 +18495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -18404,7 +18509,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -18413,7 +18518,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -18422,7 +18527,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -18431,7 +18536,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -18440,7 +18545,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -18449,7 +18554,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -18458,7 +18563,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -18467,49 +18572,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -18520,7 +18625,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -18529,7 +18634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -18538,7 +18643,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -18549,7 +18654,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -18558,7 +18663,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -18567,42 +18672,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -18611,35 +18716,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/industry/TrendForce/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7037A6FB-E481-E048-84C8-A5721F4EEE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFBC2F4-0A0E-4182-8D61-60A5EBD93B37}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13580" yWindow="780" windowWidth="22420" windowHeight="20680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -244,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,27 +337,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -365,8 +365,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +384,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1108,6 +1108,15 @@
                 <c:pt idx="108">
                   <c:v>39.167000000000002</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1825,6 +1834,15 @@
                 <c:pt idx="108">
                   <c:v>21.5</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>21.45</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2542,6 +2560,15 @@
                 <c:pt idx="108">
                   <c:v>77.5</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>76.954999999999998</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>76.954999999999998</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>76.614000000000004</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3259,6 +3286,15 @@
                 <c:pt idx="108">
                   <c:v>13.75</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>13.675000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3975,6 +4011,15 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>34.1</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4709,6 +4754,15 @@
                 <c:pt idx="108">
                   <c:v>6.8769999999999998</c:v>
                 </c:pt>
+                <c:pt idx="109">
+                  <c:v>6.8730000000000002</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>6.8730000000000002</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>6.8730000000000002</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5427,6 +5481,15 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>6.8879999999999999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>6.95</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>6.95</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>6.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5661,7 +5724,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5669,6 +5731,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5701,7 +5764,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6168,7 +6231,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6176,6 +6238,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6208,7 +6271,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6275,7 +6338,7 @@
                 <c:pt idx="4">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="m/d/yy">
+                <c:pt idx="5" formatCode="m/d/yyyy">
                   <c:v>46090</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -6371,7 +6434,7 @@
                 <c:pt idx="4">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="m/d/yy">
+                <c:pt idx="5" formatCode="m/d/yyyy">
                   <c:v>46090</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -6580,7 +6643,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6588,6 +6650,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8671,17 +8734,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y114"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -8758,7 +8821,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -8827,7 +8890,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -8904,7 +8967,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -8981,7 +9044,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -9058,7 +9121,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -9135,7 +9198,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -9212,7 +9275,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -9289,7 +9352,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -9366,7 +9429,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -9443,7 +9506,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -9520,7 +9583,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -9597,7 +9660,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -9674,7 +9737,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -9751,7 +9814,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -9828,7 +9891,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -9905,7 +9968,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -9982,7 +10045,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -10059,7 +10122,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -10136,7 +10199,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -10213,7 +10276,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -10290,7 +10353,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -10367,7 +10430,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -10444,7 +10507,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -10521,7 +10584,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -10598,7 +10661,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -10675,7 +10738,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -10752,7 +10815,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -10829,7 +10892,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -10906,7 +10969,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -10983,7 +11046,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -11060,7 +11123,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -11137,7 +11200,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -11214,7 +11277,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -11291,7 +11354,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -11368,7 +11431,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -11445,7 +11508,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -11522,7 +11585,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -11599,7 +11662,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -11676,7 +11739,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -11753,7 +11816,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -11830,7 +11893,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -11907,7 +11970,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -11984,7 +12047,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -12061,7 +12124,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -12138,7 +12201,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -12215,7 +12278,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -12292,7 +12355,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -12369,7 +12432,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -12446,7 +12509,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -12523,7 +12586,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -12600,7 +12663,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -12677,7 +12740,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -12754,7 +12817,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -12831,7 +12894,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -12908,7 +12971,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -12985,7 +13048,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -13062,7 +13125,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -13139,7 +13202,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -13216,7 +13279,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -13293,7 +13356,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -13370,7 +13433,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -13447,7 +13510,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -13524,7 +13587,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -13601,7 +13664,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -13678,7 +13741,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -13755,7 +13818,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -13832,7 +13895,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -13909,7 +13972,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -13986,7 +14049,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -14063,7 +14126,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -14140,7 +14203,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -14217,7 +14280,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -14294,7 +14357,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -14371,7 +14434,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -14448,7 +14511,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -14525,7 +14588,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -14602,7 +14665,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -14679,7 +14742,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -14756,7 +14819,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -14833,7 +14896,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -14910,7 +14973,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -14987,7 +15050,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -15064,7 +15127,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -15141,7 +15204,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -15218,7 +15281,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -15295,7 +15358,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -15372,7 +15435,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -15449,7 +15512,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -15526,7 +15589,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -15603,7 +15666,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -15680,7 +15743,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -15757,7 +15820,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -15834,7 +15897,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -15911,7 +15974,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -15988,7 +16051,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -16065,7 +16128,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -16142,7 +16205,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -16219,7 +16282,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -16296,7 +16359,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -16373,7 +16436,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -16450,7 +16513,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -16527,7 +16590,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -16604,7 +16667,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -16681,7 +16744,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -16758,7 +16821,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -16835,7 +16898,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -16912,7 +16975,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -16989,7 +17052,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -17066,7 +17129,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -17143,7 +17206,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -17220,7 +17283,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -17233,8 +17296,71 @@
       <c r="D112" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="E112" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F112" s="11">
+        <v>25</v>
+      </c>
+      <c r="G112" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H112" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I112" s="11">
+        <v>20</v>
+      </c>
+      <c r="J112" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K112" s="11">
+        <v>88</v>
+      </c>
+      <c r="L112" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="M112" s="11">
+        <v>76.954999999999998</v>
+      </c>
+      <c r="N112" s="11">
+        <v>15</v>
+      </c>
+      <c r="O112" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P112" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q112" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R112" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="S112" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T112" s="11">
+        <v>8</v>
+      </c>
+      <c r="U112" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V112" s="11">
+        <v>6.8730000000000002</v>
+      </c>
+      <c r="W112" s="11">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="X112" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y112" s="11">
+        <v>6.95</v>
+      </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -17247,8 +17373,71 @@
       <c r="D113" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="E113" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="F113" s="11">
+        <v>25</v>
+      </c>
+      <c r="G113" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H113" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I113" s="11">
+        <v>20</v>
+      </c>
+      <c r="J113" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K113" s="11">
+        <v>88</v>
+      </c>
+      <c r="L113" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="M113" s="11">
+        <v>76.954999999999998</v>
+      </c>
+      <c r="N113" s="11">
+        <v>15</v>
+      </c>
+      <c r="O113" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P113" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q113" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R113" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="S113" s="11">
+        <v>34.1</v>
+      </c>
+      <c r="T113" s="11">
+        <v>8</v>
+      </c>
+      <c r="U113" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V113" s="11">
+        <v>6.8730000000000002</v>
+      </c>
+      <c r="W113" s="11">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="X113" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y113" s="11">
+        <v>6.95</v>
+      </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -17260,6 +17449,69 @@
       </c>
       <c r="D114" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E114" s="11">
+        <v>52</v>
+      </c>
+      <c r="F114" s="11">
+        <v>25</v>
+      </c>
+      <c r="G114" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H114" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I114" s="11">
+        <v>20</v>
+      </c>
+      <c r="J114" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K114" s="11">
+        <v>88</v>
+      </c>
+      <c r="L114" s="11">
+        <v>25.5</v>
+      </c>
+      <c r="M114" s="11">
+        <v>76.614000000000004</v>
+      </c>
+      <c r="N114" s="11">
+        <v>15</v>
+      </c>
+      <c r="O114" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P114" s="11">
+        <v>13.675000000000001</v>
+      </c>
+      <c r="Q114" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R114" s="11">
+        <v>11.6</v>
+      </c>
+      <c r="S114" s="11">
+        <v>34</v>
+      </c>
+      <c r="T114" s="11">
+        <v>8</v>
+      </c>
+      <c r="U114" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V114" s="11">
+        <v>6.8730000000000002</v>
+      </c>
+      <c r="W114" s="11">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="X114" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y114" s="11">
+        <v>6.95</v>
       </c>
     </row>
   </sheetData>
@@ -17278,17 +17530,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -17377,7 +17629,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -17458,7 +17710,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -17547,7 +17799,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -17636,7 +17888,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -17654,13 +17906,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
-  <dimension ref="A1:Y9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
     <col min="7" max="7" width="9" style="11"/>
     <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
@@ -17671,7 +17923,7 @@
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -17724,7 +17976,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -17769,7 +18021,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -17822,7 +18074,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -17875,7 +18127,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -17916,7 +18168,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -17957,7 +18209,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -17998,7 +18250,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -18039,7 +18291,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -18078,6 +18330,47 @@
       </c>
       <c r="M9" s="11">
         <v>126.667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A10" s="12">
+        <v>46097</v>
+      </c>
+      <c r="B10" s="12">
+        <v>46104</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="14">
+        <v>245</v>
+      </c>
+      <c r="F10" s="14">
+        <v>205</v>
+      </c>
+      <c r="G10" s="11">
+        <v>232.5</v>
+      </c>
+      <c r="H10" s="14">
+        <v>1050</v>
+      </c>
+      <c r="I10" s="14">
+        <v>860</v>
+      </c>
+      <c r="J10" s="11">
+        <v>917.5</v>
+      </c>
+      <c r="K10" s="14">
+        <v>162</v>
+      </c>
+      <c r="L10" s="14">
+        <v>120</v>
+      </c>
+      <c r="M10" s="11">
+        <v>132.333</v>
       </c>
     </row>
   </sheetData>
@@ -18095,19 +18388,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
-  <dimension ref="A1:Y9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:Y10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -18154,7 +18447,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -18193,7 +18486,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -18240,7 +18533,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -18287,7 +18580,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -18319,7 +18612,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -18351,7 +18644,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -18383,7 +18676,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>46083</v>
       </c>
@@ -18415,7 +18708,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -18445,6 +18738,38 @@
       </c>
       <c r="J9" s="11">
         <v>11.462</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A10" s="12">
+        <v>46097</v>
+      </c>
+      <c r="B10" s="12">
+        <v>46104</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="11">
+        <v>17</v>
+      </c>
+      <c r="F10" s="11">
+        <v>10</v>
+      </c>
+      <c r="G10" s="11">
+        <v>11.682</v>
+      </c>
+      <c r="H10" s="11">
+        <v>18</v>
+      </c>
+      <c r="I10" s="11">
+        <v>10</v>
+      </c>
+      <c r="J10" s="11">
+        <v>11.962</v>
       </c>
     </row>
   </sheetData>
@@ -18462,7 +18787,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -18476,15 +18801,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -18495,7 +18820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -18509,7 +18834,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -18518,7 +18843,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -18527,7 +18852,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -18536,7 +18861,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -18545,7 +18870,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -18554,7 +18879,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -18563,7 +18888,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -18572,49 +18897,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -18625,7 +18950,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -18634,7 +18959,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -18643,7 +18968,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -18654,7 +18979,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -18663,7 +18988,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -18672,42 +18997,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -18716,35 +19041,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADFBC2F4-0A0E-4182-8D61-60A5EBD93B37}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4BC023-2D15-41B0-AC73-A46008171031}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -772,6 +772,15 @@
                 <c:pt idx="111">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1116,6 +1125,12 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>38.332999999999998</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>38.167000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1498,6 +1513,15 @@
                 <c:pt idx="111">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1841,6 +1865,12 @@
                   <c:v>21.45</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>21.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -2224,6 +2254,15 @@
                 <c:pt idx="111">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2568,6 +2607,12 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>76.614000000000004</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>76.067999999999998</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>76.067999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2950,6 +2995,15 @@
                 <c:pt idx="111">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3294,6 +3348,12 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>13.675000000000001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>13.625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3676,6 +3736,15 @@
                 <c:pt idx="111">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4019,6 +4088,12 @@
                   <c:v>34.1</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -4418,6 +4493,15 @@
                 <c:pt idx="111">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4761,6 +4845,12 @@
                   <c:v>6.8730000000000002</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>6.8730000000000002</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>6.8730000000000002</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>6.8730000000000002</c:v>
                 </c:pt>
               </c:numCache>
@@ -5146,6 +5236,15 @@
                 <c:pt idx="111">
                   <c:v>46104</c:v>
                 </c:pt>
+                <c:pt idx="112">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46105</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46105</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5490,6 +5589,12 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>6.95</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>7.0250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>7.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5522,7 +5627,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="yyyy/mm;@" sourceLinked="0"/>
+        <c:numFmt formatCode="yyyy/mm/dd;@" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5551,8 +5656,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -5706,7 +5811,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="700" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -5748,7 +5853,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ko-KR"/>
     </a:p>
@@ -6118,8 +6226,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -6178,8 +6286,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -6220,8 +6328,8 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
@@ -6255,7 +6363,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ko-KR"/>
     </a:p>
@@ -6529,8 +6640,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -6590,8 +6701,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -6632,8 +6743,8 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
@@ -6667,7 +6778,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ko-KR"/>
     </a:p>
@@ -8733,7 +8847,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y114"/>
+  <dimension ref="A1:Y117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -17512,6 +17626,174 @@
       </c>
       <c r="Y114" s="11">
         <v>6.95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A115" s="12">
+        <v>46105</v>
+      </c>
+      <c r="B115" s="12">
+        <v>46105</v>
+      </c>
+      <c r="C115" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E115" s="11">
+        <v>52</v>
+      </c>
+      <c r="F115" s="11">
+        <v>25</v>
+      </c>
+      <c r="G115" s="11">
+        <v>38.332999999999998</v>
+      </c>
+      <c r="H115" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I115" s="11">
+        <v>20</v>
+      </c>
+      <c r="J115" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K115" s="11">
+        <v>88</v>
+      </c>
+      <c r="L115" s="11">
+        <v>26</v>
+      </c>
+      <c r="M115" s="11">
+        <v>76.067999999999998</v>
+      </c>
+      <c r="N115" s="11">
+        <v>15</v>
+      </c>
+      <c r="O115" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P115" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q115" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R115" s="11">
+        <v>12</v>
+      </c>
+      <c r="S115" s="11">
+        <v>34</v>
+      </c>
+      <c r="T115" s="11">
+        <v>8</v>
+      </c>
+      <c r="U115" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V115" s="11">
+        <v>6.8730000000000002</v>
+      </c>
+      <c r="W115" s="11">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="X115" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y115" s="11">
+        <v>7.0250000000000004</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A116" s="12">
+        <v>46105</v>
+      </c>
+      <c r="B116" s="12">
+        <v>46105</v>
+      </c>
+      <c r="C116" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E116" s="11">
+        <v>50</v>
+      </c>
+      <c r="F116" s="11">
+        <v>25</v>
+      </c>
+      <c r="G116" s="11">
+        <v>38.167000000000002</v>
+      </c>
+      <c r="H116" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I116" s="11">
+        <v>20</v>
+      </c>
+      <c r="J116" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K116" s="11">
+        <v>88</v>
+      </c>
+      <c r="L116" s="11">
+        <v>26</v>
+      </c>
+      <c r="M116" s="11">
+        <v>76.067999999999998</v>
+      </c>
+      <c r="N116" s="11">
+        <v>15</v>
+      </c>
+      <c r="O116" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P116" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q116" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R116" s="11">
+        <v>12</v>
+      </c>
+      <c r="S116" s="11">
+        <v>34</v>
+      </c>
+      <c r="T116" s="11">
+        <v>8</v>
+      </c>
+      <c r="U116" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V116" s="11">
+        <v>6.8730000000000002</v>
+      </c>
+      <c r="W116" s="11">
+        <v>8.9</v>
+      </c>
+      <c r="X116" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y116" s="11">
+        <v>7.125</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A117" s="12">
+        <v>46105</v>
+      </c>
+      <c r="B117" s="12">
+        <v>46105</v>
+      </c>
+      <c r="C117" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F4BC023-2D15-41B0-AC73-A46008171031}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13E4302-C87D-4EEC-907E-97C9107AB10C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -781,6 +781,15 @@
                 <c:pt idx="114">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>46106</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1130,6 +1139,15 @@
                   <c:v>38.332999999999998</c:v>
                 </c:pt>
                 <c:pt idx="113">
+                  <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="116">
                   <c:v>38.167000000000002</c:v>
                 </c:pt>
               </c:numCache>
@@ -1522,6 +1540,15 @@
                 <c:pt idx="114">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>46106</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1871,6 +1898,15 @@
                   <c:v>21.45</c:v>
                 </c:pt>
                 <c:pt idx="113">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="116">
                   <c:v>21.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -2263,6 +2299,15 @@
                 <c:pt idx="114">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>46106</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2613,6 +2658,15 @@
                 </c:pt>
                 <c:pt idx="113">
                   <c:v>76.067999999999998</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>76.067999999999998</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>75.727000000000004</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>75.727000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3004,6 +3058,15 @@
                 <c:pt idx="114">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>46106</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3353,6 +3416,15 @@
                   <c:v>13.625</c:v>
                 </c:pt>
                 <c:pt idx="113">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="116">
                   <c:v>13.625</c:v>
                 </c:pt>
               </c:numCache>
@@ -3745,6 +3817,15 @@
                 <c:pt idx="114">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>46106</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4094,6 +4175,15 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="113">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="116">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -4502,6 +4592,15 @@
                 <c:pt idx="114">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>46106</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4852,6 +4951,15 @@
                 </c:pt>
                 <c:pt idx="113">
                   <c:v>6.8730000000000002</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>6.8730000000000002</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>6.8630000000000004</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>6.8630000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5245,6 +5353,15 @@
                 <c:pt idx="114">
                   <c:v>46105</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>46106</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>46106</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5595,6 +5712,15 @@
                 </c:pt>
                 <c:pt idx="113">
                   <c:v>7.125</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>7.125</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>7.15</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>7.2249999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8847,7 +8973,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y117"/>
+  <dimension ref="A1:Y120"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -17793,6 +17919,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D117" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E117" s="11">
+        <v>50</v>
+      </c>
+      <c r="F117" s="11">
+        <v>25</v>
+      </c>
+      <c r="G117" s="11">
+        <v>38.167000000000002</v>
+      </c>
+      <c r="H117" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I117" s="11">
+        <v>20</v>
+      </c>
+      <c r="J117" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K117" s="11">
+        <v>88</v>
+      </c>
+      <c r="L117" s="11">
+        <v>26</v>
+      </c>
+      <c r="M117" s="11">
+        <v>76.067999999999998</v>
+      </c>
+      <c r="N117" s="11">
+        <v>15</v>
+      </c>
+      <c r="O117" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P117" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q117" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R117" s="11">
+        <v>12</v>
+      </c>
+      <c r="S117" s="11">
+        <v>34</v>
+      </c>
+      <c r="T117" s="11">
+        <v>8</v>
+      </c>
+      <c r="U117" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V117" s="11">
+        <v>6.8730000000000002</v>
+      </c>
+      <c r="W117" s="11">
+        <v>8.9</v>
+      </c>
+      <c r="X117" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y117" s="11">
+        <v>7.125</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A118" s="12">
+        <v>46106</v>
+      </c>
+      <c r="B118" s="12">
+        <v>46106</v>
+      </c>
+      <c r="C118" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E118" s="11">
+        <v>50</v>
+      </c>
+      <c r="F118" s="11">
+        <v>25</v>
+      </c>
+      <c r="G118" s="11">
+        <v>38.167000000000002</v>
+      </c>
+      <c r="H118" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I118" s="11">
+        <v>20</v>
+      </c>
+      <c r="J118" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K118" s="11">
+        <v>88</v>
+      </c>
+      <c r="L118" s="11">
+        <v>26</v>
+      </c>
+      <c r="M118" s="11">
+        <v>75.727000000000004</v>
+      </c>
+      <c r="N118" s="11">
+        <v>15</v>
+      </c>
+      <c r="O118" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P118" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q118" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R118" s="11">
+        <v>12</v>
+      </c>
+      <c r="S118" s="11">
+        <v>34</v>
+      </c>
+      <c r="T118" s="11">
+        <v>8</v>
+      </c>
+      <c r="U118" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V118" s="11">
+        <v>6.8630000000000004</v>
+      </c>
+      <c r="W118" s="11">
+        <v>9</v>
+      </c>
+      <c r="X118" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="Y118" s="11">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A119" s="12">
+        <v>46106</v>
+      </c>
+      <c r="B119" s="12">
+        <v>46106</v>
+      </c>
+      <c r="C119" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E119" s="11">
+        <v>50</v>
+      </c>
+      <c r="F119" s="11">
+        <v>25</v>
+      </c>
+      <c r="G119" s="11">
+        <v>38.167000000000002</v>
+      </c>
+      <c r="H119" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I119" s="11">
+        <v>20</v>
+      </c>
+      <c r="J119" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K119" s="11">
+        <v>88</v>
+      </c>
+      <c r="L119" s="11">
+        <v>26</v>
+      </c>
+      <c r="M119" s="11">
+        <v>75.727000000000004</v>
+      </c>
+      <c r="N119" s="11">
+        <v>15</v>
+      </c>
+      <c r="O119" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P119" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q119" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R119" s="11">
+        <v>12</v>
+      </c>
+      <c r="S119" s="11">
+        <v>34</v>
+      </c>
+      <c r="T119" s="11">
+        <v>8</v>
+      </c>
+      <c r="U119" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V119" s="11">
+        <v>6.8630000000000004</v>
+      </c>
+      <c r="W119" s="11">
+        <v>9.1</v>
+      </c>
+      <c r="X119" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="Y119" s="11">
+        <v>7.2249999999999996</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A120" s="12">
+        <v>46106</v>
+      </c>
+      <c r="B120" s="12">
+        <v>46106</v>
+      </c>
+      <c r="C120" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D120" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13E4302-C87D-4EEC-907E-97C9107AB10C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88C1A74-E997-4267-B11B-A25D2F625D43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -790,6 +790,15 @@
                 <c:pt idx="117">
                   <c:v>46106</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>46107</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1149,6 +1158,15 @@
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>38.167000000000002</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>37.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1549,6 +1567,15 @@
                 <c:pt idx="117">
                   <c:v>46106</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>46107</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1907,6 +1934,15 @@
                   <c:v>21.45</c:v>
                 </c:pt>
                 <c:pt idx="116">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="119">
                   <c:v>21.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -2308,6 +2344,15 @@
                 <c:pt idx="117">
                   <c:v>46106</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>46107</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2667,6 +2712,15 @@
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>75.727000000000004</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>75.727000000000004</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>75.5</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>75.364000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3067,6 +3121,15 @@
                 <c:pt idx="117">
                   <c:v>46106</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>46107</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3425,6 +3488,15 @@
                   <c:v>13.625</c:v>
                 </c:pt>
                 <c:pt idx="116">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="119">
                   <c:v>13.625</c:v>
                 </c:pt>
               </c:numCache>
@@ -3826,6 +3898,15 @@
                 <c:pt idx="117">
                   <c:v>46106</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>46107</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4184,6 +4265,15 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="116">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="119">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -4601,6 +4691,15 @@
                 <c:pt idx="117">
                   <c:v>46106</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>46107</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4960,6 +5059,15 @@
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>6.8630000000000004</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>6.8630000000000004</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>6.8520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>6.8520000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5362,6 +5470,15 @@
                 <c:pt idx="117">
                   <c:v>46106</c:v>
                 </c:pt>
+                <c:pt idx="118">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>46107</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>46107</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5721,6 +5838,15 @@
                 </c:pt>
                 <c:pt idx="116">
                   <c:v>7.2249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>7.2249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>7.3250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>7.3250000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8973,7 +9099,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y120"/>
+  <dimension ref="A1:Y123"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -18150,6 +18276,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D120" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E120" s="11">
+        <v>50</v>
+      </c>
+      <c r="F120" s="11">
+        <v>25</v>
+      </c>
+      <c r="G120" s="11">
+        <v>38.167000000000002</v>
+      </c>
+      <c r="H120" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I120" s="11">
+        <v>20</v>
+      </c>
+      <c r="J120" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K120" s="11">
+        <v>88</v>
+      </c>
+      <c r="L120" s="11">
+        <v>26</v>
+      </c>
+      <c r="M120" s="11">
+        <v>75.727000000000004</v>
+      </c>
+      <c r="N120" s="11">
+        <v>15</v>
+      </c>
+      <c r="O120" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P120" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q120" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R120" s="11">
+        <v>12</v>
+      </c>
+      <c r="S120" s="11">
+        <v>34</v>
+      </c>
+      <c r="T120" s="11">
+        <v>8</v>
+      </c>
+      <c r="U120" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V120" s="11">
+        <v>6.8630000000000004</v>
+      </c>
+      <c r="W120" s="11">
+        <v>9.1</v>
+      </c>
+      <c r="X120" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="Y120" s="11">
+        <v>7.2249999999999996</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A121" s="12">
+        <v>46107</v>
+      </c>
+      <c r="B121" s="12">
+        <v>46107</v>
+      </c>
+      <c r="C121" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E121" s="11">
+        <v>50</v>
+      </c>
+      <c r="F121" s="11">
+        <v>25</v>
+      </c>
+      <c r="G121" s="11">
+        <v>38</v>
+      </c>
+      <c r="H121" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I121" s="11">
+        <v>20</v>
+      </c>
+      <c r="J121" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K121" s="11">
+        <v>88</v>
+      </c>
+      <c r="L121" s="11">
+        <v>26</v>
+      </c>
+      <c r="M121" s="11">
+        <v>75.5</v>
+      </c>
+      <c r="N121" s="11">
+        <v>15</v>
+      </c>
+      <c r="O121" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P121" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q121" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R121" s="11">
+        <v>12</v>
+      </c>
+      <c r="S121" s="11">
+        <v>34</v>
+      </c>
+      <c r="T121" s="11">
+        <v>8</v>
+      </c>
+      <c r="U121" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V121" s="11">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="W121" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="X121" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y121" s="11">
+        <v>7.3250000000000002</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A122" s="12">
+        <v>46107</v>
+      </c>
+      <c r="B122" s="12">
+        <v>46107</v>
+      </c>
+      <c r="C122" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E122" s="11">
+        <v>50</v>
+      </c>
+      <c r="F122" s="11">
+        <v>25</v>
+      </c>
+      <c r="G122" s="11">
+        <v>37.82</v>
+      </c>
+      <c r="H122" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I122" s="11">
+        <v>20</v>
+      </c>
+      <c r="J122" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K122" s="11">
+        <v>88</v>
+      </c>
+      <c r="L122" s="11">
+        <v>26</v>
+      </c>
+      <c r="M122" s="11">
+        <v>75.364000000000004</v>
+      </c>
+      <c r="N122" s="11">
+        <v>15</v>
+      </c>
+      <c r="O122" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P122" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q122" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R122" s="11">
+        <v>12</v>
+      </c>
+      <c r="S122" s="11">
+        <v>34</v>
+      </c>
+      <c r="T122" s="11">
+        <v>8</v>
+      </c>
+      <c r="U122" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V122" s="11">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="W122" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="X122" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y122" s="11">
+        <v>7.3250000000000002</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A123" s="12">
+        <v>46107</v>
+      </c>
+      <c r="B123" s="12">
+        <v>46107</v>
+      </c>
+      <c r="C123" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D123" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E88C1A74-E997-4267-B11B-A25D2F625D43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6772C0D0-ECE9-4B39-BF50-EDD78A05C52E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -799,6 +799,15 @@
                 <c:pt idx="120">
                   <c:v>46107</c:v>
                 </c:pt>
+                <c:pt idx="121">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>46108</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1166,6 +1175,15 @@
                   <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="119">
+                  <c:v>37.82</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>37.82</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>37.491999999999997</c:v>
+                </c:pt>
+                <c:pt idx="122">
                   <c:v>37.82</c:v>
                 </c:pt>
               </c:numCache>
@@ -1576,6 +1594,15 @@
                 <c:pt idx="120">
                   <c:v>46107</c:v>
                 </c:pt>
+                <c:pt idx="121">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>46108</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1943,6 +1970,15 @@
                   <c:v>21.45</c:v>
                 </c:pt>
                 <c:pt idx="119">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="122">
                   <c:v>21.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -2353,6 +2389,15 @@
                 <c:pt idx="120">
                   <c:v>46107</c:v>
                 </c:pt>
+                <c:pt idx="121">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>46108</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2720,6 +2765,15 @@
                   <c:v>75.5</c:v>
                 </c:pt>
                 <c:pt idx="119">
+                  <c:v>75.364000000000004</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>75.364000000000004</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>74.682000000000002</c:v>
+                </c:pt>
+                <c:pt idx="122">
                   <c:v>75.364000000000004</c:v>
                 </c:pt>
               </c:numCache>
@@ -3130,6 +3184,15 @@
                 <c:pt idx="120">
                   <c:v>46107</c:v>
                 </c:pt>
+                <c:pt idx="121">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>46108</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3497,6 +3560,15 @@
                   <c:v>13.625</c:v>
                 </c:pt>
                 <c:pt idx="119">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="122">
                   <c:v>13.625</c:v>
                 </c:pt>
               </c:numCache>
@@ -3907,6 +3979,15 @@
                 <c:pt idx="120">
                   <c:v>46107</c:v>
                 </c:pt>
+                <c:pt idx="121">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>46108</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4274,6 +4355,15 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="119">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="122">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -4700,6 +4790,15 @@
                 <c:pt idx="120">
                   <c:v>46107</c:v>
                 </c:pt>
+                <c:pt idx="121">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>46108</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5067,6 +5166,15 @@
                   <c:v>6.8520000000000003</c:v>
                 </c:pt>
                 <c:pt idx="119">
+                  <c:v>6.8520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>6.8520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>6.8520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="122">
                   <c:v>6.8520000000000003</c:v>
                 </c:pt>
               </c:numCache>
@@ -5479,6 +5587,15 @@
                 <c:pt idx="120">
                   <c:v>46107</c:v>
                 </c:pt>
+                <c:pt idx="121">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>46108</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>46108</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5846,6 +5963,15 @@
                   <c:v>7.3250000000000002</c:v>
                 </c:pt>
                 <c:pt idx="119">
+                  <c:v>7.3250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>7.3250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>7.375</c:v>
+                </c:pt>
+                <c:pt idx="122">
                   <c:v>7.3250000000000002</c:v>
                 </c:pt>
               </c:numCache>
@@ -9099,7 +9225,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y123"/>
+  <dimension ref="A1:Y126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
@@ -18507,6 +18633,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D123" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E123" s="11">
+        <v>50</v>
+      </c>
+      <c r="F123" s="11">
+        <v>25</v>
+      </c>
+      <c r="G123" s="11">
+        <v>37.82</v>
+      </c>
+      <c r="H123" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I123" s="11">
+        <v>20</v>
+      </c>
+      <c r="J123" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K123" s="11">
+        <v>88</v>
+      </c>
+      <c r="L123" s="11">
+        <v>26</v>
+      </c>
+      <c r="M123" s="11">
+        <v>75.364000000000004</v>
+      </c>
+      <c r="N123" s="11">
+        <v>15</v>
+      </c>
+      <c r="O123" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P123" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q123" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R123" s="11">
+        <v>12</v>
+      </c>
+      <c r="S123" s="11">
+        <v>34</v>
+      </c>
+      <c r="T123" s="11">
+        <v>8</v>
+      </c>
+      <c r="U123" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V123" s="11">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="W123" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="X123" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y123" s="11">
+        <v>7.3250000000000002</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A124" s="12">
+        <v>46108</v>
+      </c>
+      <c r="B124" s="12">
+        <v>46108</v>
+      </c>
+      <c r="C124" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E124" s="11">
+        <v>48</v>
+      </c>
+      <c r="F124" s="11">
+        <v>26</v>
+      </c>
+      <c r="G124" s="11">
+        <v>37.491999999999997</v>
+      </c>
+      <c r="H124" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I124" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J124" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K124" s="11">
+        <v>90</v>
+      </c>
+      <c r="L124" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="M124" s="11">
+        <v>74.682000000000002</v>
+      </c>
+      <c r="N124" s="11">
+        <v>15</v>
+      </c>
+      <c r="O124" s="11">
+        <v>12.85</v>
+      </c>
+      <c r="P124" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q124" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R124" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="S124" s="11">
+        <v>34</v>
+      </c>
+      <c r="T124" s="11">
+        <v>8</v>
+      </c>
+      <c r="U124" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V124" s="11">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="W124" s="11">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="X124" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y124" s="11">
+        <v>7.375</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A125" s="12">
+        <v>46108</v>
+      </c>
+      <c r="B125" s="12">
+        <v>46108</v>
+      </c>
+      <c r="C125" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E125" s="11">
+        <v>50</v>
+      </c>
+      <c r="F125" s="11">
+        <v>25</v>
+      </c>
+      <c r="G125" s="11">
+        <v>37.82</v>
+      </c>
+      <c r="H125" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I125" s="11">
+        <v>20</v>
+      </c>
+      <c r="J125" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K125" s="11">
+        <v>88</v>
+      </c>
+      <c r="L125" s="11">
+        <v>26</v>
+      </c>
+      <c r="M125" s="11">
+        <v>75.364000000000004</v>
+      </c>
+      <c r="N125" s="11">
+        <v>15</v>
+      </c>
+      <c r="O125" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P125" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q125" s="11">
+        <v>47.5</v>
+      </c>
+      <c r="R125" s="11">
+        <v>12</v>
+      </c>
+      <c r="S125" s="11">
+        <v>34</v>
+      </c>
+      <c r="T125" s="11">
+        <v>8</v>
+      </c>
+      <c r="U125" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V125" s="11">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="W125" s="11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="X125" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y125" s="11">
+        <v>7.3250000000000002</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A126" s="12">
+        <v>46108</v>
+      </c>
+      <c r="B126" s="12">
+        <v>46108</v>
+      </c>
+      <c r="C126" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D126" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6772C0D0-ECE9-4B39-BF50-EDD78A05C52E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFB5A60-FC5D-4AD0-AC5A-12BFEF983F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13575" yWindow="780" windowWidth="22425" windowHeight="20685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -244,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,36 +337,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +384,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -808,6 +808,15 @@
                 <c:pt idx="123">
                   <c:v>46108</c:v>
                 </c:pt>
+                <c:pt idx="124">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1185,6 +1194,18 @@
                 </c:pt>
                 <c:pt idx="122">
                   <c:v>37.82</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>37.457999999999998</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>37.457999999999998</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>37.457999999999998</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>37.457999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1603,6 +1624,15 @@
                 <c:pt idx="123">
                   <c:v>46108</c:v>
                 </c:pt>
+                <c:pt idx="124">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1979,6 +2009,18 @@
                   <c:v>21.45</c:v>
                 </c:pt>
                 <c:pt idx="122">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="126">
                   <c:v>21.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -2398,6 +2440,15 @@
                 <c:pt idx="123">
                   <c:v>46108</c:v>
                 </c:pt>
+                <c:pt idx="124">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2775,6 +2826,18 @@
                 </c:pt>
                 <c:pt idx="122">
                   <c:v>75.364000000000004</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>74.682000000000002</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>74.454999999999998</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>74.340999999999994</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>74.340999999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3193,6 +3256,15 @@
                 <c:pt idx="123">
                   <c:v>46108</c:v>
                 </c:pt>
+                <c:pt idx="124">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3569,6 +3641,18 @@
                   <c:v>13.625</c:v>
                 </c:pt>
                 <c:pt idx="122">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="126">
                   <c:v>13.625</c:v>
                 </c:pt>
               </c:numCache>
@@ -3988,6 +4072,15 @@
                 <c:pt idx="123">
                   <c:v>46108</c:v>
                 </c:pt>
+                <c:pt idx="124">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4364,6 +4457,18 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="122">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="126">
                   <c:v>34</c:v>
                 </c:pt>
               </c:numCache>
@@ -4799,6 +4904,15 @@
                 <c:pt idx="123">
                   <c:v>46108</c:v>
                 </c:pt>
+                <c:pt idx="124">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5175,6 +5289,18 @@
                   <c:v>6.8520000000000003</c:v>
                 </c:pt>
                 <c:pt idx="122">
+                  <c:v>6.8520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>6.8520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>6.8520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>6.8520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="126">
                   <c:v>6.8520000000000003</c:v>
                 </c:pt>
               </c:numCache>
@@ -5596,6 +5722,15 @@
                 <c:pt idx="123">
                   <c:v>46108</c:v>
                 </c:pt>
+                <c:pt idx="124">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>46111</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5973,6 +6108,18 @@
                 </c:pt>
                 <c:pt idx="122">
                   <c:v>7.3250000000000002</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>7.375</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>7.4249999999999998</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>7.4249999999999998</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>7.4249999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6207,6 +6354,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6214,7 +6362,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6250,7 +6397,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6717,6 +6864,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6724,7 +6872,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6760,7 +6907,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6827,7 +6974,7 @@
                 <c:pt idx="4">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="m/d/yyyy">
+                <c:pt idx="5">
                   <c:v>46090</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -6923,7 +7070,7 @@
                 <c:pt idx="4">
                   <c:v>46083</c:v>
                 </c:pt>
-                <c:pt idx="5" formatCode="m/d/yyyy">
+                <c:pt idx="5">
                   <c:v>46090</c:v>
                 </c:pt>
                 <c:pt idx="6">
@@ -7132,6 +7279,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7139,7 +7287,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9225,28 +9372,28 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y126"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y129"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:25" s="5" customFormat="1">
+      <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="9" t="s">
@@ -9313,11 +9460,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
+    <row r="2" spans="1:25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -9382,7 +9529,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -9459,7 +9606,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -9536,7 +9683,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -9613,7 +9760,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -9690,7 +9837,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -9767,7 +9914,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -9844,7 +9991,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -9921,7 +10068,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -9998,7 +10145,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -10075,7 +10222,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -10152,7 +10299,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -10229,7 +10376,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -10306,7 +10453,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -10383,7 +10530,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -10460,7 +10607,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -10537,7 +10684,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -10614,7 +10761,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -10691,7 +10838,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -10768,7 +10915,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -10845,7 +10992,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -10922,7 +11069,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -10999,7 +11146,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -11076,7 +11223,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -11153,7 +11300,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -11230,7 +11377,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -11307,7 +11454,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -11384,7 +11531,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -11461,7 +11608,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -11538,7 +11685,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -11615,7 +11762,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -11692,7 +11839,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -11769,7 +11916,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -11846,7 +11993,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -11923,7 +12070,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -12000,7 +12147,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -12077,7 +12224,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -12154,7 +12301,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -12231,7 +12378,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -12308,7 +12455,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -12385,7 +12532,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -12462,7 +12609,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -12539,7 +12686,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -12616,7 +12763,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -12693,7 +12840,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -12770,7 +12917,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -12847,7 +12994,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -12924,7 +13071,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -13001,7 +13148,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -13078,7 +13225,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -13155,7 +13302,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -13232,7 +13379,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -13309,7 +13456,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -13386,7 +13533,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -13463,7 +13610,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -13540,7 +13687,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -13617,7 +13764,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -13694,7 +13841,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -13771,7 +13918,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -13848,7 +13995,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -13925,7 +14072,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -14002,7 +14149,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -14079,7 +14226,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -14156,7 +14303,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -14233,7 +14380,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -14310,7 +14457,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -14387,7 +14534,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -14464,7 +14611,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -14541,7 +14688,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -14618,7 +14765,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -14695,7 +14842,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -14772,7 +14919,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -14849,7 +14996,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -14926,7 +15073,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -15003,7 +15150,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -15080,7 +15227,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -15157,7 +15304,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -15234,7 +15381,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -15311,7 +15458,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -15388,7 +15535,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -15465,7 +15612,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -15542,7 +15689,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -15619,7 +15766,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -15696,7 +15843,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -15773,7 +15920,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -15850,7 +15997,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -15927,7 +16074,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -16004,7 +16151,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -16081,7 +16228,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -16158,7 +16305,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -16235,7 +16382,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -16312,7 +16459,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -16389,7 +16536,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -16466,7 +16613,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -16543,7 +16690,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -16620,7 +16767,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -16697,7 +16844,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -16774,7 +16921,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -16851,7 +16998,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -16928,7 +17075,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -17005,7 +17152,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -17082,7 +17229,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -17159,7 +17306,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -17236,7 +17383,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -17313,7 +17460,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -17390,7 +17537,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -17467,7 +17614,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -17544,7 +17691,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -17621,7 +17768,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -17698,7 +17845,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -17775,7 +17922,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -17852,7 +17999,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -17929,7 +18076,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -18006,7 +18153,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -18083,7 +18230,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -18160,7 +18307,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -18237,7 +18384,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -18314,7 +18461,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -18391,7 +18538,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -18468,7 +18615,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -18545,7 +18692,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -18622,7 +18769,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -18699,7 +18846,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -18776,7 +18923,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -18853,7 +19000,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -18865,6 +19012,300 @@
       </c>
       <c r="D126" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E126" s="11">
+        <v>48</v>
+      </c>
+      <c r="F126" s="11">
+        <v>26</v>
+      </c>
+      <c r="G126" s="11">
+        <v>37.457999999999998</v>
+      </c>
+      <c r="H126" s="11">
+        <v>23.6</v>
+      </c>
+      <c r="I126" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J126" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K126" s="11">
+        <v>90</v>
+      </c>
+      <c r="L126" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="M126" s="11">
+        <v>74.682000000000002</v>
+      </c>
+      <c r="N126" s="11">
+        <v>15</v>
+      </c>
+      <c r="O126" s="11">
+        <v>12.85</v>
+      </c>
+      <c r="P126" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q126" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R126" s="11">
+        <v>12.2</v>
+      </c>
+      <c r="S126" s="11">
+        <v>34</v>
+      </c>
+      <c r="T126" s="11">
+        <v>8</v>
+      </c>
+      <c r="U126" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="V126" s="11">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="W126" s="11">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="X126" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y126" s="11">
+        <v>7.375</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25">
+      <c r="A127" s="12">
+        <v>46111</v>
+      </c>
+      <c r="B127" s="12">
+        <v>46111</v>
+      </c>
+      <c r="C127" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E127" s="11">
+        <v>48</v>
+      </c>
+      <c r="F127" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G127" s="11">
+        <v>37.457999999999998</v>
+      </c>
+      <c r="H127" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I127" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J127" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K127" s="11">
+        <v>90</v>
+      </c>
+      <c r="L127" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M127" s="11">
+        <v>74.454999999999998</v>
+      </c>
+      <c r="N127" s="11">
+        <v>15</v>
+      </c>
+      <c r="O127" s="11">
+        <v>13</v>
+      </c>
+      <c r="P127" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q127" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R127" s="11">
+        <v>12</v>
+      </c>
+      <c r="S127" s="11">
+        <v>34</v>
+      </c>
+      <c r="T127" s="11">
+        <v>8</v>
+      </c>
+      <c r="U127" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V127" s="11">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="W127" s="11">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="X127" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y127" s="11">
+        <v>7.4249999999999998</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25">
+      <c r="A128" s="12">
+        <v>46111</v>
+      </c>
+      <c r="B128" s="12">
+        <v>46111</v>
+      </c>
+      <c r="C128" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E128" s="11">
+        <v>48</v>
+      </c>
+      <c r="F128" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G128" s="11">
+        <v>37.457999999999998</v>
+      </c>
+      <c r="H128" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I128" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J128" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K128" s="11">
+        <v>90</v>
+      </c>
+      <c r="L128" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M128" s="11">
+        <v>74.340999999999994</v>
+      </c>
+      <c r="N128" s="11">
+        <v>15</v>
+      </c>
+      <c r="O128" s="11">
+        <v>13</v>
+      </c>
+      <c r="P128" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q128" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R128" s="11">
+        <v>12</v>
+      </c>
+      <c r="S128" s="11">
+        <v>34</v>
+      </c>
+      <c r="T128" s="11">
+        <v>8</v>
+      </c>
+      <c r="U128" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V128" s="11">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="W128" s="11">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="X128" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y128" s="11">
+        <v>7.4249999999999998</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25">
+      <c r="A129" s="12">
+        <v>46111</v>
+      </c>
+      <c r="B129" s="12">
+        <v>46111</v>
+      </c>
+      <c r="C129" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E129" s="11">
+        <v>48</v>
+      </c>
+      <c r="F129" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G129" s="11">
+        <v>37.457999999999998</v>
+      </c>
+      <c r="H129" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I129" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J129" s="11">
+        <v>21.45</v>
+      </c>
+      <c r="K129" s="11">
+        <v>90</v>
+      </c>
+      <c r="L129" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M129" s="11">
+        <v>74.340999999999994</v>
+      </c>
+      <c r="N129" s="11">
+        <v>15</v>
+      </c>
+      <c r="O129" s="11">
+        <v>13</v>
+      </c>
+      <c r="P129" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q129" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R129" s="11">
+        <v>12</v>
+      </c>
+      <c r="S129" s="11">
+        <v>34</v>
+      </c>
+      <c r="T129" s="11">
+        <v>8</v>
+      </c>
+      <c r="U129" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V129" s="11">
+        <v>6.8520000000000003</v>
+      </c>
+      <c r="W129" s="11">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="X129" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y129" s="11">
+        <v>7.4249999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -18883,27 +19324,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:37" s="5" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="10" t="s">
@@ -18982,11 +19423,11 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+    <row r="2" spans="1:37">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -19063,7 +19504,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -19152,7 +19593,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -19241,7 +19682,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -19259,34 +19700,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
-  <dimension ref="A1:Y10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9" style="11"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9" style="11"/>
+    <col min="10" max="10" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="25" width="9" style="11"/>
+    <col min="13" max="13" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:25" s="5" customFormat="1">
+      <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -19329,11 +19771,11 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
+    <row r="2" spans="1:25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="13" t="s">
         <v>54</v>
       </c>
@@ -19374,7 +19816,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -19427,7 +19869,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -19480,7 +19922,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -19521,7 +19963,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -19562,7 +20004,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -19603,7 +20045,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -19644,7 +20086,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -19685,7 +20127,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -19724,6 +20166,47 @@
       </c>
       <c r="M10" s="11">
         <v>132.333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B11" s="12">
+        <v>46111</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="14">
+        <v>250</v>
+      </c>
+      <c r="F11" s="14">
+        <v>200</v>
+      </c>
+      <c r="G11" s="11">
+        <v>232.5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>1060</v>
+      </c>
+      <c r="I11" s="14">
+        <v>870</v>
+      </c>
+      <c r="J11" s="11">
+        <v>925</v>
+      </c>
+      <c r="K11" s="14">
+        <v>171</v>
+      </c>
+      <c r="L11" s="14">
+        <v>130</v>
+      </c>
+      <c r="M11" s="11">
+        <v>143.333</v>
       </c>
     </row>
   </sheetData>
@@ -19741,29 +20224,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
-  <dimension ref="A1:Y10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:25" s="5" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -19800,11 +20283,11 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+    <row r="2" spans="1:25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -19839,7 +20322,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -19886,7 +20369,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -19933,7 +20416,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -19965,7 +20448,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -19997,7 +20480,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -20029,11 +20512,11 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+    <row r="8" spans="1:25">
+      <c r="A8" s="12">
         <v>46083</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="12">
         <v>46090</v>
       </c>
       <c r="C8" s="8">
@@ -20061,7 +20544,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -20093,7 +20576,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -20123,6 +20606,38 @@
       </c>
       <c r="J10" s="11">
         <v>11.962</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="12">
+        <v>46104</v>
+      </c>
+      <c r="B11" s="12">
+        <v>46111</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="11">
+        <v>20</v>
+      </c>
+      <c r="F11" s="11">
+        <v>11</v>
+      </c>
+      <c r="G11" s="11">
+        <v>12.727</v>
+      </c>
+      <c r="H11" s="11">
+        <v>20</v>
+      </c>
+      <c r="I11" s="11">
+        <v>11</v>
+      </c>
+      <c r="J11" s="11">
+        <v>12.865</v>
       </c>
     </row>
   </sheetData>
@@ -20140,7 +20655,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -20154,15 +20669,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -20173,7 +20688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -20187,7 +20702,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -20196,7 +20711,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -20205,7 +20720,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -20214,7 +20729,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -20223,7 +20738,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -20232,7 +20747,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -20241,7 +20756,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -20250,49 +20765,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -20303,7 +20818,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -20312,7 +20827,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -20321,7 +20836,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -20332,7 +20847,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -20341,7 +20856,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -20350,42 +20865,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -20394,35 +20909,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFB5A60-FC5D-4AD0-AC5A-12BFEF983F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4C9056-DD59-4BE9-AF4A-31B8092C8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -354,13 +354,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -817,6 +817,15 @@
                 <c:pt idx="126">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="127">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>46112</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1206,6 +1215,15 @@
                 </c:pt>
                 <c:pt idx="126">
                   <c:v>37.457999999999998</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>37.392000000000003</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>37.392000000000003</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>37.426000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1633,6 +1651,15 @@
                 <c:pt idx="126">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="127">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>46112</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2022,6 +2049,15 @@
                 </c:pt>
                 <c:pt idx="126">
                   <c:v>21.45</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>21.4</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>21.4</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>21.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2449,6 +2485,15 @@
                 <c:pt idx="126">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="127">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>46112</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2838,6 +2883,15 @@
                 </c:pt>
                 <c:pt idx="126">
                   <c:v>74.340999999999994</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>74.227000000000004</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>74.227000000000004</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>74.227000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3265,6 +3319,15 @@
                 <c:pt idx="126">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="127">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>46112</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3653,6 +3716,15 @@
                   <c:v>13.625</c:v>
                 </c:pt>
                 <c:pt idx="126">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="129">
                   <c:v>13.625</c:v>
                 </c:pt>
               </c:numCache>
@@ -4081,6 +4153,15 @@
                 <c:pt idx="126">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="127">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>46112</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4470,6 +4551,15 @@
                 </c:pt>
                 <c:pt idx="126">
                   <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>33.96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4913,6 +5003,15 @@
                 <c:pt idx="126">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="127">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>46112</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5302,6 +5401,15 @@
                 </c:pt>
                 <c:pt idx="126">
                   <c:v>6.8520000000000003</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>6.8419999999999996</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>6.8339999999999996</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>6.8339999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5731,6 +5839,15 @@
                 <c:pt idx="126">
                   <c:v>46111</c:v>
                 </c:pt>
+                <c:pt idx="127">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>46112</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6120,6 +6237,15 @@
                 </c:pt>
                 <c:pt idx="126">
                   <c:v>7.4249999999999998</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>7.5250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>7.5250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>7.55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9372,7 +9498,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y129"/>
+  <dimension ref="A1:Y132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
@@ -9384,16 +9510,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="9" t="s">
@@ -9461,10 +9587,10 @@
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -19306,6 +19432,237 @@
       </c>
       <c r="Y129" s="11">
         <v>7.4249999999999998</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25">
+      <c r="A130" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B130" s="12">
+        <v>46112</v>
+      </c>
+      <c r="C130" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E130" s="11">
+        <v>48</v>
+      </c>
+      <c r="F130" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G130" s="11">
+        <v>37.392000000000003</v>
+      </c>
+      <c r="H130" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I130" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J130" s="11">
+        <v>21.4</v>
+      </c>
+      <c r="K130" s="11">
+        <v>90</v>
+      </c>
+      <c r="L130" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M130" s="11">
+        <v>74.227000000000004</v>
+      </c>
+      <c r="N130" s="11">
+        <v>15</v>
+      </c>
+      <c r="O130" s="11">
+        <v>13</v>
+      </c>
+      <c r="P130" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q130" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R130" s="11">
+        <v>12</v>
+      </c>
+      <c r="S130" s="11">
+        <v>34</v>
+      </c>
+      <c r="T130" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U130" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V130" s="11">
+        <v>6.8419999999999996</v>
+      </c>
+      <c r="W130" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="X130" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="Y130" s="11">
+        <v>7.5250000000000004</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25">
+      <c r="A131" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B131" s="12">
+        <v>46112</v>
+      </c>
+      <c r="C131" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E131" s="11">
+        <v>48</v>
+      </c>
+      <c r="F131" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G131" s="11">
+        <v>37.392000000000003</v>
+      </c>
+      <c r="H131" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I131" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J131" s="11">
+        <v>21.4</v>
+      </c>
+      <c r="K131" s="11">
+        <v>90</v>
+      </c>
+      <c r="L131" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M131" s="11">
+        <v>74.227000000000004</v>
+      </c>
+      <c r="N131" s="11">
+        <v>15</v>
+      </c>
+      <c r="O131" s="11">
+        <v>13</v>
+      </c>
+      <c r="P131" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q131" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R131" s="11">
+        <v>12</v>
+      </c>
+      <c r="S131" s="11">
+        <v>34</v>
+      </c>
+      <c r="T131" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U131" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V131" s="11">
+        <v>6.8339999999999996</v>
+      </c>
+      <c r="W131" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="X131" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="Y131" s="11">
+        <v>7.5250000000000004</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25">
+      <c r="A132" s="12">
+        <v>46112</v>
+      </c>
+      <c r="B132" s="12">
+        <v>46112</v>
+      </c>
+      <c r="C132" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E132" s="11">
+        <v>48</v>
+      </c>
+      <c r="F132" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G132" s="11">
+        <v>37.426000000000002</v>
+      </c>
+      <c r="H132" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I132" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J132" s="11">
+        <v>21.4</v>
+      </c>
+      <c r="K132" s="11">
+        <v>90</v>
+      </c>
+      <c r="L132" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M132" s="11">
+        <v>74.227000000000004</v>
+      </c>
+      <c r="N132" s="11">
+        <v>15</v>
+      </c>
+      <c r="O132" s="11">
+        <v>13</v>
+      </c>
+      <c r="P132" s="11">
+        <v>13.625</v>
+      </c>
+      <c r="Q132" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R132" s="11">
+        <v>12</v>
+      </c>
+      <c r="S132" s="11">
+        <v>33.96</v>
+      </c>
+      <c r="T132" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U132" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V132" s="11">
+        <v>6.8339999999999996</v>
+      </c>
+      <c r="W132" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="X132" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="Y132" s="11">
+        <v>7.55</v>
       </c>
     </row>
   </sheetData>
@@ -19335,16 +19692,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="5" customFormat="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="10" t="s">
@@ -19424,10 +19781,10 @@
       <c r="AK1" s="1"/>
     </row>
     <row r="2" spans="1:37">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -19719,16 +20076,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -19772,10 +20129,10 @@
       <c r="Y1" s="9"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="13" t="s">
         <v>54</v>
       </c>
@@ -20237,16 +20594,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -20284,10 +20641,10 @@
       <c r="Y1" s="9"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="15"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4C9056-DD59-4BE9-AF4A-31B8092C8332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F64F38D-1E36-46ED-8E9A-F25F5546BE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32205" yWindow="-3525" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -25,12 +25,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -244,23 +247,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +276,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +319,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,27 +340,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -365,8 +368,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +387,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -826,6 +829,15 @@
                 <c:pt idx="129">
                   <c:v>46112</c:v>
                 </c:pt>
+                <c:pt idx="130">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1224,6 +1236,12 @@
                 </c:pt>
                 <c:pt idx="129">
                   <c:v>37.426000000000002</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>37.164000000000001</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>37.067</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1660,6 +1678,15 @@
                 <c:pt idx="129">
                   <c:v>46112</c:v>
                 </c:pt>
+                <c:pt idx="130">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2057,6 +2084,12 @@
                   <c:v>21.4</c:v>
                 </c:pt>
                 <c:pt idx="129">
+                  <c:v>21.4</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>21.4</c:v>
+                </c:pt>
+                <c:pt idx="131">
                   <c:v>21.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -2494,6 +2527,15 @@
                 <c:pt idx="129">
                   <c:v>46112</c:v>
                 </c:pt>
+                <c:pt idx="130">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2892,6 +2934,12 @@
                 </c:pt>
                 <c:pt idx="129">
                   <c:v>74.227000000000004</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>74.114000000000004</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>74</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3328,6 +3376,15 @@
                 <c:pt idx="129">
                   <c:v>46112</c:v>
                 </c:pt>
+                <c:pt idx="130">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3726,6 +3783,12 @@
                 </c:pt>
                 <c:pt idx="129">
                   <c:v>13.625</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>13.574999999999999</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>13.574999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4162,6 +4225,15 @@
                 <c:pt idx="129">
                   <c:v>46112</c:v>
                 </c:pt>
+                <c:pt idx="130">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4559,6 +4631,12 @@
                   <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="129">
+                  <c:v>33.96</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>33.96</c:v>
+                </c:pt>
+                <c:pt idx="131">
                   <c:v>33.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -5012,6 +5090,15 @@
                 <c:pt idx="129">
                   <c:v>46112</c:v>
                 </c:pt>
+                <c:pt idx="130">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5410,6 +5497,12 @@
                 </c:pt>
                 <c:pt idx="129">
                   <c:v>6.8339999999999996</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>6.7969999999999997</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>6.7969999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5848,6 +5941,15 @@
                 <c:pt idx="129">
                   <c:v>46112</c:v>
                 </c:pt>
+                <c:pt idx="130">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>46113</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6246,6 +6348,12 @@
                 </c:pt>
                 <c:pt idx="129">
                   <c:v>7.55</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>7.625</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>7.625</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6480,7 +6588,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6488,6 +6595,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6523,7 +6631,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6990,7 +7098,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6998,6 +7105,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7033,7 +7141,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7405,7 +7513,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7413,6 +7520,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9498,18 +9606,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y132"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y135"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -9586,7 +9694,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -9655,7 +9763,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -9732,7 +9840,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -9809,7 +9917,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -9886,7 +9994,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -9963,7 +10071,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -10040,7 +10148,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -10117,7 +10225,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -10194,7 +10302,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -10271,7 +10379,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -10348,7 +10456,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -10425,7 +10533,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -10502,7 +10610,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -10579,7 +10687,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -10656,7 +10764,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -10733,7 +10841,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -10810,7 +10918,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -10887,7 +10995,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -10964,7 +11072,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -11041,7 +11149,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -11118,7 +11226,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -11195,7 +11303,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -11272,7 +11380,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -11349,7 +11457,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -11426,7 +11534,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -11503,7 +11611,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -11580,7 +11688,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -11657,7 +11765,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -11734,7 +11842,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -11811,7 +11919,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -11888,7 +11996,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -11965,7 +12073,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -12042,7 +12150,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -12119,7 +12227,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -12196,7 +12304,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -12273,7 +12381,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -12350,7 +12458,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -12427,7 +12535,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -12504,7 +12612,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -12581,7 +12689,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -12658,7 +12766,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -12735,7 +12843,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -12812,7 +12920,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -12889,7 +12997,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -12966,7 +13074,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -13043,7 +13151,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -13120,7 +13228,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -13197,7 +13305,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -13274,7 +13382,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -13351,7 +13459,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -13428,7 +13536,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -13505,7 +13613,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -13582,7 +13690,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -13659,7 +13767,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -13736,7 +13844,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -13813,7 +13921,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -13890,7 +13998,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -13967,7 +14075,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -14044,7 +14152,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -14121,7 +14229,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -14198,7 +14306,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -14275,7 +14383,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -14352,7 +14460,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -14429,7 +14537,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -14506,7 +14614,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -14583,7 +14691,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -14660,7 +14768,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -14737,7 +14845,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -14814,7 +14922,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -14891,7 +14999,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -14968,7 +15076,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -15045,7 +15153,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -15122,7 +15230,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -15199,7 +15307,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -15276,7 +15384,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -15353,7 +15461,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -15430,7 +15538,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -15507,7 +15615,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -15584,7 +15692,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -15661,7 +15769,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -15738,7 +15846,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -15815,7 +15923,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -15892,7 +16000,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -15969,7 +16077,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -16046,7 +16154,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -16123,7 +16231,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -16200,7 +16308,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -16277,7 +16385,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -16354,7 +16462,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -16431,7 +16539,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -16508,7 +16616,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -16585,7 +16693,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -16662,7 +16770,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -16739,7 +16847,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -16816,7 +16924,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -16893,7 +17001,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -16970,7 +17078,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -17047,7 +17155,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -17124,7 +17232,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -17201,7 +17309,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -17278,7 +17386,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -17355,7 +17463,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -17432,7 +17540,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -17509,7 +17617,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -17586,7 +17694,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -17663,7 +17771,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -17740,7 +17848,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -17817,7 +17925,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -17894,7 +18002,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -17971,7 +18079,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -18048,7 +18156,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -18125,7 +18233,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -18202,7 +18310,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -18279,7 +18387,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -18356,7 +18464,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -18433,7 +18541,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -18510,7 +18618,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -18587,7 +18695,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -18664,7 +18772,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -18741,7 +18849,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -18818,7 +18926,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -18895,7 +19003,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -18972,7 +19080,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -19049,7 +19157,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -19126,7 +19234,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -19203,7 +19311,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -19280,7 +19388,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -19357,7 +19465,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -19434,7 +19542,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -19511,7 +19619,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -19588,7 +19696,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -19663,6 +19771,174 @@
       </c>
       <c r="Y132" s="11">
         <v>7.55</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A133" s="12">
+        <v>46113</v>
+      </c>
+      <c r="B133" s="12">
+        <v>46113</v>
+      </c>
+      <c r="C133" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E133" s="11">
+        <v>48</v>
+      </c>
+      <c r="F133" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G133" s="11">
+        <v>37.164000000000001</v>
+      </c>
+      <c r="H133" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I133" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J133" s="11">
+        <v>21.4</v>
+      </c>
+      <c r="K133" s="11">
+        <v>90</v>
+      </c>
+      <c r="L133" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M133" s="11">
+        <v>74.114000000000004</v>
+      </c>
+      <c r="N133" s="11">
+        <v>15</v>
+      </c>
+      <c r="O133" s="11">
+        <v>13</v>
+      </c>
+      <c r="P133" s="11">
+        <v>13.574999999999999</v>
+      </c>
+      <c r="Q133" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R133" s="11">
+        <v>12</v>
+      </c>
+      <c r="S133" s="11">
+        <v>33.96</v>
+      </c>
+      <c r="T133" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U133" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="V133" s="11">
+        <v>6.7969999999999997</v>
+      </c>
+      <c r="W133" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="X133" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="Y133" s="11">
+        <v>7.625</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A134" s="12">
+        <v>46113</v>
+      </c>
+      <c r="B134" s="12">
+        <v>46113</v>
+      </c>
+      <c r="C134" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E134" s="11">
+        <v>48</v>
+      </c>
+      <c r="F134" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G134" s="11">
+        <v>37.067</v>
+      </c>
+      <c r="H134" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I134" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J134" s="11">
+        <v>21.4</v>
+      </c>
+      <c r="K134" s="11">
+        <v>90</v>
+      </c>
+      <c r="L134" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M134" s="11">
+        <v>74</v>
+      </c>
+      <c r="N134" s="11">
+        <v>15</v>
+      </c>
+      <c r="O134" s="11">
+        <v>13</v>
+      </c>
+      <c r="P134" s="11">
+        <v>13.574999999999999</v>
+      </c>
+      <c r="Q134" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R134" s="11">
+        <v>12</v>
+      </c>
+      <c r="S134" s="11">
+        <v>33.96</v>
+      </c>
+      <c r="T134" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U134" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="V134" s="11">
+        <v>6.7969999999999997</v>
+      </c>
+      <c r="W134" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="X134" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="Y134" s="11">
+        <v>7.625</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A135" s="12">
+        <v>46113</v>
+      </c>
+      <c r="B135" s="12">
+        <v>46113</v>
+      </c>
+      <c r="C135" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -19681,17 +19957,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -19780,7 +20056,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -19861,7 +20137,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -19950,7 +20226,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -20039,7 +20315,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -20058,24 +20334,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -20128,7 +20404,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -20173,7 +20449,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -20226,7 +20502,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -20279,7 +20555,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -20320,7 +20596,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -20361,7 +20637,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -20402,7 +20678,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -20443,7 +20719,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -20484,7 +20760,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -20525,7 +20801,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -20582,18 +20858,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -20640,7 +20916,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -20679,7 +20955,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -20726,7 +21002,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -20773,7 +21049,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -20805,7 +21081,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -20837,7 +21113,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -20869,7 +21145,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -20901,7 +21177,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -20933,7 +21209,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -20965,7 +21241,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -21012,7 +21288,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -21026,15 +21302,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -21045,7 +21321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -21059,7 +21335,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -21068,7 +21344,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -21077,7 +21353,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -21086,7 +21362,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -21095,7 +21371,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -21104,7 +21380,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -21113,7 +21389,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -21122,49 +21398,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -21175,7 +21451,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -21184,7 +21460,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -21193,7 +21469,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -21204,7 +21480,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -21213,7 +21489,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -21222,42 +21498,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -21266,35 +21542,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F64F38D-1E36-46ED-8E9A-F25F5546BE08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400A75AB-7806-4B78-9D37-B0682E9893A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32205" yWindow="-3525" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2170" yWindow="2080" windowWidth="17280" windowHeight="10690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -25,15 +25,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -247,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -276,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -319,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -340,27 +337,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -368,8 +365,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -387,7 +384,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -838,6 +835,15 @@
                 <c:pt idx="132">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1241,6 +1247,9 @@
                   <c:v>37.164000000000001</c:v>
                 </c:pt>
                 <c:pt idx="131">
+                  <c:v>37.067</c:v>
+                </c:pt>
+                <c:pt idx="132">
                   <c:v>37.067</c:v>
                 </c:pt>
               </c:numCache>
@@ -1687,6 +1696,15 @@
                 <c:pt idx="132">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2090,6 +2108,9 @@
                   <c:v>21.4</c:v>
                 </c:pt>
                 <c:pt idx="131">
+                  <c:v>21.4</c:v>
+                </c:pt>
+                <c:pt idx="132">
                   <c:v>21.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -2536,6 +2557,15 @@
                 <c:pt idx="132">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2939,6 +2969,9 @@
                   <c:v>74.114000000000004</c:v>
                 </c:pt>
                 <c:pt idx="131">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="132">
                   <c:v>74</c:v>
                 </c:pt>
               </c:numCache>
@@ -3385,6 +3418,15 @@
                 <c:pt idx="132">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3788,6 +3830,9 @@
                   <c:v>13.574999999999999</c:v>
                 </c:pt>
                 <c:pt idx="131">
+                  <c:v>13.574999999999999</c:v>
+                </c:pt>
+                <c:pt idx="132">
                   <c:v>13.574999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -4234,6 +4279,15 @@
                 <c:pt idx="132">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4637,6 +4691,9 @@
                   <c:v>33.96</c:v>
                 </c:pt>
                 <c:pt idx="131">
+                  <c:v>33.96</c:v>
+                </c:pt>
+                <c:pt idx="132">
                   <c:v>33.96</c:v>
                 </c:pt>
               </c:numCache>
@@ -5099,6 +5156,15 @@
                 <c:pt idx="132">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5502,6 +5568,9 @@
                   <c:v>6.7969999999999997</c:v>
                 </c:pt>
                 <c:pt idx="131">
+                  <c:v>6.7969999999999997</c:v>
+                </c:pt>
+                <c:pt idx="132">
                   <c:v>6.7969999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -5950,6 +6019,15 @@
                 <c:pt idx="132">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>46114</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6353,6 +6431,9 @@
                   <c:v>7.625</c:v>
                 </c:pt>
                 <c:pt idx="131">
+                  <c:v>7.625</c:v>
+                </c:pt>
+                <c:pt idx="132">
                   <c:v>7.625</c:v>
                 </c:pt>
               </c:numCache>
@@ -6588,6 +6669,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6595,7 +6677,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6631,7 +6712,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7098,6 +7179,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7105,7 +7187,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7141,7 +7222,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7513,6 +7594,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7520,7 +7602,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9606,18 +9687,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y135"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y138"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -9694,7 +9775,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -9763,7 +9844,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -9840,7 +9921,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -9917,7 +9998,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -9994,7 +10075,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -10071,7 +10152,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -10148,7 +10229,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -10225,7 +10306,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -10302,7 +10383,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -10379,7 +10460,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -10456,7 +10537,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -10533,7 +10614,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -10610,7 +10691,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -10687,7 +10768,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -10764,7 +10845,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -10841,7 +10922,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -10918,7 +10999,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -10995,7 +11076,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -11072,7 +11153,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -11149,7 +11230,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -11226,7 +11307,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -11303,7 +11384,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -11380,7 +11461,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -11457,7 +11538,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -11534,7 +11615,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -11611,7 +11692,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -11688,7 +11769,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -11765,7 +11846,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -11842,7 +11923,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -11919,7 +12000,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -11996,7 +12077,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -12073,7 +12154,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -12150,7 +12231,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -12227,7 +12308,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -12304,7 +12385,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -12381,7 +12462,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -12458,7 +12539,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -12535,7 +12616,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -12612,7 +12693,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -12689,7 +12770,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -12766,7 +12847,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -12843,7 +12924,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -12920,7 +13001,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -12997,7 +13078,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -13074,7 +13155,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -13151,7 +13232,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -13228,7 +13309,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -13305,7 +13386,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -13382,7 +13463,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -13459,7 +13540,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -13536,7 +13617,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -13613,7 +13694,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -13690,7 +13771,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -13767,7 +13848,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -13844,7 +13925,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -13921,7 +14002,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -13998,7 +14079,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -14075,7 +14156,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -14152,7 +14233,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -14229,7 +14310,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -14306,7 +14387,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -14383,7 +14464,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -14460,7 +14541,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -14537,7 +14618,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -14614,7 +14695,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -14691,7 +14772,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -14768,7 +14849,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -14845,7 +14926,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -14922,7 +15003,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -14999,7 +15080,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -15076,7 +15157,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -15153,7 +15234,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -15230,7 +15311,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -15307,7 +15388,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -15384,7 +15465,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -15461,7 +15542,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -15538,7 +15619,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -15615,7 +15696,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -15692,7 +15773,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -15769,7 +15850,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -15846,7 +15927,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -15923,7 +16004,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -16000,7 +16081,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -16077,7 +16158,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -16154,7 +16235,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -16231,7 +16312,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -16308,7 +16389,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -16385,7 +16466,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -16462,7 +16543,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -16539,7 +16620,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -16616,7 +16697,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -16693,7 +16774,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -16770,7 +16851,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -16847,7 +16928,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -16924,7 +17005,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -17001,7 +17082,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -17078,7 +17159,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -17155,7 +17236,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -17232,7 +17313,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -17309,7 +17390,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -17386,7 +17467,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -17463,7 +17544,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -17540,7 +17621,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -17617,7 +17698,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -17694,7 +17775,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -17771,7 +17852,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -17848,7 +17929,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -17925,7 +18006,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -18002,7 +18083,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -18079,7 +18160,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -18156,7 +18237,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -18233,7 +18314,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -18310,7 +18391,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -18387,7 +18468,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -18464,7 +18545,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -18541,7 +18622,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -18618,7 +18699,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -18695,7 +18776,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -18772,7 +18853,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -18849,7 +18930,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -18926,7 +19007,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -19003,7 +19084,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -19080,7 +19161,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -19157,7 +19238,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -19234,7 +19315,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -19311,7 +19392,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -19388,7 +19469,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -19465,7 +19546,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -19542,7 +19623,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -19619,7 +19700,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -19696,7 +19777,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -19773,7 +19854,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -19850,7 +19931,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -19927,7 +20008,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -19938,6 +20019,111 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D135" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E135" s="11">
+        <v>48</v>
+      </c>
+      <c r="F135" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G135" s="11">
+        <v>37.067</v>
+      </c>
+      <c r="H135" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I135" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J135" s="11">
+        <v>21.4</v>
+      </c>
+      <c r="K135" s="11">
+        <v>90</v>
+      </c>
+      <c r="L135" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M135" s="11">
+        <v>74</v>
+      </c>
+      <c r="N135" s="11">
+        <v>15</v>
+      </c>
+      <c r="O135" s="11">
+        <v>13</v>
+      </c>
+      <c r="P135" s="11">
+        <v>13.574999999999999</v>
+      </c>
+      <c r="Q135" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R135" s="11">
+        <v>12</v>
+      </c>
+      <c r="S135" s="11">
+        <v>33.96</v>
+      </c>
+      <c r="T135" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U135" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="V135" s="11">
+        <v>6.7969999999999997</v>
+      </c>
+      <c r="W135" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="X135" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="Y135" s="11">
+        <v>7.625</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25">
+      <c r="A136" s="12">
+        <v>46114</v>
+      </c>
+      <c r="B136" s="12">
+        <v>46114</v>
+      </c>
+      <c r="C136" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25">
+      <c r="A137" s="12">
+        <v>46114</v>
+      </c>
+      <c r="B137" s="12">
+        <v>46114</v>
+      </c>
+      <c r="C137" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25">
+      <c r="A138" s="12">
+        <v>46114</v>
+      </c>
+      <c r="B138" s="12">
+        <v>46114</v>
+      </c>
+      <c r="C138" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D138" s="7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -19957,17 +20143,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -20056,7 +20242,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -20137,7 +20323,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -20226,7 +20412,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -20315,7 +20501,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -20334,24 +20520,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -20404,7 +20590,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -20449,7 +20635,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -20502,7 +20688,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -20555,7 +20741,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -20596,7 +20782,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -20637,7 +20823,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -20678,7 +20864,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -20719,7 +20905,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -20760,7 +20946,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -20801,7 +20987,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -20858,18 +21044,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -20916,7 +21102,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -20955,7 +21141,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -21002,7 +21188,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -21049,7 +21235,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -21081,7 +21267,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -21113,7 +21299,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -21145,7 +21331,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -21177,7 +21363,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -21209,7 +21395,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -21241,7 +21427,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -21288,7 +21474,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -21302,15 +21488,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -21321,7 +21507,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -21335,7 +21521,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -21344,7 +21530,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -21353,7 +21539,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -21362,7 +21548,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -21371,7 +21557,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -21380,7 +21566,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -21389,7 +21575,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -21398,49 +21584,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -21451,7 +21637,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -21460,7 +21646,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -21469,7 +21655,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -21480,7 +21666,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -21489,7 +21675,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -21498,42 +21684,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -21542,35 +21728,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400A75AB-7806-4B78-9D37-B0682E9893A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9D44CC-7703-4B4D-8D0E-7FEFF56BFB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2170" yWindow="2080" windowWidth="17280" windowHeight="10690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -244,23 +247,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +276,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +319,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,27 +340,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -365,8 +368,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +387,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1252,6 +1255,12 @@
                 <c:pt idx="132">
                   <c:v>37.067</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>36.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>36.832999999999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2113,6 +2122,12 @@
                 <c:pt idx="132">
                   <c:v>21.4</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>21.3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2974,6 +2989,12 @@
                 <c:pt idx="132">
                   <c:v>74</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>73.317999999999998</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>73.317999999999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3835,6 +3856,12 @@
                 <c:pt idx="132">
                   <c:v>13.574999999999999</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>13.55</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>13.55</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4695,6 +4722,12 @@
                 </c:pt>
                 <c:pt idx="132">
                   <c:v>33.96</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>33.659999999999997</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>33.659999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5573,6 +5606,12 @@
                 <c:pt idx="132">
                   <c:v>6.7969999999999997</c:v>
                 </c:pt>
+                <c:pt idx="133">
+                  <c:v>6.766</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>6.766</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6434,6 +6473,12 @@
                   <c:v>7.625</c:v>
                 </c:pt>
                 <c:pt idx="132">
+                  <c:v>7.625</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>7.625</c:v>
+                </c:pt>
+                <c:pt idx="134">
                   <c:v>7.625</c:v>
                 </c:pt>
               </c:numCache>
@@ -6669,7 +6714,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6677,6 +6721,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6712,7 +6757,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7179,7 +7224,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7187,6 +7231,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7222,7 +7267,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7594,7 +7639,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7602,6 +7646,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9688,17 +9733,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y138"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -9775,7 +9820,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -9844,7 +9889,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -9921,7 +9966,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -9998,7 +10043,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -10075,7 +10120,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -10152,7 +10197,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -10229,7 +10274,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -10306,7 +10351,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -10383,7 +10428,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -10460,7 +10505,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -10537,7 +10582,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -10614,7 +10659,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -10691,7 +10736,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -10768,7 +10813,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -10845,7 +10890,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -10922,7 +10967,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -10999,7 +11044,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -11076,7 +11121,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -11153,7 +11198,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -11230,7 +11275,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -11307,7 +11352,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -11384,7 +11429,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -11461,7 +11506,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -11538,7 +11583,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -11615,7 +11660,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -11692,7 +11737,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -11769,7 +11814,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -11846,7 +11891,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -11923,7 +11968,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -12000,7 +12045,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -12077,7 +12122,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -12154,7 +12199,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -12231,7 +12276,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -12308,7 +12353,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -12385,7 +12430,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -12462,7 +12507,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -12539,7 +12584,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -12616,7 +12661,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -12693,7 +12738,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -12770,7 +12815,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -12847,7 +12892,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -12924,7 +12969,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -13001,7 +13046,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -13078,7 +13123,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -13155,7 +13200,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -13232,7 +13277,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -13309,7 +13354,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -13386,7 +13431,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -13463,7 +13508,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -13540,7 +13585,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -13617,7 +13662,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -13694,7 +13739,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -13771,7 +13816,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -13848,7 +13893,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -13925,7 +13970,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -14002,7 +14047,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -14079,7 +14124,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -14156,7 +14201,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -14233,7 +14278,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -14310,7 +14355,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -14387,7 +14432,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -14464,7 +14509,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -14541,7 +14586,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -14618,7 +14663,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -14695,7 +14740,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -14772,7 +14817,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -14849,7 +14894,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -14926,7 +14971,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -15003,7 +15048,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -15080,7 +15125,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -15157,7 +15202,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -15234,7 +15279,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -15311,7 +15356,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -15388,7 +15433,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -15465,7 +15510,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -15542,7 +15587,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -15619,7 +15664,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -15696,7 +15741,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -15773,7 +15818,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -15850,7 +15895,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -15927,7 +15972,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -16004,7 +16049,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -16081,7 +16126,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -16158,7 +16203,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -16235,7 +16280,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -16312,7 +16357,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -16389,7 +16434,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -16466,7 +16511,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -16543,7 +16588,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -16620,7 +16665,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -16697,7 +16742,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -16774,7 +16819,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -16851,7 +16896,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -16928,7 +16973,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -17005,7 +17050,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -17082,7 +17127,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -17159,7 +17204,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -17236,7 +17281,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -17313,7 +17358,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -17390,7 +17435,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -17467,7 +17512,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -17544,7 +17589,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -17621,7 +17666,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -17698,7 +17743,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -17775,7 +17820,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -17852,7 +17897,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -17929,7 +17974,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -18006,7 +18051,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -18083,7 +18128,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -18160,7 +18205,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -18237,7 +18282,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -18314,7 +18359,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -18391,7 +18436,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -18468,7 +18513,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -18545,7 +18590,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -18622,7 +18667,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -18699,7 +18744,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -18776,7 +18821,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -18853,7 +18898,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -18930,7 +18975,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -19007,7 +19052,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -19084,7 +19129,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -19161,7 +19206,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -19238,7 +19283,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -19315,7 +19360,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -19392,7 +19437,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -19469,7 +19514,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -19546,7 +19591,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -19623,7 +19668,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -19700,7 +19745,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -19777,7 +19822,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -19854,7 +19899,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -19931,7 +19976,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -20008,7 +20053,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -20085,7 +20130,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -20098,8 +20143,71 @@
       <c r="D136" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="E136" s="11">
+        <v>48</v>
+      </c>
+      <c r="F136" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G136" s="11">
+        <v>36.832999999999998</v>
+      </c>
+      <c r="H136" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I136" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J136" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K136" s="11">
+        <v>90</v>
+      </c>
+      <c r="L136" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M136" s="11">
+        <v>73.317999999999998</v>
+      </c>
+      <c r="N136" s="11">
+        <v>15</v>
+      </c>
+      <c r="O136" s="11">
+        <v>13</v>
+      </c>
+      <c r="P136" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q136" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R136" s="11">
+        <v>12</v>
+      </c>
+      <c r="S136" s="11">
+        <v>33.659999999999997</v>
+      </c>
+      <c r="T136" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U136" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="V136" s="11">
+        <v>6.766</v>
+      </c>
+      <c r="W136" s="11">
+        <v>9.65</v>
+      </c>
+      <c r="X136" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y136" s="11">
+        <v>7.625</v>
+      </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -20112,8 +20220,71 @@
       <c r="D137" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="E137" s="11">
+        <v>48</v>
+      </c>
+      <c r="F137" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G137" s="11">
+        <v>36.832999999999998</v>
+      </c>
+      <c r="H137" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I137" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J137" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K137" s="11">
+        <v>92</v>
+      </c>
+      <c r="L137" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M137" s="11">
+        <v>73.317999999999998</v>
+      </c>
+      <c r="N137" s="11">
+        <v>15</v>
+      </c>
+      <c r="O137" s="11">
+        <v>13</v>
+      </c>
+      <c r="P137" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q137" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R137" s="11">
+        <v>12</v>
+      </c>
+      <c r="S137" s="11">
+        <v>33.659999999999997</v>
+      </c>
+      <c r="T137" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U137" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="V137" s="11">
+        <v>6.766</v>
+      </c>
+      <c r="W137" s="11">
+        <v>9.65</v>
+      </c>
+      <c r="X137" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y137" s="11">
+        <v>7.625</v>
+      </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -20143,17 +20314,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -20242,7 +20413,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -20323,7 +20494,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -20412,7 +20583,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -20501,7 +20672,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -20520,24 +20691,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -20590,7 +20761,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -20635,7 +20806,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -20688,7 +20859,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -20741,7 +20912,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -20782,7 +20953,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -20823,7 +20994,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -20864,7 +21035,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -20905,7 +21076,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -20946,7 +21117,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -20987,7 +21158,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -21044,18 +21215,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -21102,7 +21273,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -21141,7 +21312,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -21188,7 +21359,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -21235,7 +21406,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -21267,7 +21438,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -21299,7 +21470,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -21331,7 +21502,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -21363,7 +21534,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -21395,7 +21566,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -21427,7 +21598,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -21474,7 +21645,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -21488,15 +21659,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -21507,7 +21678,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -21521,7 +21692,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -21530,7 +21701,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -21539,7 +21710,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -21548,7 +21719,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -21557,7 +21728,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -21566,7 +21737,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -21575,7 +21746,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -21584,49 +21755,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -21637,7 +21808,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -21646,7 +21817,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -21655,7 +21826,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -21666,7 +21837,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -21675,7 +21846,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -21684,42 +21855,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -21728,35 +21899,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAD60B3-27EA-41D2-9209-D6EC749F0A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FC7B14-15ED-4CE0-A823-CE5041307AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -244,23 +247,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +276,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +319,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,27 +340,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -365,8 +368,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +387,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1270,6 +1273,12 @@
                 <c:pt idx="135">
                   <c:v>37</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>37</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2149,6 +2158,12 @@
                 <c:pt idx="135">
                   <c:v>21.3</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>21.3</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3028,6 +3043,12 @@
                 <c:pt idx="135">
                   <c:v>73.317999999999998</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>73.090999999999994</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>73.090999999999994</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3907,6 +3928,12 @@
                 <c:pt idx="135">
                   <c:v>13.55</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>13.55</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>13.55</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4785,6 +4812,12 @@
                 </c:pt>
                 <c:pt idx="135">
                   <c:v>33.659999999999997</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>33.659999999999997</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>33.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5681,6 +5714,12 @@
                 <c:pt idx="135">
                   <c:v>6.766</c:v>
                 </c:pt>
+                <c:pt idx="136">
+                  <c:v>6.73</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>6.73</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6561,6 +6600,12 @@
                 </c:pt>
                 <c:pt idx="135">
                   <c:v>7.625</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>7.6749999999999998</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>7.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6795,7 +6840,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6803,6 +6847,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6838,7 +6883,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7305,7 +7350,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7313,6 +7357,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7348,7 +7393,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7720,7 +7765,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7728,6 +7772,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9814,17 +9859,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y141"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -9901,7 +9946,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -9970,7 +10015,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -10047,7 +10092,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -10124,7 +10169,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -10201,7 +10246,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -10278,7 +10323,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -10355,7 +10400,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -10432,7 +10477,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -10509,7 +10554,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -10586,7 +10631,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -10663,7 +10708,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -10740,7 +10785,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -10817,7 +10862,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -10894,7 +10939,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -10971,7 +11016,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -11048,7 +11093,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -11125,7 +11170,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -11202,7 +11247,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -11279,7 +11324,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -11356,7 +11401,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -11433,7 +11478,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -11510,7 +11555,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -11587,7 +11632,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -11664,7 +11709,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -11741,7 +11786,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -11818,7 +11863,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -11895,7 +11940,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -11972,7 +12017,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -12049,7 +12094,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -12126,7 +12171,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -12203,7 +12248,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -12280,7 +12325,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -12357,7 +12402,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -12434,7 +12479,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -12511,7 +12556,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -12588,7 +12633,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -12665,7 +12710,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -12742,7 +12787,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -12819,7 +12864,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -12896,7 +12941,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -12973,7 +13018,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -13050,7 +13095,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -13127,7 +13172,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -13204,7 +13249,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -13281,7 +13326,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -13358,7 +13403,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -13435,7 +13480,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -13512,7 +13557,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -13589,7 +13634,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -13666,7 +13711,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -13743,7 +13788,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -13820,7 +13865,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -13897,7 +13942,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -13974,7 +14019,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -14051,7 +14096,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -14128,7 +14173,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -14205,7 +14250,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -14282,7 +14327,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -14359,7 +14404,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -14436,7 +14481,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -14513,7 +14558,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -14590,7 +14635,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -14667,7 +14712,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -14744,7 +14789,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -14821,7 +14866,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -14898,7 +14943,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -14975,7 +15020,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -15052,7 +15097,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -15129,7 +15174,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -15206,7 +15251,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -15283,7 +15328,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -15360,7 +15405,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -15437,7 +15482,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -15514,7 +15559,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -15591,7 +15636,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -15668,7 +15713,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -15745,7 +15790,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -15822,7 +15867,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -15899,7 +15944,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -15976,7 +16021,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -16053,7 +16098,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -16130,7 +16175,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -16207,7 +16252,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -16284,7 +16329,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -16361,7 +16406,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -16438,7 +16483,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -16515,7 +16560,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -16592,7 +16637,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -16669,7 +16714,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -16746,7 +16791,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -16823,7 +16868,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -16900,7 +16945,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -16977,7 +17022,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -17054,7 +17099,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -17131,7 +17176,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -17208,7 +17253,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -17285,7 +17330,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -17362,7 +17407,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -17439,7 +17484,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -17516,7 +17561,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -17593,7 +17638,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -17670,7 +17715,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -17747,7 +17792,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -17824,7 +17869,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -17901,7 +17946,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -17978,7 +18023,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -18055,7 +18100,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -18132,7 +18177,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -18209,7 +18254,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -18286,7 +18331,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -18363,7 +18408,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -18440,7 +18485,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -18517,7 +18562,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -18594,7 +18639,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -18671,7 +18716,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -18748,7 +18793,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -18825,7 +18870,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -18902,7 +18947,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -18979,7 +19024,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -19056,7 +19101,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -19133,7 +19178,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -19210,7 +19255,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -19287,7 +19332,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -19364,7 +19409,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -19441,7 +19486,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -19518,7 +19563,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -19595,7 +19640,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -19672,7 +19717,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -19749,7 +19794,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -19826,7 +19871,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -19903,7 +19948,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -19980,7 +20025,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -20057,7 +20102,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -20134,7 +20179,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -20211,7 +20256,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -20288,7 +20333,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -20365,7 +20410,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -20442,7 +20487,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -20455,8 +20500,71 @@
       <c r="D139" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="E139" s="11">
+        <v>48</v>
+      </c>
+      <c r="F139" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G139" s="11">
+        <v>37</v>
+      </c>
+      <c r="H139" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I139" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J139" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K139" s="11">
+        <v>90</v>
+      </c>
+      <c r="L139" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M139" s="11">
+        <v>73.090999999999994</v>
+      </c>
+      <c r="N139" s="11">
+        <v>15</v>
+      </c>
+      <c r="O139" s="11">
+        <v>13</v>
+      </c>
+      <c r="P139" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q139" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R139" s="11">
+        <v>12</v>
+      </c>
+      <c r="S139" s="11">
+        <v>33.659999999999997</v>
+      </c>
+      <c r="T139" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U139" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="V139" s="11">
+        <v>6.73</v>
+      </c>
+      <c r="W139" s="11">
+        <v>9.65</v>
+      </c>
+      <c r="X139" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y139" s="11">
+        <v>7.6749999999999998</v>
+      </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -20469,8 +20577,71 @@
       <c r="D140" s="7" t="s">
         <v>53</v>
       </c>
+      <c r="E140" s="11">
+        <v>48</v>
+      </c>
+      <c r="F140" s="11">
+        <v>25.8</v>
+      </c>
+      <c r="G140" s="11">
+        <v>37</v>
+      </c>
+      <c r="H140" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I140" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J140" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K140" s="11">
+        <v>90</v>
+      </c>
+      <c r="L140" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M140" s="11">
+        <v>73.090999999999994</v>
+      </c>
+      <c r="N140" s="11">
+        <v>15</v>
+      </c>
+      <c r="O140" s="11">
+        <v>13</v>
+      </c>
+      <c r="P140" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q140" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R140" s="11">
+        <v>12</v>
+      </c>
+      <c r="S140" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T140" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U140" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="V140" s="11">
+        <v>6.73</v>
+      </c>
+      <c r="W140" s="11">
+        <v>9.65</v>
+      </c>
+      <c r="X140" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y140" s="11">
+        <v>7.7</v>
+      </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -20500,17 +20671,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
   <dimension ref="A1:AK5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -20599,7 +20770,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -20680,7 +20851,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -20769,7 +20940,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -20858,7 +21029,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
     </row>
@@ -20877,24 +21048,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -20947,7 +21118,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -20992,7 +21163,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -21045,7 +21216,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -21098,7 +21269,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -21139,7 +21310,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -21180,7 +21351,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -21221,7 +21392,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -21262,7 +21433,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -21303,7 +21474,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -21344,7 +21515,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -21401,18 +21572,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -21459,7 +21630,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -21498,7 +21669,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -21545,7 +21716,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -21592,7 +21763,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -21624,7 +21795,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -21656,7 +21827,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -21688,7 +21859,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -21720,7 +21891,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -21752,7 +21923,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -21784,7 +21955,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -21831,7 +22002,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -21845,15 +22016,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -21864,7 +22035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -21878,7 +22049,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -21887,7 +22058,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -21896,7 +22067,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -21905,7 +22076,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -21914,7 +22085,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -21923,7 +22094,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -21932,7 +22103,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -21941,49 +22112,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -21994,7 +22165,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -22003,7 +22174,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -22012,7 +22183,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -22023,7 +22194,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -22032,7 +22203,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -22041,42 +22212,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -22085,35 +22256,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0FC7B14-15ED-4CE0-A823-CE5041307AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99837A0A-F2D0-48AC-92BA-47F53B3E84B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -25,15 +25,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -247,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -276,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -319,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -340,36 +337,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -387,7 +384,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1279,6 +1276,9 @@
                 <c:pt idx="137">
                   <c:v>37</c:v>
                 </c:pt>
+                <c:pt idx="138">
+                  <c:v>37</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2164,6 +2164,9 @@
                 <c:pt idx="137">
                   <c:v>21.3</c:v>
                 </c:pt>
+                <c:pt idx="138">
+                  <c:v>21.25</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3049,6 +3052,9 @@
                 <c:pt idx="137">
                   <c:v>73.090999999999994</c:v>
                 </c:pt>
+                <c:pt idx="138">
+                  <c:v>73.090999999999994</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3934,6 +3940,9 @@
                 <c:pt idx="137">
                   <c:v>13.55</c:v>
                 </c:pt>
+                <c:pt idx="138">
+                  <c:v>13.55</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4817,6 +4826,9 @@
                   <c:v>33.659999999999997</c:v>
                 </c:pt>
                 <c:pt idx="137">
+                  <c:v>33.6</c:v>
+                </c:pt>
+                <c:pt idx="138">
                   <c:v>33.6</c:v>
                 </c:pt>
               </c:numCache>
@@ -5720,6 +5732,9 @@
                 <c:pt idx="137">
                   <c:v>6.73</c:v>
                 </c:pt>
+                <c:pt idx="138">
+                  <c:v>6.73</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6605,6 +6620,9 @@
                   <c:v>7.6749999999999998</c:v>
                 </c:pt>
                 <c:pt idx="137">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="138">
                   <c:v>7.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -6840,6 +6858,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6847,7 +6866,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6883,7 +6901,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7350,6 +7368,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7357,7 +7376,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7393,7 +7411,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7765,6 +7783,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7772,7 +7791,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9859,27 +9877,27 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y141"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:25" s="5" customFormat="1">
+      <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="9" t="s">
@@ -9946,11 +9964,11 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
+    <row r="2" spans="1:25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -10015,7 +10033,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -10092,7 +10110,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -10169,7 +10187,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -10246,7 +10264,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -10323,7 +10341,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -10400,7 +10418,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -10477,7 +10495,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -10554,7 +10572,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -10631,7 +10649,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -10708,7 +10726,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -10785,7 +10803,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -10862,7 +10880,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -10939,7 +10957,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -11016,7 +11034,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -11093,7 +11111,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -11170,7 +11188,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -11247,7 +11265,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -11324,7 +11342,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -11401,7 +11419,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -11478,7 +11496,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -11555,7 +11573,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -11632,7 +11650,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -11709,7 +11727,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -11786,7 +11804,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -11863,7 +11881,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -11940,7 +11958,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -12017,7 +12035,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -12094,7 +12112,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -12171,7 +12189,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -12248,7 +12266,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -12325,7 +12343,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -12402,7 +12420,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -12479,7 +12497,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -12556,7 +12574,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -12633,7 +12651,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -12710,7 +12728,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -12787,7 +12805,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -12864,7 +12882,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -12941,7 +12959,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -13018,7 +13036,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -13095,7 +13113,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -13172,7 +13190,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -13249,7 +13267,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -13326,7 +13344,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -13403,7 +13421,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -13480,7 +13498,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -13557,7 +13575,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -13634,7 +13652,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -13711,7 +13729,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -13788,7 +13806,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -13865,7 +13883,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -13942,7 +13960,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -14019,7 +14037,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -14096,7 +14114,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -14173,7 +14191,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -14250,7 +14268,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -14327,7 +14345,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -14404,7 +14422,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -14481,7 +14499,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -14558,7 +14576,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -14635,7 +14653,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -14712,7 +14730,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -14789,7 +14807,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -14866,7 +14884,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -14943,7 +14961,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -15020,7 +15038,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -15097,7 +15115,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -15174,7 +15192,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -15251,7 +15269,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -15328,7 +15346,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -15405,7 +15423,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -15482,7 +15500,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -15559,7 +15577,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -15636,7 +15654,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -15713,7 +15731,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -15790,7 +15808,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -15867,7 +15885,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -15944,7 +15962,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -16021,7 +16039,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -16098,7 +16116,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -16175,7 +16193,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -16252,7 +16270,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -16329,7 +16347,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -16406,7 +16424,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -16483,7 +16501,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -16560,7 +16578,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -16637,7 +16655,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -16714,7 +16732,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -16791,7 +16809,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -16868,7 +16886,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -16945,7 +16963,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -17022,7 +17040,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -17099,7 +17117,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -17176,7 +17194,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -17253,7 +17271,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -17330,7 +17348,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -17407,7 +17425,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -17484,7 +17502,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -17561,7 +17579,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -17638,7 +17656,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -17715,7 +17733,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -17792,7 +17810,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -17869,7 +17887,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -17946,7 +17964,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -18023,7 +18041,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -18100,7 +18118,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -18177,7 +18195,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -18254,7 +18272,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -18331,7 +18349,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -18408,7 +18426,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -18485,7 +18503,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -18562,7 +18580,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -18639,7 +18657,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -18716,7 +18734,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -18793,7 +18811,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -18870,7 +18888,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -18947,7 +18965,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -19024,7 +19042,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -19101,7 +19119,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -19178,7 +19196,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -19255,7 +19273,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -19332,7 +19350,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -19409,7 +19427,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -19486,7 +19504,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -19563,7 +19581,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -19640,7 +19658,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -19717,7 +19735,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -19794,7 +19812,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -19871,7 +19889,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -19948,7 +19966,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -20025,7 +20043,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -20102,7 +20120,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -20179,7 +20197,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -20256,7 +20274,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -20333,7 +20351,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -20410,7 +20428,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -20487,7 +20505,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -20564,7 +20582,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -20641,7 +20659,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -20653,6 +20671,69 @@
       </c>
       <c r="D141" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E141" s="11">
+        <v>48</v>
+      </c>
+      <c r="F141" s="11">
+        <v>26</v>
+      </c>
+      <c r="G141" s="11">
+        <v>37</v>
+      </c>
+      <c r="H141" s="11">
+        <v>23.8</v>
+      </c>
+      <c r="I141" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J141" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K141" s="11">
+        <v>90</v>
+      </c>
+      <c r="L141" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="M141" s="11">
+        <v>73.090999999999994</v>
+      </c>
+      <c r="N141" s="11">
+        <v>15</v>
+      </c>
+      <c r="O141" s="11">
+        <v>13</v>
+      </c>
+      <c r="P141" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q141" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="R141" s="11">
+        <v>12</v>
+      </c>
+      <c r="S141" s="11">
+        <v>33.6</v>
+      </c>
+      <c r="T141" s="11">
+        <v>7.95</v>
+      </c>
+      <c r="U141" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="V141" s="11">
+        <v>6.73</v>
+      </c>
+      <c r="W141" s="11">
+        <v>9.65</v>
+      </c>
+      <c r="X141" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y141" s="11">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -20670,28 +20751,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
-  <dimension ref="A1:AK5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AK6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="25" width="9" style="11"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9" style="11"/>
+    <col min="8" max="10" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:37" s="5" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="10" t="s">
@@ -20770,11 +20853,11 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+    <row r="2" spans="1:37">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -20851,7 +20934,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -20859,7 +20942,7 @@
         <v>46022</v>
       </c>
       <c r="C3" s="8">
-        <v>0.70833333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>53</v>
@@ -20940,7 +21023,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -20948,7 +21031,7 @@
         <v>46052</v>
       </c>
       <c r="C4" s="8">
-        <v>0.70833333333333337</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>53</v>
@@ -21029,9 +21112,114 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+    <row r="5" spans="1:37">
+      <c r="A5" s="6">
+        <v>46023</v>
+      </c>
+      <c r="B5" s="6">
+        <v>46079</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="11">
+        <v>78.5</v>
+      </c>
+      <c r="F5" s="11">
+        <v>72.5</v>
+      </c>
+      <c r="G5" s="11">
+        <v>75</v>
+      </c>
+      <c r="K5" s="11">
+        <v>92</v>
+      </c>
+      <c r="L5" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="M5" s="11">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B6" s="6">
+        <v>46112</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="11">
+        <v>78.5</v>
+      </c>
+      <c r="F6" s="11">
+        <v>72.5</v>
+      </c>
+      <c r="G6" s="11">
+        <v>75</v>
+      </c>
+      <c r="H6" s="11">
+        <v>175</v>
+      </c>
+      <c r="I6" s="11">
+        <v>130</v>
+      </c>
+      <c r="J6" s="11">
+        <v>165</v>
+      </c>
+      <c r="K6" s="11">
+        <v>92</v>
+      </c>
+      <c r="L6" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="M6" s="11">
+        <v>85</v>
+      </c>
+      <c r="N6" s="11">
+        <v>36</v>
+      </c>
+      <c r="O6" s="11">
+        <v>27</v>
+      </c>
+      <c r="P6" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>17</v>
+      </c>
+      <c r="R6" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="S6" s="11">
+        <v>13</v>
+      </c>
+      <c r="T6" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U6" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="V6" s="11">
+        <v>6</v>
+      </c>
+      <c r="W6" s="11">
+        <v>6</v>
+      </c>
+      <c r="X6" s="11">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="11">
+        <v>5.5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -21048,34 +21236,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:25" s="5" customFormat="1">
+      <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="13" t="s">
@@ -21118,11 +21306,11 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
+    <row r="2" spans="1:25">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="13" t="s">
         <v>54</v>
       </c>
@@ -21163,7 +21351,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -21216,7 +21404,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -21269,7 +21457,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -21310,7 +21498,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -21351,7 +21539,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -21392,7 +21580,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -21433,7 +21621,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -21474,7 +21662,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -21515,7 +21703,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -21572,28 +21760,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:25" s="5" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>52</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -21630,11 +21818,11 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+    <row r="2" spans="1:25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="10" t="s">
         <v>54</v>
       </c>
@@ -21669,7 +21857,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -21716,7 +21904,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -21763,7 +21951,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -21795,7 +21983,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -21827,7 +22015,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -21859,7 +22047,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -21891,7 +22079,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -21923,7 +22111,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -21955,7 +22143,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -22002,7 +22190,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -22016,15 +22204,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -22035,7 +22223,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -22049,7 +22237,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -22058,7 +22246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -22067,7 +22255,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -22076,7 +22264,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -22085,7 +22273,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -22094,7 +22282,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -22103,7 +22291,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -22112,49 +22300,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -22165,7 +22353,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -22174,7 +22362,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -22183,7 +22371,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -22194,7 +22382,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -22203,7 +22391,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -22212,42 +22400,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -22256,35 +22444,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE37BA9-FA98-4236-B7BE-D8705C46B5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE804B8-453D-49BB-8CE6-81827ED49567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -874,6 +874,15 @@
                 <c:pt idx="141">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="142">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>46120</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1304,6 +1313,15 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="140">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="143">
                   <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
@@ -1777,6 +1795,15 @@
                 <c:pt idx="141">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="142">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>46120</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2207,6 +2234,15 @@
                   <c:v>21.25</c:v>
                 </c:pt>
                 <c:pt idx="140">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="143">
                   <c:v>21.25</c:v>
                 </c:pt>
               </c:numCache>
@@ -2680,6 +2716,15 @@
                 <c:pt idx="141">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="142">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>46120</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3111,6 +3156,15 @@
                 </c:pt>
                 <c:pt idx="140">
                   <c:v>73.036000000000001</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>73.036000000000001</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>72.817999999999998</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>72.817999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3583,6 +3637,15 @@
                 <c:pt idx="141">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="142">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>46120</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4013,6 +4076,15 @@
                   <c:v>13.55</c:v>
                 </c:pt>
                 <c:pt idx="140">
+                  <c:v>13.55</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>13.55</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>13.55</c:v>
+                </c:pt>
+                <c:pt idx="143">
                   <c:v>13.55</c:v>
                 </c:pt>
               </c:numCache>
@@ -4486,6 +4558,15 @@
                 <c:pt idx="141">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="142">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>46120</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4916,6 +4997,15 @@
                   <c:v>33.6</c:v>
                 </c:pt>
                 <c:pt idx="140">
+                  <c:v>33.56</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>33.56</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>33.56</c:v>
+                </c:pt>
+                <c:pt idx="143">
                   <c:v>33.56</c:v>
                 </c:pt>
               </c:numCache>
@@ -5405,6 +5495,15 @@
                 <c:pt idx="141">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="142">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>46120</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5835,6 +5934,15 @@
                   <c:v>6.72</c:v>
                 </c:pt>
                 <c:pt idx="140">
+                  <c:v>6.72</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>6.72</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>6.72</c:v>
+                </c:pt>
+                <c:pt idx="143">
                   <c:v>6.72</c:v>
                 </c:pt>
               </c:numCache>
@@ -6310,6 +6418,15 @@
                 <c:pt idx="141">
                   <c:v>46119</c:v>
                 </c:pt>
+                <c:pt idx="142">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>46120</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>46120</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6740,6 +6857,15 @@
                   <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="140">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>7.7</c:v>
+                </c:pt>
+                <c:pt idx="143">
                   <c:v>7.7</c:v>
                 </c:pt>
               </c:numCache>
@@ -6769,7 +6895,7 @@
         <c:axId val="1539939664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="46203"/>
+          <c:max val="46387"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -6815,7 +6941,7 @@
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
-        <c:majorUnit val="1"/>
+        <c:majorUnit val="2"/>
         <c:majorTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
@@ -10083,7 +10209,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y144"/>
+  <dimension ref="A1:Y147"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.125" style="12" bestFit="1" customWidth="1"/>
@@ -21061,7 +21187,7 @@
         <v>73.036000000000001</v>
       </c>
       <c r="N143" s="11">
-        <v>16.899999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="O143" s="11">
         <v>12.95</v>
@@ -21108,6 +21234,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D144" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E144" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F144" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="G144" s="11">
+        <v>37</v>
+      </c>
+      <c r="H144" s="11">
+        <v>24</v>
+      </c>
+      <c r="I144" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J144" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K144" s="11">
+        <v>89</v>
+      </c>
+      <c r="L144" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="M144" s="11">
+        <v>73.036000000000001</v>
+      </c>
+      <c r="N144" s="11">
+        <v>14.9</v>
+      </c>
+      <c r="O144" s="11">
+        <v>12.95</v>
+      </c>
+      <c r="P144" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q144" s="11">
+        <v>49</v>
+      </c>
+      <c r="R144" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="S144" s="11">
+        <v>33.56</v>
+      </c>
+      <c r="T144" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="U144" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="V144" s="11">
+        <v>6.72</v>
+      </c>
+      <c r="W144" s="11">
+        <v>9.75</v>
+      </c>
+      <c r="X144" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y144" s="11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A145" s="12">
+        <v>46120</v>
+      </c>
+      <c r="B145" s="12">
+        <v>46120</v>
+      </c>
+      <c r="C145" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E145" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F145" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="G145" s="11">
+        <v>37</v>
+      </c>
+      <c r="H145" s="11">
+        <v>24</v>
+      </c>
+      <c r="I145" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J145" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K145" s="11">
+        <v>89</v>
+      </c>
+      <c r="L145" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="M145" s="11">
+        <v>72.817999999999998</v>
+      </c>
+      <c r="N145" s="11">
+        <v>14.9</v>
+      </c>
+      <c r="O145" s="11">
+        <v>12.95</v>
+      </c>
+      <c r="P145" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q145" s="11">
+        <v>49</v>
+      </c>
+      <c r="R145" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="S145" s="11">
+        <v>33.56</v>
+      </c>
+      <c r="T145" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="U145" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="V145" s="11">
+        <v>6.72</v>
+      </c>
+      <c r="W145" s="11">
+        <v>9.75</v>
+      </c>
+      <c r="X145" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y145" s="11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A146" s="12">
+        <v>46120</v>
+      </c>
+      <c r="B146" s="12">
+        <v>46120</v>
+      </c>
+      <c r="C146" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E146" s="11">
+        <v>48.5</v>
+      </c>
+      <c r="F146" s="11">
+        <v>26.2</v>
+      </c>
+      <c r="G146" s="11">
+        <v>37</v>
+      </c>
+      <c r="H146" s="11">
+        <v>24</v>
+      </c>
+      <c r="I146" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="J146" s="11">
+        <v>21.25</v>
+      </c>
+      <c r="K146" s="11">
+        <v>89</v>
+      </c>
+      <c r="L146" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="M146" s="11">
+        <v>72.817999999999998</v>
+      </c>
+      <c r="N146" s="11">
+        <v>14.9</v>
+      </c>
+      <c r="O146" s="11">
+        <v>12.95</v>
+      </c>
+      <c r="P146" s="11">
+        <v>13.55</v>
+      </c>
+      <c r="Q146" s="11">
+        <v>49</v>
+      </c>
+      <c r="R146" s="11">
+        <v>12.5</v>
+      </c>
+      <c r="S146" s="11">
+        <v>33.56</v>
+      </c>
+      <c r="T146" s="11">
+        <v>7.8</v>
+      </c>
+      <c r="U146" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="V146" s="11">
+        <v>6.72</v>
+      </c>
+      <c r="W146" s="11">
+        <v>9.75</v>
+      </c>
+      <c r="X146" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y146" s="11">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A147" s="12">
+        <v>46120</v>
+      </c>
+      <c r="B147" s="12">
+        <v>46120</v>
+      </c>
+      <c r="C147" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D147" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBDD5A9-415C-4036-9C3E-2B1E5F6A8D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82324EB5-987E-4CE3-A042-F5F822F6681D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -20,26 +20,17 @@
     <sheet name="fig" sheetId="6" r:id="rId5"/>
     <sheet name="info" sheetId="1" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -253,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +337,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +365,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +384,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -898,6 +889,15 @@
                 <c:pt idx="150">
                   <c:v>46122</c:v>
                 </c:pt>
+                <c:pt idx="151">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1359,6 +1359,12 @@
                 </c:pt>
                 <c:pt idx="150">
                   <c:v>37.033000000000001</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>37.033000000000001</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>37.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1858,6 +1864,15 @@
                 <c:pt idx="150">
                   <c:v>46122</c:v>
                 </c:pt>
+                <c:pt idx="151">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2318,6 +2333,12 @@
                   <c:v>21.25</c:v>
                 </c:pt>
                 <c:pt idx="150">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="152">
                   <c:v>21.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -2818,6 +2839,15 @@
                 <c:pt idx="150">
                   <c:v>46122</c:v>
                 </c:pt>
+                <c:pt idx="151">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3279,6 +3309,12 @@
                 </c:pt>
                 <c:pt idx="150">
                   <c:v>71.5</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>71.272999999999996</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>71.182000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3778,6 +3814,15 @@
                 <c:pt idx="150">
                   <c:v>46122</c:v>
                 </c:pt>
+                <c:pt idx="151">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4239,6 +4284,12 @@
                 </c:pt>
                 <c:pt idx="150">
                   <c:v>13.5</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>13.475</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4738,6 +4789,15 @@
                 <c:pt idx="150">
                   <c:v>46122</c:v>
                 </c:pt>
+                <c:pt idx="151">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5198,6 +5258,12 @@
                   <c:v>33.4</c:v>
                 </c:pt>
                 <c:pt idx="150">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="152">
                   <c:v>33.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -5714,6 +5780,15 @@
                 <c:pt idx="150">
                   <c:v>46122</c:v>
                 </c:pt>
+                <c:pt idx="151">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6175,6 +6250,12 @@
                 </c:pt>
                 <c:pt idx="150">
                   <c:v>6.63</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>6.61</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>6.61</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6676,6 +6757,15 @@
                 <c:pt idx="150">
                   <c:v>46122</c:v>
                 </c:pt>
+                <c:pt idx="151">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7137,6 +7227,12 @@
                 </c:pt>
                 <c:pt idx="150">
                   <c:v>7.75</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>7.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7414,7 +7510,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7496,6 +7592,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7534,6 +7633,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>242.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>222.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7610,6 +7712,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7648,6 +7753,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>935</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>930</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7724,6 +7832,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7762,6 +7873,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>149.333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7978,7 +8092,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8060,6 +8174,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8098,6 +8215,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>12.526999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.318</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8174,6 +8294,9 @@
                 <c:pt idx="9">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8212,6 +8335,9 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>12.71</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.412000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10475,22 +10601,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22904F78-1984-4AE6-95B0-F134CF800348}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y153"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y156"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -10567,7 +10693,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -10636,7 +10762,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -10713,7 +10839,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -10790,7 +10916,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -10867,7 +10993,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -10944,7 +11070,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -11021,7 +11147,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -11098,7 +11224,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -11175,7 +11301,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -11252,7 +11378,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -11329,7 +11455,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -11406,7 +11532,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -11483,7 +11609,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -11560,7 +11686,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -11637,7 +11763,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -11714,7 +11840,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -11791,7 +11917,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -11868,7 +11994,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -11945,7 +12071,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -12022,7 +12148,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -12099,7 +12225,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -12176,7 +12302,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -12253,7 +12379,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -12330,7 +12456,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -12407,7 +12533,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -12484,7 +12610,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -12561,7 +12687,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -12638,7 +12764,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -12715,7 +12841,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -12792,7 +12918,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -12869,7 +12995,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -12946,7 +13072,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -13023,7 +13149,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -13100,7 +13226,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -13177,7 +13303,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -13254,7 +13380,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -13331,7 +13457,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -13408,7 +13534,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -13485,7 +13611,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -13562,7 +13688,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -13639,7 +13765,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -13716,7 +13842,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -13793,7 +13919,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -13870,7 +13996,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -13947,7 +14073,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -14024,7 +14150,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -14101,7 +14227,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -14178,7 +14304,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -14255,7 +14381,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -14332,7 +14458,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -14409,7 +14535,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -14486,7 +14612,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -14563,7 +14689,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -14640,7 +14766,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -14717,7 +14843,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -14794,7 +14920,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -14871,7 +14997,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -14948,7 +15074,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -15025,7 +15151,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -15102,7 +15228,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -15179,7 +15305,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -15256,7 +15382,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -15333,7 +15459,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -15410,7 +15536,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -15487,7 +15613,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -15564,7 +15690,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -15641,7 +15767,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -15718,7 +15844,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -15795,7 +15921,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -15872,7 +15998,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -15949,7 +16075,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -16026,7 +16152,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -16103,7 +16229,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -16180,7 +16306,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -16257,7 +16383,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -16334,7 +16460,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -16411,7 +16537,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -16488,7 +16614,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -16565,7 +16691,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -16642,7 +16768,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -16719,7 +16845,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -16796,7 +16922,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -16873,7 +16999,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -16950,7 +17076,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -17027,7 +17153,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -17104,7 +17230,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -17181,7 +17307,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -17258,7 +17384,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -17335,7 +17461,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -17412,7 +17538,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -17489,7 +17615,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -17566,7 +17692,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -17643,7 +17769,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -17720,7 +17846,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -17797,7 +17923,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -17874,7 +18000,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -17951,7 +18077,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -18028,7 +18154,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -18105,7 +18231,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -18182,7 +18308,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -18259,7 +18385,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -18336,7 +18462,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -18413,7 +18539,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -18490,7 +18616,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -18567,7 +18693,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -18644,7 +18770,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -18721,7 +18847,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -18798,7 +18924,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -18875,7 +19001,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -18952,7 +19078,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -19029,7 +19155,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -19106,7 +19232,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -19183,7 +19309,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -19260,7 +19386,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -19337,7 +19463,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -19414,7 +19540,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -19491,7 +19617,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -19568,7 +19694,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -19645,7 +19771,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -19722,7 +19848,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -19799,7 +19925,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -19876,7 +20002,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -19953,7 +20079,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -20030,7 +20156,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -20107,7 +20233,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -20184,7 +20310,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -20261,7 +20387,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -20338,7 +20464,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -20415,7 +20541,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -20492,7 +20618,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -20569,7 +20695,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -20646,7 +20772,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -20723,7 +20849,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -20800,7 +20926,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -20877,7 +21003,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -20954,7 +21080,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -21031,7 +21157,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -21108,7 +21234,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -21185,7 +21311,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -21262,7 +21388,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -21339,7 +21465,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -21416,7 +21542,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -21493,7 +21619,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -21570,7 +21696,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -21647,7 +21773,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -21724,7 +21850,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -21801,7 +21927,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -21878,7 +22004,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -21955,7 +22081,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -22032,7 +22158,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -22109,7 +22235,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -22186,7 +22312,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -22261,6 +22387,174 @@
       </c>
       <c r="Y153" s="11">
         <v>7.75</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A154" s="12">
+        <v>46125</v>
+      </c>
+      <c r="B154" s="12">
+        <v>46125</v>
+      </c>
+      <c r="C154" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E154" s="11">
+        <v>49</v>
+      </c>
+      <c r="F154" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G154" s="11">
+        <v>37.033000000000001</v>
+      </c>
+      <c r="H154" s="11">
+        <v>24</v>
+      </c>
+      <c r="I154" s="11">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="J154" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K154" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L154" s="11">
+        <v>27.5</v>
+      </c>
+      <c r="M154" s="11">
+        <v>71.272999999999996</v>
+      </c>
+      <c r="N154" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O154" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P154" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q154" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R154" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="S154" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T154" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="U154" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="V154" s="11">
+        <v>6.61</v>
+      </c>
+      <c r="W154" s="11">
+        <v>10</v>
+      </c>
+      <c r="X154" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y154" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A155" s="12">
+        <v>46125</v>
+      </c>
+      <c r="B155" s="12">
+        <v>46125</v>
+      </c>
+      <c r="C155" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E155" s="11">
+        <v>49</v>
+      </c>
+      <c r="F155" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G155" s="11">
+        <v>37.1</v>
+      </c>
+      <c r="H155" s="11">
+        <v>24</v>
+      </c>
+      <c r="I155" s="11">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="J155" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K155" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L155" s="11">
+        <v>27.5</v>
+      </c>
+      <c r="M155" s="11">
+        <v>71.182000000000002</v>
+      </c>
+      <c r="N155" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O155" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P155" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q155" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R155" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="S155" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T155" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="U155" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="V155" s="11">
+        <v>6.61</v>
+      </c>
+      <c r="W155" s="11">
+        <v>10</v>
+      </c>
+      <c r="X155" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y155" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A156" s="12">
+        <v>46125</v>
+      </c>
+      <c r="B156" s="12">
+        <v>46125</v>
+      </c>
+      <c r="C156" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -22277,22 +22571,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E2CD10-06F7-40BE-85D8-E29219BBD9A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -22381,7 +22675,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -22462,7 +22756,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -22551,7 +22845,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -22640,7 +22934,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -22672,7 +22966,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -22762,27 +23056,27 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3556165B-22F0-4AF5-853E-ED25EB5C0B71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -22835,7 +23129,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -22880,7 +23174,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -22933,7 +23227,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -22986,7 +23280,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -23027,7 +23321,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -23068,7 +23362,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -23109,7 +23403,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -23150,7 +23444,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -23191,7 +23485,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -23232,7 +23526,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -23273,7 +23567,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -23312,6 +23606,47 @@
       </c>
       <c r="M12" s="11">
         <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" s="12">
+        <v>46118</v>
+      </c>
+      <c r="B13" s="12">
+        <v>46125</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="14">
+        <v>240</v>
+      </c>
+      <c r="F13" s="14">
+        <v>200</v>
+      </c>
+      <c r="G13" s="11">
+        <v>222.5</v>
+      </c>
+      <c r="H13" s="14">
+        <v>1150</v>
+      </c>
+      <c r="I13" s="14">
+        <v>880</v>
+      </c>
+      <c r="J13" s="11">
+        <v>930</v>
+      </c>
+      <c r="K13" s="14">
+        <v>171</v>
+      </c>
+      <c r="L13" s="14">
+        <v>134</v>
+      </c>
+      <c r="M13" s="11">
+        <v>149.333</v>
       </c>
     </row>
   </sheetData>
@@ -23328,21 +23663,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C550C51-95E6-4243-AC05-025707E45857}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:Y12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -23389,7 +23724,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -23428,7 +23763,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -23475,7 +23810,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -23522,7 +23857,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -23554,7 +23889,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -23586,7 +23921,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -23618,7 +23953,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -23650,7 +23985,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -23682,7 +24017,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -23714,7 +24049,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -23746,7 +24081,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -23776,6 +24111,38 @@
       </c>
       <c r="J12" s="11">
         <v>12.71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" s="12">
+        <v>46118</v>
+      </c>
+      <c r="B13" s="12">
+        <v>46125</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="11">
+        <v>20</v>
+      </c>
+      <c r="F13" s="11">
+        <v>10</v>
+      </c>
+      <c r="G13" s="11">
+        <v>12.318</v>
+      </c>
+      <c r="H13" s="11">
+        <v>20</v>
+      </c>
+      <c r="I13" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J13" s="11">
+        <v>12.412000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23791,10 +24158,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD8F7D3-2DB0-479E-83DC-4D765C588609}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -23806,18 +24173,18 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -23828,7 +24195,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -23842,7 +24209,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -23851,7 +24218,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -23860,7 +24227,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -23869,7 +24236,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -23878,7 +24245,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -23887,7 +24254,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -23896,7 +24263,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -23905,49 +24272,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -23958,7 +24325,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -23967,7 +24334,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -23976,7 +24343,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -23987,7 +24354,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -23996,7 +24363,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -24005,42 +24372,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -24049,35 +24416,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D063FFBD-DD72-4C97-939A-9997EE9741A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA62476-1871-4DBA-BFCE-FB62E18C7426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -907,6 +907,15 @@
                 <c:pt idx="156">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="157">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1383,6 +1392,15 @@
                 </c:pt>
                 <c:pt idx="155">
                   <c:v>37.1</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>37.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>37.533000000000001</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>37.466999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1900,6 +1918,15 @@
                 <c:pt idx="156">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="157">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2376,6 +2403,15 @@
                 </c:pt>
                 <c:pt idx="155">
                   <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>21.3</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>21.5</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>21.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2893,6 +2929,15 @@
                 <c:pt idx="156">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="157">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3369,6 +3414,15 @@
                 </c:pt>
                 <c:pt idx="155">
                   <c:v>70.727000000000004</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>70.727000000000004</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>70.5</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>70.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3886,6 +3940,15 @@
                 <c:pt idx="156">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="157">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4361,6 +4424,15 @@
                   <c:v>13.475</c:v>
                 </c:pt>
                 <c:pt idx="155">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>13.475</c:v>
+                </c:pt>
+                <c:pt idx="158">
                   <c:v>13.475</c:v>
                 </c:pt>
               </c:numCache>
@@ -4879,6 +4951,15 @@
                 <c:pt idx="156">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="157">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5355,6 +5436,15 @@
                 </c:pt>
                 <c:pt idx="155">
                   <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>33.4</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>33.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>33.200000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5888,6 +5978,15 @@
                 <c:pt idx="156">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="157">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6364,6 +6463,15 @@
                 </c:pt>
                 <c:pt idx="155">
                   <c:v>6.57</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>6.57</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>6.53</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>6.53</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6883,6 +6991,15 @@
                 <c:pt idx="156">
                   <c:v>46126</c:v>
                 </c:pt>
+                <c:pt idx="157">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>46127</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>46127</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7359,6 +7476,15 @@
                 </c:pt>
                 <c:pt idx="155">
                   <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>7.85</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>7.85</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10731,7 +10857,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y159"/>
+  <dimension ref="A1:Y162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -22911,6 +23037,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D159" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E159" s="11">
+        <v>49</v>
+      </c>
+      <c r="F159" s="11">
+        <v>26.5</v>
+      </c>
+      <c r="G159" s="11">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="H159" s="11">
+        <v>24</v>
+      </c>
+      <c r="I159" s="11">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="J159" s="11">
+        <v>21.3</v>
+      </c>
+      <c r="K159" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L159" s="11">
+        <v>28</v>
+      </c>
+      <c r="M159" s="11">
+        <v>70.727000000000004</v>
+      </c>
+      <c r="N159" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O159" s="11">
+        <v>12.9</v>
+      </c>
+      <c r="P159" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q159" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R159" s="11">
+        <v>13.5</v>
+      </c>
+      <c r="S159" s="11">
+        <v>33.4</v>
+      </c>
+      <c r="T159" s="11">
+        <v>7.4</v>
+      </c>
+      <c r="U159" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="V159" s="11">
+        <v>6.57</v>
+      </c>
+      <c r="W159" s="11">
+        <v>10</v>
+      </c>
+      <c r="X159" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y159" s="11">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A160" s="12">
+        <v>46127</v>
+      </c>
+      <c r="B160" s="12">
+        <v>46127</v>
+      </c>
+      <c r="C160" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E160" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="F160" s="11">
+        <v>27</v>
+      </c>
+      <c r="G160" s="11">
+        <v>37.533000000000001</v>
+      </c>
+      <c r="H160" s="11">
+        <v>24</v>
+      </c>
+      <c r="I160" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J160" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K160" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L160" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="M160" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="N160" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O160" s="11">
+        <v>13</v>
+      </c>
+      <c r="P160" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q160" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R160" s="11">
+        <v>14</v>
+      </c>
+      <c r="S160" s="11">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="T160" s="11">
+        <v>7.4</v>
+      </c>
+      <c r="U160" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="V160" s="11">
+        <v>6.53</v>
+      </c>
+      <c r="W160" s="11">
+        <v>10</v>
+      </c>
+      <c r="X160" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y160" s="11">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A161" s="12">
+        <v>46127</v>
+      </c>
+      <c r="B161" s="12">
+        <v>46127</v>
+      </c>
+      <c r="C161" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E161" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="F161" s="11">
+        <v>27</v>
+      </c>
+      <c r="G161" s="11">
+        <v>37.466999999999999</v>
+      </c>
+      <c r="H161" s="11">
+        <v>24</v>
+      </c>
+      <c r="I161" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J161" s="11">
+        <v>21.5</v>
+      </c>
+      <c r="K161" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L161" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="M161" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="N161" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O161" s="11">
+        <v>13</v>
+      </c>
+      <c r="P161" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q161" s="11">
+        <v>49.3</v>
+      </c>
+      <c r="R161" s="11">
+        <v>14</v>
+      </c>
+      <c r="S161" s="11">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="T161" s="11">
+        <v>7.4</v>
+      </c>
+      <c r="U161" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="V161" s="11">
+        <v>6.53</v>
+      </c>
+      <c r="W161" s="11">
+        <v>10</v>
+      </c>
+      <c r="X161" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="Y161" s="11">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A162" s="12">
+        <v>46127</v>
+      </c>
+      <c r="B162" s="12">
+        <v>46127</v>
+      </c>
+      <c r="C162" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D162" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBC2416-D944-4263-B5B1-D1A38C4E2AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A53F82D6-F67C-4D2F-8857-01C732C8B42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -244,23 +244,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -273,7 +273,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -316,7 +316,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -337,27 +337,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -365,8 +365,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -384,7 +384,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1438,6 +1438,9 @@
                 <c:pt idx="164">
                   <c:v>38.5</c:v>
                 </c:pt>
+                <c:pt idx="165">
+                  <c:v>38.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2485,6 +2488,9 @@
                 <c:pt idx="164">
                   <c:v>21.7</c:v>
                 </c:pt>
+                <c:pt idx="165">
+                  <c:v>21.7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3532,6 +3538,9 @@
                 <c:pt idx="164">
                   <c:v>69.182000000000002</c:v>
                 </c:pt>
+                <c:pt idx="165">
+                  <c:v>69.182000000000002</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4579,6 +4588,9 @@
                 <c:pt idx="164">
                   <c:v>13.475</c:v>
                 </c:pt>
+                <c:pt idx="165">
+                  <c:v>13.475</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5624,6 +5636,9 @@
                   <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="164">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="165">
                   <c:v>33</c:v>
                 </c:pt>
               </c:numCache>
@@ -6689,6 +6704,9 @@
                 <c:pt idx="164">
                   <c:v>6.43</c:v>
                 </c:pt>
+                <c:pt idx="165">
+                  <c:v>6.43</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -7736,6 +7754,9 @@
                   <c:v>8.0250000000000004</c:v>
                 </c:pt>
                 <c:pt idx="164">
+                  <c:v>8.0250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="165">
                   <c:v>8.0250000000000004</c:v>
                 </c:pt>
               </c:numCache>
@@ -8014,7 +8035,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8596,7 +8617,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11110,17 +11131,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y168"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -11197,7 +11218,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -11266,7 +11287,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -11343,7 +11364,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -11420,7 +11441,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -11497,7 +11518,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -11574,7 +11595,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -11651,7 +11672,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -11728,7 +11749,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -11805,7 +11826,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -11882,7 +11903,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -11959,7 +11980,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -12036,7 +12057,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -12113,7 +12134,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -12190,7 +12211,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -12267,7 +12288,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -12344,7 +12365,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -12421,7 +12442,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -12498,7 +12519,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -12575,7 +12596,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -12652,7 +12673,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -12729,7 +12750,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -12806,7 +12827,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -12883,7 +12904,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -12960,7 +12981,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -13037,7 +13058,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -13114,7 +13135,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -13191,7 +13212,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -13268,7 +13289,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -13345,7 +13366,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -13422,7 +13443,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -13499,7 +13520,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -13576,7 +13597,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -13653,7 +13674,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -13730,7 +13751,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -13807,7 +13828,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -13884,7 +13905,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -13961,7 +13982,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -14038,7 +14059,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -14115,7 +14136,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -14192,7 +14213,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -14269,7 +14290,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -14346,7 +14367,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -14423,7 +14444,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -14500,7 +14521,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -14577,7 +14598,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -14654,7 +14675,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -14731,7 +14752,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -14808,7 +14829,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -14885,7 +14906,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -14962,7 +14983,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -15039,7 +15060,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -15116,7 +15137,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -15193,7 +15214,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -15270,7 +15291,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -15347,7 +15368,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -15424,7 +15445,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -15501,7 +15522,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -15578,7 +15599,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -15655,7 +15676,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -15732,7 +15753,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -15809,7 +15830,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -15886,7 +15907,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -15963,7 +15984,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -16040,7 +16061,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -16117,7 +16138,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -16194,7 +16215,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -16271,7 +16292,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -16348,7 +16369,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -16425,7 +16446,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -16502,7 +16523,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -16579,7 +16600,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -16656,7 +16677,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -16733,7 +16754,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -16810,7 +16831,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -16887,7 +16908,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -16964,7 +16985,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -17041,7 +17062,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -17118,7 +17139,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -17195,7 +17216,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -17272,7 +17293,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -17349,7 +17370,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -17426,7 +17447,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -17503,7 +17524,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -17580,7 +17601,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -17657,7 +17678,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -17734,7 +17755,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -17811,7 +17832,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -17888,7 +17909,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -17965,7 +17986,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -18042,7 +18063,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -18119,7 +18140,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -18196,7 +18217,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -18273,7 +18294,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -18350,7 +18371,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -18427,7 +18448,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -18504,7 +18525,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -18581,7 +18602,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -18658,7 +18679,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -18735,7 +18756,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -18812,7 +18833,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -18889,7 +18910,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -18966,7 +18987,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -19043,7 +19064,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -19120,7 +19141,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -19197,7 +19218,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -19274,7 +19295,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -19351,7 +19372,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -19428,7 +19449,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -19505,7 +19526,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -19582,7 +19603,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -19659,7 +19680,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -19736,7 +19757,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -19813,7 +19834,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -19890,7 +19911,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -19967,7 +19988,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -20044,7 +20065,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -20121,7 +20142,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -20198,7 +20219,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -20275,7 +20296,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -20352,7 +20373,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -20429,7 +20450,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -20506,7 +20527,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -20583,7 +20604,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -20660,7 +20681,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -20737,7 +20758,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -20814,7 +20835,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -20891,7 +20912,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -20968,7 +20989,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -21045,7 +21066,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -21122,7 +21143,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -21199,7 +21220,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -21276,7 +21297,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -21353,7 +21374,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -21430,7 +21451,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -21507,7 +21528,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -21584,7 +21605,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -21661,7 +21682,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -21738,7 +21759,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -21815,7 +21836,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -21892,7 +21913,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -21969,7 +21990,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -22046,7 +22067,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -22123,7 +22144,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -22200,7 +22221,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -22277,7 +22298,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -22354,7 +22375,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -22431,7 +22452,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -22508,7 +22529,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -22585,7 +22606,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -22662,7 +22683,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -22739,7 +22760,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -22816,7 +22837,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -22893,7 +22914,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -22970,7 +22991,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -23047,7 +23068,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -23124,7 +23145,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -23201,7 +23222,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -23278,7 +23299,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -23355,7 +23376,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -23432,7 +23453,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -23509,7 +23530,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -23586,7 +23607,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -23663,7 +23684,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -23740,7 +23761,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -23817,7 +23838,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25">
       <c r="A166" s="12">
         <v>46129</v>
       </c>
@@ -23894,7 +23915,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25">
       <c r="A167" s="12">
         <v>46129</v>
       </c>
@@ -23971,7 +23992,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25">
       <c r="A168" s="12">
         <v>46129</v>
       </c>
@@ -23983,6 +24004,69 @@
       </c>
       <c r="D168" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E168" s="11">
+        <v>49.5</v>
+      </c>
+      <c r="F168" s="11">
+        <v>28</v>
+      </c>
+      <c r="G168" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="H168" s="11">
+        <v>24</v>
+      </c>
+      <c r="I168" s="11">
+        <v>20.6</v>
+      </c>
+      <c r="J168" s="11">
+        <v>21.7</v>
+      </c>
+      <c r="K168" s="11">
+        <v>87.5</v>
+      </c>
+      <c r="L168" s="11">
+        <v>29</v>
+      </c>
+      <c r="M168" s="11">
+        <v>69.182000000000002</v>
+      </c>
+      <c r="N168" s="11">
+        <v>14.7</v>
+      </c>
+      <c r="O168" s="11">
+        <v>13</v>
+      </c>
+      <c r="P168" s="11">
+        <v>13.475</v>
+      </c>
+      <c r="Q168" s="11">
+        <v>50</v>
+      </c>
+      <c r="R168" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="S168" s="11">
+        <v>33</v>
+      </c>
+      <c r="T168" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="U168" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="V168" s="11">
+        <v>6.43</v>
+      </c>
+      <c r="W168" s="11">
+        <v>10.1</v>
+      </c>
+      <c r="X168" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="Y168" s="11">
+        <v>8.0250000000000004</v>
       </c>
     </row>
   </sheetData>
@@ -24002,19 +24086,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -24103,7 +24187,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -24184,7 +24268,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -24273,7 +24357,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -24362,7 +24446,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -24394,7 +24478,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -24487,24 +24571,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -24557,7 +24641,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -24602,7 +24686,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -24655,7 +24739,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -24708,7 +24792,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -24749,7 +24833,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -24790,7 +24874,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -24831,7 +24915,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -24872,7 +24956,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -24913,7 +24997,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -24954,7 +25038,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -24995,7 +25079,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -25036,7 +25120,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -25094,18 +25178,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -25152,7 +25236,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -25191,7 +25275,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -25238,7 +25322,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -25285,7 +25369,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -25317,7 +25401,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -25349,7 +25433,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -25381,7 +25465,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -25413,7 +25497,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -25445,7 +25529,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -25477,7 +25561,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -25509,7 +25593,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -25541,7 +25625,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -25589,7 +25673,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -25604,15 +25688,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -25623,7 +25707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -25637,7 +25721,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -25646,7 +25730,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -25655,7 +25739,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -25664,7 +25748,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -25673,7 +25757,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -25682,7 +25766,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -25691,7 +25775,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -25700,49 +25784,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -25753,7 +25837,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -25762,7 +25846,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -25771,7 +25855,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -25782,7 +25866,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -25791,7 +25875,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -25800,42 +25884,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -25844,35 +25928,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B979E86-1EF4-43AC-9DDF-1ADD664A07ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2377663E-6357-427B-ACA4-89239981EAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -253,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -952,6 +952,15 @@
                 <c:pt idx="168">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="169">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1467,6 +1476,12 @@
                 </c:pt>
                 <c:pt idx="168">
                   <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>38.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2020,6 +2035,15 @@
                 <c:pt idx="168">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="169">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2535,6 +2559,12 @@
                 </c:pt>
                 <c:pt idx="168">
                   <c:v>21.8</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>21.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3088,6 +3118,15 @@
                 <c:pt idx="168">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="169">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3603,6 +3642,12 @@
                 </c:pt>
                 <c:pt idx="168">
                   <c:v>68.545000000000002</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>68</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4156,6 +4201,15 @@
                 <c:pt idx="168">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="169">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4670,6 +4724,12 @@
                   <c:v>13.375</c:v>
                 </c:pt>
                 <c:pt idx="168">
+                  <c:v>13.375</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>13.375</c:v>
+                </c:pt>
+                <c:pt idx="170">
                   <c:v>13.375</c:v>
                 </c:pt>
               </c:numCache>
@@ -5224,6 +5284,15 @@
                 <c:pt idx="168">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="169">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5738,6 +5807,12 @@
                   <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="168">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="170">
                   <c:v>33</c:v>
                 </c:pt>
               </c:numCache>
@@ -6308,6 +6383,15 @@
                 <c:pt idx="168">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="169">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6823,6 +6907,12 @@
                 </c:pt>
                 <c:pt idx="168">
                   <c:v>6.39</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>6.33</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>6.33</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7378,6 +7468,15 @@
                 <c:pt idx="168">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="169">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>46133</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>46133</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7893,6 +7992,12 @@
                 </c:pt>
                 <c:pt idx="168">
                   <c:v>8.0749999999999993</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>8.125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8170,7 +8275,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8255,6 +8360,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8297,6 +8405,9 @@
                 <c:pt idx="10">
                   <c:v>222.5</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8307,6 +8418,148 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Module!$M$1:$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>DDR4 UDIMM 16GB 3200</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v> Average </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Module!$B$3:$B$1119</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="1117"/>
+                <c:pt idx="0">
+                  <c:v>46048</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46055</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46062</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46076</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46083</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46097</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46104</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46111</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46118</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46125</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Module!$M$3:$M$1119</c:f>
+              <c:numCache>
+                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:ptCount val="1117"/>
+                <c:pt idx="0">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>118.333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>121</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>122.667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>123.333</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>126.667</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>132.333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>143.333</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>149.333</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>149.209</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-C247-486A-B615-212EDB24F1C8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1526098480"/>
+        <c:axId val="1427473968"/>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
@@ -8375,6 +8628,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8417,6 +8673,9 @@
                 <c:pt idx="10">
                   <c:v>930</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>975</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8424,126 +8683,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-C247-486A-B615-212EDB24F1C8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Module!$M$1:$M$2</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>DDR4 UDIMM 16GB 3200</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v> Average </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Module!$B$3:$B$1119</c:f>
-              <c:numCache>
-                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="1117"/>
-                <c:pt idx="0">
-                  <c:v>46048</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>46055</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>46062</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>46076</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>46083</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>46090</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>46097</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>46104</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>46111</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>46118</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>46125</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Module!$M$3:$M$1119</c:f>
-              <c:numCache>
-                <c:formatCode>_-* #,##0.00_-;\-* #,##0.00_-;_-* "-"_-;_-@_-</c:formatCode>
-                <c:ptCount val="1117"/>
-                <c:pt idx="0">
-                  <c:v>94</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>110</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>118.333</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>121</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>122.667</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>123.333</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>126.667</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>132.333</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>143.333</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>150</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>149.333</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C247-486A-B615-212EDB24F1C8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8555,9 +8694,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1526098480"/>
-        <c:axId val="1427473968"/>
+        <c:axId val="1552709439"/>
+        <c:axId val="1552697919"/>
       </c:lineChart>
       <c:dateAx>
         <c:axId val="1526098480"/>
@@ -8616,6 +8756,7 @@
         <c:axId val="1427473968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="50"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -8668,6 +8809,66 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:valAx>
+        <c:axId val="1552697919"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="400"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1552709439"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:dateAx>
+        <c:axId val="1552709439"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy\-mm\-dd;@" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1552697919"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -8752,7 +8953,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8837,6 +9038,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8878,6 +9082,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>12.318</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.227</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8957,6 +9164,9 @@
                 <c:pt idx="10">
                   <c:v>46125</c:v>
                 </c:pt>
+                <c:pt idx="11">
+                  <c:v>46132</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8998,6 +9208,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>12.412000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.335000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11265,18 +11478,18 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y171"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y174"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -11353,7 +11566,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -11422,7 +11635,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -11499,7 +11712,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -11576,7 +11789,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -11653,7 +11866,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -11730,7 +11943,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -11807,7 +12020,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -11884,7 +12097,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -11961,7 +12174,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -12038,7 +12251,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -12115,7 +12328,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -12192,7 +12405,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -12269,7 +12482,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -12346,7 +12559,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -12423,7 +12636,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -12500,7 +12713,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -12577,7 +12790,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -12654,7 +12867,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -12731,7 +12944,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -12808,7 +13021,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -12885,7 +13098,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -12962,7 +13175,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -13039,7 +13252,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -13116,7 +13329,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -13193,7 +13406,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -13270,7 +13483,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -13347,7 +13560,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -13424,7 +13637,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -13501,7 +13714,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -13578,7 +13791,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -13655,7 +13868,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -13732,7 +13945,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -13809,7 +14022,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -13886,7 +14099,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -13963,7 +14176,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -14040,7 +14253,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -14117,7 +14330,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -14194,7 +14407,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -14271,7 +14484,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -14348,7 +14561,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -14425,7 +14638,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -14502,7 +14715,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -14579,7 +14792,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -14656,7 +14869,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -14733,7 +14946,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -14810,7 +15023,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -14887,7 +15100,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -14964,7 +15177,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -15041,7 +15254,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -15118,7 +15331,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -15195,7 +15408,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -15272,7 +15485,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -15349,7 +15562,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -15426,7 +15639,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -15503,7 +15716,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -15580,7 +15793,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -15657,7 +15870,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -15734,7 +15947,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -15811,7 +16024,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -15888,7 +16101,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -15965,7 +16178,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -16042,7 +16255,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -16119,7 +16332,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -16196,7 +16409,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -16273,7 +16486,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -16350,7 +16563,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -16427,7 +16640,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -16504,7 +16717,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -16581,7 +16794,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -16658,7 +16871,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -16735,7 +16948,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -16812,7 +17025,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -16889,7 +17102,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -16966,7 +17179,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -17043,7 +17256,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -17120,7 +17333,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -17197,7 +17410,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -17274,7 +17487,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -17351,7 +17564,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -17428,7 +17641,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -17505,7 +17718,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -17582,7 +17795,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -17659,7 +17872,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -17736,7 +17949,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -17813,7 +18026,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -17890,7 +18103,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -17967,7 +18180,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -18044,7 +18257,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -18121,7 +18334,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -18198,7 +18411,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -18275,7 +18488,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -18352,7 +18565,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -18429,7 +18642,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -18506,7 +18719,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -18583,7 +18796,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -18660,7 +18873,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -18737,7 +18950,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -18814,7 +19027,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -18891,7 +19104,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -18968,7 +19181,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -19045,7 +19258,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -19122,7 +19335,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -19199,7 +19412,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -19276,7 +19489,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -19353,7 +19566,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -19430,7 +19643,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -19507,7 +19720,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -19584,7 +19797,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -19661,7 +19874,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -19738,7 +19951,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -19815,7 +20028,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -19892,7 +20105,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -19969,7 +20182,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -20046,7 +20259,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -20123,7 +20336,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -20200,7 +20413,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -20277,7 +20490,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -20354,7 +20567,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -20431,7 +20644,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -20508,7 +20721,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -20585,7 +20798,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -20662,7 +20875,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -20739,7 +20952,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -20816,7 +21029,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -20893,7 +21106,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -20970,7 +21183,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -21047,7 +21260,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -21124,7 +21337,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -21201,7 +21414,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -21278,7 +21491,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -21355,7 +21568,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -21432,7 +21645,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -21509,7 +21722,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -21586,7 +21799,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -21663,7 +21876,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -21740,7 +21953,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -21817,7 +22030,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -21894,7 +22107,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -21971,7 +22184,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -22048,7 +22261,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -22125,7 +22338,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -22202,7 +22415,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -22279,7 +22492,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -22356,7 +22569,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -22433,7 +22646,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -22510,7 +22723,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -22587,7 +22800,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -22664,7 +22877,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -22741,7 +22954,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -22818,7 +23031,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -22895,7 +23108,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -22972,7 +23185,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -23049,7 +23262,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -23126,7 +23339,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -23203,7 +23416,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -23280,7 +23493,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -23357,7 +23570,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -23434,7 +23647,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -23511,7 +23724,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -23588,7 +23801,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -23665,7 +23878,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -23742,7 +23955,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -23819,7 +24032,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -23896,7 +24109,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -23973,7 +24186,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:25">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A166" s="12">
         <v>46129</v>
       </c>
@@ -24050,7 +24263,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:25">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A167" s="12">
         <v>46129</v>
       </c>
@@ -24127,7 +24340,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="168" spans="1:25">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A168" s="12">
         <v>46129</v>
       </c>
@@ -24204,7 +24417,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:25">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A169" s="12">
         <v>46132</v>
       </c>
@@ -24281,7 +24494,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="170" spans="1:25">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A170" s="12">
         <v>46132</v>
       </c>
@@ -24358,7 +24571,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="171" spans="1:25">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A171" s="12">
         <v>46132</v>
       </c>
@@ -24433,6 +24646,174 @@
       </c>
       <c r="Y171" s="11">
         <v>8.0749999999999993</v>
+      </c>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A172" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B172" s="12">
+        <v>46133</v>
+      </c>
+      <c r="C172" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E172" s="11">
+        <v>50</v>
+      </c>
+      <c r="F172" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G172" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H172" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I172" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J172" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K172" s="11">
+        <v>85</v>
+      </c>
+      <c r="L172" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M172" s="11">
+        <v>68</v>
+      </c>
+      <c r="N172" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O172" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P172" s="11">
+        <v>13.375</v>
+      </c>
+      <c r="Q172" s="11">
+        <v>51</v>
+      </c>
+      <c r="R172" s="11">
+        <v>15</v>
+      </c>
+      <c r="S172" s="11">
+        <v>33</v>
+      </c>
+      <c r="T172" s="11">
+        <v>7</v>
+      </c>
+      <c r="U172" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="V172" s="11">
+        <v>6.33</v>
+      </c>
+      <c r="W172" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="X172" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y172" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A173" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B173" s="12">
+        <v>46133</v>
+      </c>
+      <c r="C173" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E173" s="11">
+        <v>50</v>
+      </c>
+      <c r="F173" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G173" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H173" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I173" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J173" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K173" s="11">
+        <v>84</v>
+      </c>
+      <c r="L173" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M173" s="11">
+        <v>68</v>
+      </c>
+      <c r="N173" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O173" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P173" s="11">
+        <v>13.375</v>
+      </c>
+      <c r="Q173" s="11">
+        <v>51</v>
+      </c>
+      <c r="R173" s="11">
+        <v>15</v>
+      </c>
+      <c r="S173" s="11">
+        <v>33</v>
+      </c>
+      <c r="T173" s="11">
+        <v>7</v>
+      </c>
+      <c r="U173" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="V173" s="11">
+        <v>6.33</v>
+      </c>
+      <c r="W173" s="11">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="X173" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y173" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A174" s="12">
+        <v>46133</v>
+      </c>
+      <c r="B174" s="12">
+        <v>46133</v>
+      </c>
+      <c r="C174" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -24452,19 +24833,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -24553,7 +24934,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -24634,7 +25015,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -24723,7 +25104,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -24812,7 +25193,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -24844,7 +25225,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -24936,25 +25317,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -25007,7 +25388,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -25052,7 +25433,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -25105,7 +25486,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -25158,7 +25539,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -25199,7 +25580,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -25240,7 +25621,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -25281,7 +25662,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -25322,7 +25703,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -25363,7 +25744,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -25404,7 +25785,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -25445,7 +25826,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -25486,7 +25867,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -25525,6 +25906,47 @@
       </c>
       <c r="M13" s="11">
         <v>149.333</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A14" s="12">
+        <v>46125</v>
+      </c>
+      <c r="B14" s="12">
+        <v>46132</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="14">
+        <v>230</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="11">
+        <v>219</v>
+      </c>
+      <c r="H14" s="14">
+        <v>1150</v>
+      </c>
+      <c r="I14" s="14">
+        <v>900</v>
+      </c>
+      <c r="J14" s="11">
+        <v>975</v>
+      </c>
+      <c r="K14" s="14">
+        <v>172</v>
+      </c>
+      <c r="L14" s="14">
+        <v>136</v>
+      </c>
+      <c r="M14" s="11">
+        <v>149.209</v>
       </c>
     </row>
   </sheetData>
@@ -25543,19 +25965,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:Y13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -25602,7 +26024,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -25641,7 +26063,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -25688,7 +26110,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -25735,7 +26157,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -25767,7 +26189,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -25799,7 +26221,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -25831,7 +26253,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -25863,7 +26285,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -25895,7 +26317,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -25927,7 +26349,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -25959,7 +26381,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -25991,7 +26413,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -26021,6 +26443,38 @@
       </c>
       <c r="J13" s="11">
         <v>12.412000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A14" s="12">
+        <v>46125</v>
+      </c>
+      <c r="B14" s="12">
+        <v>46132</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="11">
+        <v>19.5</v>
+      </c>
+      <c r="F14" s="11">
+        <v>10</v>
+      </c>
+      <c r="G14" s="11">
+        <v>12.227</v>
+      </c>
+      <c r="H14" s="11">
+        <v>19</v>
+      </c>
+      <c r="I14" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="J14" s="11">
+        <v>12.335000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -26039,7 +26493,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -26054,15 +26508,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -26073,7 +26527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -26087,7 +26541,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -26096,7 +26550,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -26105,7 +26559,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -26114,7 +26568,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -26123,7 +26577,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -26132,7 +26586,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -26141,7 +26595,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -26150,49 +26604,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -26203,7 +26657,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -26212,7 +26666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -26221,7 +26675,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -26232,7 +26686,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -26241,7 +26695,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -26250,42 +26704,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -26294,35 +26748,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE6605F-C62B-4E58-AFDF-7FA27088E75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92ADDAE3-4D1C-493F-86CA-92D4DBF57628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -970,6 +970,15 @@
                 <c:pt idx="174">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1500,6 +1509,15 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>38.667000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2071,6 +2089,15 @@
                 <c:pt idx="174">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2600,6 +2627,15 @@
                   <c:v>21.9</c:v>
                 </c:pt>
                 <c:pt idx="173">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="176">
                   <c:v>21.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -3172,6 +3208,15 @@
                 <c:pt idx="174">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3702,6 +3747,15 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>66.227000000000004</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>66.227000000000004</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>64.727000000000004</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>64.727000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4273,6 +4327,15 @@
                 <c:pt idx="174">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4803,6 +4866,15 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>13.25</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>13.25</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>13.2</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>13.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5374,6 +5446,15 @@
                 <c:pt idx="174">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5904,6 +5985,15 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>32.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>32.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6491,6 +6581,15 @@
                 <c:pt idx="174">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7021,6 +7120,15 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>6.18</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>6.18</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>6.12</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>6.12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7594,6 +7702,15 @@
                 <c:pt idx="174">
                   <c:v>46134</c:v>
                 </c:pt>
+                <c:pt idx="175">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>46135</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8123,6 +8240,15 @@
                   <c:v>8.125</c:v>
                 </c:pt>
                 <c:pt idx="173">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="176">
                   <c:v>8.125</c:v>
                 </c:pt>
               </c:numCache>
@@ -11604,7 +11730,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y177"/>
+  <dimension ref="A1:Y180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -25159,7 +25285,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A177" s="12">
         <v>46134</v>
       </c>
@@ -25170,6 +25296,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D177" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E177" s="11">
+        <v>50.5</v>
+      </c>
+      <c r="F177" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G177" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H177" s="11">
+        <v>24</v>
+      </c>
+      <c r="I177" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J177" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K177" s="11">
+        <v>83</v>
+      </c>
+      <c r="L177" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M177" s="11">
+        <v>66.227000000000004</v>
+      </c>
+      <c r="N177" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O177" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="P177" s="11">
+        <v>13.25</v>
+      </c>
+      <c r="Q177" s="11">
+        <v>51</v>
+      </c>
+      <c r="R177" s="11">
+        <v>15</v>
+      </c>
+      <c r="S177" s="11">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="T177" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U177" s="11">
+        <v>5</v>
+      </c>
+      <c r="V177" s="11">
+        <v>6.18</v>
+      </c>
+      <c r="W177" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="X177" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y177" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A178" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B178" s="12">
+        <v>46135</v>
+      </c>
+      <c r="C178" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E178" s="11">
+        <v>50.5</v>
+      </c>
+      <c r="F178" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G178" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H178" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I178" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J178" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K178" s="11">
+        <v>80</v>
+      </c>
+      <c r="L178" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M178" s="11">
+        <v>64.727000000000004</v>
+      </c>
+      <c r="N178" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O178" s="11">
+        <v>12</v>
+      </c>
+      <c r="P178" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="Q178" s="11">
+        <v>51</v>
+      </c>
+      <c r="R178" s="11">
+        <v>15</v>
+      </c>
+      <c r="S178" s="11">
+        <v>32.6</v>
+      </c>
+      <c r="T178" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U178" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V178" s="11">
+        <v>6.12</v>
+      </c>
+      <c r="W178" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="X178" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y178" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A179" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B179" s="12">
+        <v>46135</v>
+      </c>
+      <c r="C179" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E179" s="11">
+        <v>50.5</v>
+      </c>
+      <c r="F179" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G179" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H179" s="11">
+        <v>24.5</v>
+      </c>
+      <c r="I179" s="11">
+        <v>20.8</v>
+      </c>
+      <c r="J179" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K179" s="11">
+        <v>80</v>
+      </c>
+      <c r="L179" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="M179" s="11">
+        <v>64.727000000000004</v>
+      </c>
+      <c r="N179" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="O179" s="11">
+        <v>12</v>
+      </c>
+      <c r="P179" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="Q179" s="11">
+        <v>51</v>
+      </c>
+      <c r="R179" s="11">
+        <v>15</v>
+      </c>
+      <c r="S179" s="11">
+        <v>32.6</v>
+      </c>
+      <c r="T179" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U179" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V179" s="11">
+        <v>6.12</v>
+      </c>
+      <c r="W179" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="X179" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y179" s="11">
+        <v>8.125</v>
+      </c>
+    </row>
+    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A180" s="12">
+        <v>46135</v>
+      </c>
+      <c r="B180" s="12">
+        <v>46135</v>
+      </c>
+      <c r="C180" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D180" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687CC511-7C71-412E-B650-A015FC1E1FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA055C8D-BD6A-4CE5-9CB7-DC2EC2D70C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -253,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1537,6 +1537,9 @@
                 <c:pt idx="179">
                   <c:v>38.5</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>38.5</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2674,6 +2677,9 @@
                 <c:pt idx="179">
                   <c:v>21.9</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>21.9</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3811,6 +3817,9 @@
                 <c:pt idx="179">
                   <c:v>63.908999999999999</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>63.908999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4948,6 +4957,9 @@
                 <c:pt idx="179">
                   <c:v>13.15</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>13.15</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6083,6 +6095,9 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="179">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="180">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -7238,6 +7253,9 @@
                 <c:pt idx="179">
                   <c:v>6.06</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>6.05</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -8375,6 +8393,9 @@
                   <c:v>8.125</c:v>
                 </c:pt>
                 <c:pt idx="179">
+                  <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="180">
                   <c:v>8.125</c:v>
                 </c:pt>
               </c:numCache>
@@ -8653,7 +8674,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9331,7 +9352,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11857,17 +11878,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y183"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -11944,7 +11965,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -12013,7 +12034,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -12090,7 +12111,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -12167,7 +12188,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -12244,7 +12265,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -12321,7 +12342,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -12398,7 +12419,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -12475,7 +12496,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -12552,7 +12573,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -12629,7 +12650,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -12706,7 +12727,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -12783,7 +12804,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -12860,7 +12881,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -12937,7 +12958,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -13014,7 +13035,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -13091,7 +13112,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -13168,7 +13189,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -13245,7 +13266,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -13322,7 +13343,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -13399,7 +13420,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -13476,7 +13497,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -13553,7 +13574,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -13630,7 +13651,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -13707,7 +13728,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -13784,7 +13805,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -13861,7 +13882,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -13938,7 +13959,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -14015,7 +14036,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -14092,7 +14113,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -14169,7 +14190,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -14246,7 +14267,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -14323,7 +14344,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -14400,7 +14421,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -14477,7 +14498,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -14554,7 +14575,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -14631,7 +14652,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -14708,7 +14729,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -14785,7 +14806,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -14862,7 +14883,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -14939,7 +14960,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -15016,7 +15037,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -15093,7 +15114,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -15170,7 +15191,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -15247,7 +15268,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -15324,7 +15345,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -15401,7 +15422,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -15478,7 +15499,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -15555,7 +15576,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -15632,7 +15653,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -15709,7 +15730,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -15786,7 +15807,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -15863,7 +15884,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -15940,7 +15961,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -16017,7 +16038,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -16094,7 +16115,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -16171,7 +16192,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -16248,7 +16269,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -16325,7 +16346,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -16402,7 +16423,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -16479,7 +16500,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -16556,7 +16577,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -16633,7 +16654,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -16710,7 +16731,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -16787,7 +16808,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -16864,7 +16885,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -16941,7 +16962,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -17018,7 +17039,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -17095,7 +17116,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -17172,7 +17193,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -17249,7 +17270,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -17326,7 +17347,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -17403,7 +17424,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -17480,7 +17501,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -17557,7 +17578,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -17634,7 +17655,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -17711,7 +17732,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -17788,7 +17809,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -17865,7 +17886,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -17942,7 +17963,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -18019,7 +18040,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -18096,7 +18117,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -18173,7 +18194,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -18250,7 +18271,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -18327,7 +18348,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -18404,7 +18425,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -18481,7 +18502,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -18558,7 +18579,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -18635,7 +18656,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -18712,7 +18733,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -18789,7 +18810,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -18866,7 +18887,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -18943,7 +18964,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -19020,7 +19041,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -19097,7 +19118,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -19174,7 +19195,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -19251,7 +19272,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -19328,7 +19349,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -19405,7 +19426,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -19482,7 +19503,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -19559,7 +19580,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -19636,7 +19657,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -19713,7 +19734,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -19790,7 +19811,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -19867,7 +19888,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -19944,7 +19965,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -20021,7 +20042,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -20098,7 +20119,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -20175,7 +20196,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -20252,7 +20273,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -20329,7 +20350,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -20406,7 +20427,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -20483,7 +20504,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -20560,7 +20581,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -20637,7 +20658,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -20714,7 +20735,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -20791,7 +20812,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -20868,7 +20889,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -20945,7 +20966,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -21022,7 +21043,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -21099,7 +21120,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -21176,7 +21197,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -21253,7 +21274,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -21330,7 +21351,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -21407,7 +21428,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -21484,7 +21505,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -21561,7 +21582,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -21638,7 +21659,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -21715,7 +21736,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -21792,7 +21813,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -21869,7 +21890,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -21946,7 +21967,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -22023,7 +22044,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -22100,7 +22121,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -22177,7 +22198,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -22254,7 +22275,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -22331,7 +22352,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -22408,7 +22429,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -22485,7 +22506,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -22562,7 +22583,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -22639,7 +22660,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -22716,7 +22737,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -22793,7 +22814,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -22870,7 +22891,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -22947,7 +22968,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -23024,7 +23045,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -23101,7 +23122,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -23178,7 +23199,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -23255,7 +23276,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -23332,7 +23353,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -23409,7 +23430,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -23486,7 +23507,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -23563,7 +23584,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -23640,7 +23661,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -23717,7 +23738,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -23794,7 +23815,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -23871,7 +23892,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -23948,7 +23969,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -24025,7 +24046,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -24102,7 +24123,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -24179,7 +24200,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -24256,7 +24277,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -24333,7 +24354,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -24410,7 +24431,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -24487,7 +24508,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -24564,7 +24585,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25">
       <c r="A166" s="12">
         <v>46129</v>
       </c>
@@ -24641,7 +24662,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25">
       <c r="A167" s="12">
         <v>46129</v>
       </c>
@@ -24718,7 +24739,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25">
       <c r="A168" s="12">
         <v>46129</v>
       </c>
@@ -24795,7 +24816,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25">
       <c r="A169" s="12">
         <v>46132</v>
       </c>
@@ -24872,7 +24893,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25">
       <c r="A170" s="12">
         <v>46132</v>
       </c>
@@ -24949,7 +24970,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25">
       <c r="A171" s="12">
         <v>46132</v>
       </c>
@@ -25026,7 +25047,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25">
       <c r="A172" s="12">
         <v>46133</v>
       </c>
@@ -25103,7 +25124,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25">
       <c r="A173" s="12">
         <v>46133</v>
       </c>
@@ -25180,7 +25201,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25">
       <c r="A174" s="12">
         <v>46133</v>
       </c>
@@ -25257,7 +25278,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25">
       <c r="A175" s="12">
         <v>46134</v>
       </c>
@@ -25334,7 +25355,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25">
       <c r="A176" s="12">
         <v>46134</v>
       </c>
@@ -25411,7 +25432,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25">
       <c r="A177" s="12">
         <v>46134</v>
       </c>
@@ -25488,7 +25509,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25">
       <c r="A178" s="12">
         <v>46135</v>
       </c>
@@ -25565,7 +25586,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25">
       <c r="A179" s="12">
         <v>46135</v>
       </c>
@@ -25642,7 +25663,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25">
       <c r="A180" s="12">
         <v>46135</v>
       </c>
@@ -25719,7 +25740,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25">
       <c r="A181" s="12">
         <v>46136</v>
       </c>
@@ -25796,7 +25817,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25">
       <c r="A182" s="12">
         <v>46136</v>
       </c>
@@ -25873,7 +25894,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25">
       <c r="A183" s="12">
         <v>46136</v>
       </c>
@@ -25885,6 +25906,69 @@
       </c>
       <c r="D183" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E183" s="11">
+        <v>50.6</v>
+      </c>
+      <c r="F183" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G183" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="H183" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I183" s="11">
+        <v>21</v>
+      </c>
+      <c r="J183" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K183" s="11">
+        <v>80</v>
+      </c>
+      <c r="L183" s="11">
+        <v>30</v>
+      </c>
+      <c r="M183" s="11">
+        <v>63.908999999999999</v>
+      </c>
+      <c r="N183" s="11">
+        <v>14.4</v>
+      </c>
+      <c r="O183" s="11">
+        <v>12</v>
+      </c>
+      <c r="P183" s="11">
+        <v>13.15</v>
+      </c>
+      <c r="Q183" s="11">
+        <v>51</v>
+      </c>
+      <c r="R183" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="S183" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="T183" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U183" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V183" s="11">
+        <v>6.05</v>
+      </c>
+      <c r="W183" s="11">
+        <v>10.3</v>
+      </c>
+      <c r="X183" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y183" s="11">
+        <v>8.125</v>
       </c>
     </row>
   </sheetData>
@@ -25904,19 +25988,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -26005,7 +26089,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -26086,7 +26170,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -26175,7 +26259,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -26264,7 +26348,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -26296,7 +26380,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -26389,24 +26473,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -26459,7 +26543,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -26504,7 +26588,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -26557,7 +26641,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -26610,7 +26694,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -26651,7 +26735,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -26692,7 +26776,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -26733,7 +26817,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -26774,7 +26858,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -26815,7 +26899,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -26856,7 +26940,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -26897,7 +26981,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -26938,7 +27022,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -26979,7 +27063,7 @@
         <v>149.333</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -27037,18 +27121,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -27095,7 +27179,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -27134,7 +27218,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -27181,7 +27265,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -27228,7 +27312,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -27260,7 +27344,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -27292,7 +27376,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -27324,7 +27408,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -27356,7 +27440,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -27388,7 +27472,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -27420,7 +27504,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -27452,7 +27536,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -27484,7 +27568,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -27516,7 +27600,7 @@
         <v>12.412000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -27564,7 +27648,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -27579,15 +27663,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -27598,7 +27682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -27612,7 +27696,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -27621,7 +27705,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -27630,7 +27714,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -27639,7 +27723,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -27648,7 +27732,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -27657,7 +27741,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -27666,7 +27750,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -27675,49 +27759,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -27728,7 +27812,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -27737,7 +27821,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -27746,7 +27830,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -27757,7 +27841,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -27766,7 +27850,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -27775,42 +27859,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -27819,35 +27903,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA055C8D-BD6A-4CE5-9CB7-DC2EC2D70C24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04BEFC4-4335-4787-B4F9-B65B1A0209BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -253,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -988,6 +988,15 @@
                 <c:pt idx="180">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1539,6 +1548,12 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>38.433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2128,6 +2143,15 @@
                 <c:pt idx="180">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2678,6 +2702,12 @@
                   <c:v>21.9</c:v>
                 </c:pt>
                 <c:pt idx="180">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="182">
                   <c:v>21.9</c:v>
                 </c:pt>
               </c:numCache>
@@ -3268,6 +3298,15 @@
                 <c:pt idx="180">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3819,6 +3858,12 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>63.908999999999999</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>63.173999999999999</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>63.173999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4408,6 +4453,15 @@
                 <c:pt idx="180">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4959,6 +5013,12 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>13.15</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>13.074999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5548,6 +5608,15 @@
                 <c:pt idx="180">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6098,6 +6167,12 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="180">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="182">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -6704,6 +6779,15 @@
                 <c:pt idx="180">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7255,6 +7339,12 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>6.05</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7846,6 +7936,15 @@
                 <c:pt idx="180">
                   <c:v>46136</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8397,6 +8496,12 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>8.125</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>8.1750000000000007</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>8.1750000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8674,7 +8779,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8762,6 +8867,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8806,6 +8914,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>219</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>218.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8888,6 +8999,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8932,6 +9046,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>149.209</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>148.86799999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9030,6 +9147,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9074,6 +9194,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>970</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9352,7 +9475,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9440,6 +9563,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9484,6 +9610,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>12.227</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.864000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9566,6 +9695,9 @@
                 <c:pt idx="11">
                   <c:v>46132</c:v>
                 </c:pt>
+                <c:pt idx="12">
+                  <c:v>46139</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9610,6 +9742,9 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>12.335000000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.962</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11877,18 +12012,18 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y183"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y186"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -11965,7 +12100,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -12034,7 +12169,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -12111,7 +12246,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -12188,7 +12323,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -12265,7 +12400,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -12342,7 +12477,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -12419,7 +12554,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -12496,7 +12631,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -12573,7 +12708,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -12650,7 +12785,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -12727,7 +12862,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -12804,7 +12939,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -12881,7 +13016,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -12958,7 +13093,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -13035,7 +13170,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -13112,7 +13247,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -13189,7 +13324,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -13266,7 +13401,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -13343,7 +13478,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -13420,7 +13555,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -13497,7 +13632,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -13574,7 +13709,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -13651,7 +13786,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -13728,7 +13863,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -13805,7 +13940,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -13882,7 +14017,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -13959,7 +14094,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -14036,7 +14171,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -14113,7 +14248,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -14190,7 +14325,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -14267,7 +14402,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -14344,7 +14479,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -14421,7 +14556,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -14498,7 +14633,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -14575,7 +14710,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -14652,7 +14787,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -14729,7 +14864,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -14806,7 +14941,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -14883,7 +15018,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -14960,7 +15095,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -15037,7 +15172,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -15114,7 +15249,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -15191,7 +15326,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -15268,7 +15403,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -15345,7 +15480,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -15422,7 +15557,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -15499,7 +15634,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -15576,7 +15711,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -15653,7 +15788,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -15730,7 +15865,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -15807,7 +15942,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -15884,7 +16019,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -15961,7 +16096,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -16038,7 +16173,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -16115,7 +16250,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -16192,7 +16327,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -16269,7 +16404,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -16346,7 +16481,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -16423,7 +16558,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -16500,7 +16635,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -16577,7 +16712,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -16654,7 +16789,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -16731,7 +16866,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -16808,7 +16943,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -16885,7 +17020,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -16962,7 +17097,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -17039,7 +17174,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -17116,7 +17251,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -17193,7 +17328,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -17270,7 +17405,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -17347,7 +17482,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -17424,7 +17559,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -17501,7 +17636,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -17578,7 +17713,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -17655,7 +17790,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -17732,7 +17867,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -17809,7 +17944,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -17886,7 +18021,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -17963,7 +18098,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -18040,7 +18175,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -18117,7 +18252,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -18194,7 +18329,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -18271,7 +18406,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -18348,7 +18483,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -18425,7 +18560,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -18502,7 +18637,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -18579,7 +18714,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -18656,7 +18791,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -18733,7 +18868,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -18810,7 +18945,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -18887,7 +19022,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -18964,7 +19099,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -19041,7 +19176,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -19118,7 +19253,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -19195,7 +19330,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -19272,7 +19407,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -19349,7 +19484,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -19426,7 +19561,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -19503,7 +19638,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -19580,7 +19715,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -19657,7 +19792,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -19734,7 +19869,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -19811,7 +19946,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -19888,7 +20023,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -19965,7 +20100,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -20042,7 +20177,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -20119,7 +20254,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -20196,7 +20331,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -20273,7 +20408,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -20350,7 +20485,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -20427,7 +20562,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -20504,7 +20639,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -20581,7 +20716,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -20658,7 +20793,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -20735,7 +20870,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -20812,7 +20947,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -20889,7 +21024,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -20966,7 +21101,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -21043,7 +21178,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -21120,7 +21255,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -21197,7 +21332,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -21274,7 +21409,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -21351,7 +21486,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -21428,7 +21563,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -21505,7 +21640,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -21582,7 +21717,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -21659,7 +21794,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -21736,7 +21871,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -21813,7 +21948,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -21890,7 +22025,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -21967,7 +22102,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -22044,7 +22179,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -22121,7 +22256,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -22198,7 +22333,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -22275,7 +22410,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -22352,7 +22487,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -22429,7 +22564,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -22506,7 +22641,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -22583,7 +22718,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -22660,7 +22795,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -22737,7 +22872,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -22814,7 +22949,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -22891,7 +23026,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -22968,7 +23103,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -23045,7 +23180,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -23122,7 +23257,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -23199,7 +23334,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -23276,7 +23411,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -23353,7 +23488,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -23430,7 +23565,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -23507,7 +23642,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -23584,7 +23719,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -23661,7 +23796,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -23738,7 +23873,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -23815,7 +23950,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -23892,7 +24027,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -23969,7 +24104,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -24046,7 +24181,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -24123,7 +24258,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -24200,7 +24335,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -24277,7 +24412,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -24354,7 +24489,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -24431,7 +24566,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -24508,7 +24643,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -24585,7 +24720,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:25">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A166" s="12">
         <v>46129</v>
       </c>
@@ -24662,7 +24797,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:25">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A167" s="12">
         <v>46129</v>
       </c>
@@ -24739,7 +24874,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="168" spans="1:25">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A168" s="12">
         <v>46129</v>
       </c>
@@ -24816,7 +24951,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:25">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A169" s="12">
         <v>46132</v>
       </c>
@@ -24893,7 +25028,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="170" spans="1:25">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A170" s="12">
         <v>46132</v>
       </c>
@@ -24970,7 +25105,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="171" spans="1:25">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A171" s="12">
         <v>46132</v>
       </c>
@@ -25047,7 +25182,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="172" spans="1:25">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A172" s="12">
         <v>46133</v>
       </c>
@@ -25124,7 +25259,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="173" spans="1:25">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A173" s="12">
         <v>46133</v>
       </c>
@@ -25201,7 +25336,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="174" spans="1:25">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A174" s="12">
         <v>46133</v>
       </c>
@@ -25278,7 +25413,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="175" spans="1:25">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A175" s="12">
         <v>46134</v>
       </c>
@@ -25355,7 +25490,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="176" spans="1:25">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A176" s="12">
         <v>46134</v>
       </c>
@@ -25432,7 +25567,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="177" spans="1:25">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A177" s="12">
         <v>46134</v>
       </c>
@@ -25509,7 +25644,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="178" spans="1:25">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A178" s="12">
         <v>46135</v>
       </c>
@@ -25586,7 +25721,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="179" spans="1:25">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A179" s="12">
         <v>46135</v>
       </c>
@@ -25663,7 +25798,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="180" spans="1:25">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A180" s="12">
         <v>46135</v>
       </c>
@@ -25740,7 +25875,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="181" spans="1:25">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A181" s="12">
         <v>46136</v>
       </c>
@@ -25817,7 +25952,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="182" spans="1:25">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A182" s="12">
         <v>46136</v>
       </c>
@@ -25894,7 +26029,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="183" spans="1:25">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A183" s="12">
         <v>46136</v>
       </c>
@@ -25969,6 +26104,174 @@
       </c>
       <c r="Y183" s="11">
         <v>8.125</v>
+      </c>
+    </row>
+    <row r="184" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A184" s="12">
+        <v>46139</v>
+      </c>
+      <c r="B184" s="12">
+        <v>46139</v>
+      </c>
+      <c r="C184" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E184" s="11">
+        <v>50.8</v>
+      </c>
+      <c r="F184" s="11">
+        <v>28.55</v>
+      </c>
+      <c r="G184" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="H184" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I184" s="11">
+        <v>21</v>
+      </c>
+      <c r="J184" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K184" s="11">
+        <v>78</v>
+      </c>
+      <c r="L184" s="11">
+        <v>30.3</v>
+      </c>
+      <c r="M184" s="11">
+        <v>63.173999999999999</v>
+      </c>
+      <c r="N184" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O184" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P184" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q184" s="11">
+        <v>51</v>
+      </c>
+      <c r="R184" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="S184" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="T184" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U184" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V184" s="11">
+        <v>6</v>
+      </c>
+      <c r="W184" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X184" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y184" s="11">
+        <v>8.1750000000000007</v>
+      </c>
+    </row>
+    <row r="185" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A185" s="12">
+        <v>46139</v>
+      </c>
+      <c r="B185" s="12">
+        <v>46139</v>
+      </c>
+      <c r="C185" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E185" s="11">
+        <v>50.8</v>
+      </c>
+      <c r="F185" s="11">
+        <v>28.55</v>
+      </c>
+      <c r="G185" s="11">
+        <v>38.433</v>
+      </c>
+      <c r="H185" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I185" s="11">
+        <v>21</v>
+      </c>
+      <c r="J185" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K185" s="11">
+        <v>78</v>
+      </c>
+      <c r="L185" s="11">
+        <v>30.3</v>
+      </c>
+      <c r="M185" s="11">
+        <v>63.173999999999999</v>
+      </c>
+      <c r="N185" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O185" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P185" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q185" s="11">
+        <v>51</v>
+      </c>
+      <c r="R185" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="S185" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="T185" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U185" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V185" s="11">
+        <v>6</v>
+      </c>
+      <c r="W185" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X185" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y185" s="11">
+        <v>8.1750000000000007</v>
+      </c>
+    </row>
+    <row r="186" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A186" s="12">
+        <v>46139</v>
+      </c>
+      <c r="B186" s="12">
+        <v>46139</v>
+      </c>
+      <c r="C186" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -25988,19 +26291,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -26089,7 +26392,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -26170,7 +26473,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -26259,7 +26562,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -26348,7 +26651,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -26380,7 +26683,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -26472,25 +26775,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -26543,7 +26846,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -26588,7 +26891,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -26641,7 +26944,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -26694,7 +26997,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -26735,7 +27038,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -26776,7 +27079,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -26817,7 +27120,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -26858,7 +27161,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -26899,7 +27202,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -26940,7 +27243,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -26981,7 +27284,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -27022,7 +27325,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -27063,7 +27366,7 @@
         <v>149.333</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -27102,6 +27405,47 @@
       </c>
       <c r="M14" s="11">
         <v>149.209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A15" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B15" s="12">
+        <v>46139</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="14">
+        <v>225</v>
+      </c>
+      <c r="F15" s="14">
+        <v>195</v>
+      </c>
+      <c r="G15" s="11">
+        <v>218.5</v>
+      </c>
+      <c r="H15" s="14">
+        <v>1185</v>
+      </c>
+      <c r="I15" s="14">
+        <v>880</v>
+      </c>
+      <c r="J15" s="11">
+        <v>970</v>
+      </c>
+      <c r="K15" s="14">
+        <v>171</v>
+      </c>
+      <c r="L15" s="14">
+        <v>135</v>
+      </c>
+      <c r="M15" s="11">
+        <v>148.86799999999999</v>
       </c>
     </row>
   </sheetData>
@@ -27120,19 +27464,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:Y14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -27179,7 +27523,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -27218,7 +27562,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -27265,7 +27609,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -27312,7 +27656,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -27344,7 +27688,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -27376,7 +27720,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -27408,7 +27752,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -27440,7 +27784,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -27472,7 +27816,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -27504,7 +27848,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -27536,7 +27880,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -27568,7 +27912,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -27600,7 +27944,7 @@
         <v>12.412000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -27630,6 +27974,38 @@
       </c>
       <c r="J14" s="11">
         <v>12.335000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A15" s="12">
+        <v>46132</v>
+      </c>
+      <c r="B15" s="12">
+        <v>46139</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="11">
+        <v>18</v>
+      </c>
+      <c r="F15" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G15" s="11">
+        <v>11.864000000000001</v>
+      </c>
+      <c r="H15" s="11">
+        <v>18</v>
+      </c>
+      <c r="I15" s="11">
+        <v>9</v>
+      </c>
+      <c r="J15" s="11">
+        <v>11.962</v>
       </c>
     </row>
   </sheetData>
@@ -27648,7 +28024,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -27663,15 +28039,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -27682,7 +28058,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -27696,7 +28072,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -27705,7 +28081,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -27714,7 +28090,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -27723,7 +28099,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -27732,7 +28108,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -27741,7 +28117,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -27750,7 +28126,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -27759,49 +28135,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -27812,7 +28188,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -27821,7 +28197,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -27830,7 +28206,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -27841,7 +28217,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -27850,7 +28226,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -27859,42 +28235,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -27903,35 +28279,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04BEFC4-4335-4787-B4F9-B65B1A0209BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC42A364-A1BC-4728-AA15-B4A7D3727EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -997,6 +997,15 @@
                 <c:pt idx="183">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1554,6 +1563,18 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>38.433</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>38.433</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>38.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2152,6 +2173,15 @@
                 <c:pt idx="183">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2709,6 +2739,18 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>21.9</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3307,6 +3349,15 @@
                 <c:pt idx="183">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3864,6 +3915,18 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>63.173999999999999</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>63.173999999999999</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>62.390999999999998</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>62.390999999999998</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>62.390999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4462,6 +4525,15 @@
                 <c:pt idx="183">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5018,6 +5090,18 @@
                   <c:v>13.074999999999999</c:v>
                 </c:pt>
                 <c:pt idx="182">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="186">
                   <c:v>13.074999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -5617,6 +5701,15 @@
                 <c:pt idx="183">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6173,6 +6266,18 @@
                   <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="182">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="186">
                   <c:v>32.5</c:v>
                 </c:pt>
               </c:numCache>
@@ -6788,6 +6893,15 @@
                 <c:pt idx="183">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7345,6 +7459,18 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>5.94</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5.94</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>5.94</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7945,6 +8071,15 @@
                 <c:pt idx="183">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="184">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46140</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46140</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8502,6 +8637,18 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>8.1750000000000007</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>8.1750000000000007</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>8.2249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>8.2249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>8.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12012,7 +12159,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y186"/>
+  <dimension ref="A1:Y189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -26272,6 +26419,300 @@
       </c>
       <c r="D186" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E186" s="11">
+        <v>50.8</v>
+      </c>
+      <c r="F186" s="11">
+        <v>28.55</v>
+      </c>
+      <c r="G186" s="11">
+        <v>38.433</v>
+      </c>
+      <c r="H186" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I186" s="11">
+        <v>21</v>
+      </c>
+      <c r="J186" s="11">
+        <v>21.9</v>
+      </c>
+      <c r="K186" s="11">
+        <v>78</v>
+      </c>
+      <c r="L186" s="11">
+        <v>30.3</v>
+      </c>
+      <c r="M186" s="11">
+        <v>63.173999999999999</v>
+      </c>
+      <c r="N186" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O186" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P186" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q186" s="11">
+        <v>51</v>
+      </c>
+      <c r="R186" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="S186" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="T186" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U186" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V186" s="11">
+        <v>6</v>
+      </c>
+      <c r="W186" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X186" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y186" s="11">
+        <v>8.1750000000000007</v>
+      </c>
+    </row>
+    <row r="187" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A187" s="12">
+        <v>46140</v>
+      </c>
+      <c r="B187" s="12">
+        <v>46140</v>
+      </c>
+      <c r="C187" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E187" s="11">
+        <v>50.8</v>
+      </c>
+      <c r="F187" s="11">
+        <v>28.55</v>
+      </c>
+      <c r="G187" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H187" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I187" s="11">
+        <v>21</v>
+      </c>
+      <c r="J187" s="11">
+        <v>22</v>
+      </c>
+      <c r="K187" s="11">
+        <v>78</v>
+      </c>
+      <c r="L187" s="11">
+        <v>30.3</v>
+      </c>
+      <c r="M187" s="11">
+        <v>62.390999999999998</v>
+      </c>
+      <c r="N187" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O187" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P187" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q187" s="11">
+        <v>51</v>
+      </c>
+      <c r="R187" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="S187" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="T187" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U187" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V187" s="11">
+        <v>5.94</v>
+      </c>
+      <c r="W187" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X187" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y187" s="11">
+        <v>8.2249999999999996</v>
+      </c>
+    </row>
+    <row r="188" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A188" s="12">
+        <v>46140</v>
+      </c>
+      <c r="B188" s="12">
+        <v>46140</v>
+      </c>
+      <c r="C188" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E188" s="11">
+        <v>50.8</v>
+      </c>
+      <c r="F188" s="11">
+        <v>28.55</v>
+      </c>
+      <c r="G188" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H188" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I188" s="11">
+        <v>21</v>
+      </c>
+      <c r="J188" s="11">
+        <v>22</v>
+      </c>
+      <c r="K188" s="11">
+        <v>78</v>
+      </c>
+      <c r="L188" s="11">
+        <v>30.3</v>
+      </c>
+      <c r="M188" s="11">
+        <v>62.390999999999998</v>
+      </c>
+      <c r="N188" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O188" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P188" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q188" s="11">
+        <v>51</v>
+      </c>
+      <c r="R188" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="S188" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="T188" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U188" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V188" s="11">
+        <v>5.94</v>
+      </c>
+      <c r="W188" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X188" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y188" s="11">
+        <v>8.2249999999999996</v>
+      </c>
+    </row>
+    <row r="189" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A189" s="12">
+        <v>46140</v>
+      </c>
+      <c r="B189" s="12">
+        <v>46140</v>
+      </c>
+      <c r="C189" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E189" s="11">
+        <v>50.8</v>
+      </c>
+      <c r="F189" s="11">
+        <v>28.9</v>
+      </c>
+      <c r="G189" s="11">
+        <v>38.5</v>
+      </c>
+      <c r="H189" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I189" s="11">
+        <v>21</v>
+      </c>
+      <c r="J189" s="11">
+        <v>22</v>
+      </c>
+      <c r="K189" s="11">
+        <v>78</v>
+      </c>
+      <c r="L189" s="11">
+        <v>30.3</v>
+      </c>
+      <c r="M189" s="11">
+        <v>62.390999999999998</v>
+      </c>
+      <c r="N189" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O189" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P189" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q189" s="11">
+        <v>51</v>
+      </c>
+      <c r="R189" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="S189" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="T189" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U189" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V189" s="11">
+        <v>5.94</v>
+      </c>
+      <c r="W189" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X189" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Y189" s="11">
+        <v>8.25</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC42A364-A1BC-4728-AA15-B4A7D3727EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7A013F-B044-4963-9804-DF3E70CA571E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1006,6 +1006,15 @@
                 <c:pt idx="186">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="187">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1575,6 +1584,12 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>38.667000000000002</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>38.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2182,6 +2197,15 @@
                 <c:pt idx="186">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="187">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2750,6 +2774,12 @@
                   <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="186">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="188">
                   <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
@@ -3358,6 +3388,15 @@
                 <c:pt idx="186">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="187">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3927,6 +3966,12 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>62.390999999999998</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>61.783000000000001</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>61.783000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4534,6 +4579,15 @@
                 <c:pt idx="186">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="187">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5102,6 +5156,12 @@
                   <c:v>13.074999999999999</c:v>
                 </c:pt>
                 <c:pt idx="186">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="188">
                   <c:v>13.074999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -5710,6 +5770,15 @@
                 <c:pt idx="186">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="187">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6279,6 +6348,12 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>32.479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>32.479999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6902,6 +6977,15 @@
                 <c:pt idx="186">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="187">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7471,6 +7555,12 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>5.94</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>5.9</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>5.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8080,6 +8170,15 @@
                 <c:pt idx="186">
                   <c:v>46140</c:v>
                 </c:pt>
+                <c:pt idx="187">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46141</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>46141</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8649,6 +8748,12 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>8.25</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>8.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>8.3000000000000007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12159,7 +12264,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y189"/>
+  <dimension ref="A1:Y192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -26713,6 +26818,174 @@
       </c>
       <c r="Y189" s="11">
         <v>8.25</v>
+      </c>
+    </row>
+    <row r="190" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A190" s="12">
+        <v>46141</v>
+      </c>
+      <c r="B190" s="12">
+        <v>46141</v>
+      </c>
+      <c r="C190" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E190" s="11">
+        <v>50.8</v>
+      </c>
+      <c r="F190" s="11">
+        <v>28.9</v>
+      </c>
+      <c r="G190" s="11">
+        <v>38.667000000000002</v>
+      </c>
+      <c r="H190" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I190" s="11">
+        <v>21</v>
+      </c>
+      <c r="J190" s="11">
+        <v>22</v>
+      </c>
+      <c r="K190" s="11">
+        <v>75</v>
+      </c>
+      <c r="L190" s="11">
+        <v>30.3</v>
+      </c>
+      <c r="M190" s="11">
+        <v>61.783000000000001</v>
+      </c>
+      <c r="N190" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O190" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P190" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q190" s="11">
+        <v>51</v>
+      </c>
+      <c r="R190" s="11">
+        <v>15.2</v>
+      </c>
+      <c r="S190" s="11">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="T190" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U190" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="V190" s="11">
+        <v>5.9</v>
+      </c>
+      <c r="W190" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X190" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y190" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="191" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A191" s="12">
+        <v>46141</v>
+      </c>
+      <c r="B191" s="12">
+        <v>46141</v>
+      </c>
+      <c r="C191" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E191" s="11">
+        <v>51</v>
+      </c>
+      <c r="F191" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G191" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H191" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I191" s="11">
+        <v>21</v>
+      </c>
+      <c r="J191" s="11">
+        <v>22</v>
+      </c>
+      <c r="K191" s="11">
+        <v>75</v>
+      </c>
+      <c r="L191" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="M191" s="11">
+        <v>61.783000000000001</v>
+      </c>
+      <c r="N191" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O191" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P191" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q191" s="11">
+        <v>51</v>
+      </c>
+      <c r="R191" s="11">
+        <v>15.3</v>
+      </c>
+      <c r="S191" s="11">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="T191" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U191" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="V191" s="11">
+        <v>5.9</v>
+      </c>
+      <c r="W191" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X191" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y191" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="192" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A192" s="12">
+        <v>46141</v>
+      </c>
+      <c r="B192" s="12">
+        <v>46141</v>
+      </c>
+      <c r="C192" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7A013F-B044-4963-9804-DF3E70CA571E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AAA28A-0FD7-43DD-BC80-2D7F07CD9451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1015,6 +1015,15 @@
                 <c:pt idx="189">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="190">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1590,6 +1599,15 @@
                 </c:pt>
                 <c:pt idx="188">
                   <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>38.866999999999997</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2206,6 +2224,15 @@
                 <c:pt idx="189">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="190">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2780,6 +2807,15 @@
                   <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="188">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="191">
                   <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
@@ -3397,6 +3433,15 @@
                 <c:pt idx="189">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="190">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3972,6 +4017,15 @@
                 </c:pt>
                 <c:pt idx="188">
                   <c:v>61.783000000000001</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>61.783000000000001</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>61.152000000000001</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>61.152000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4588,6 +4642,15 @@
                 <c:pt idx="189">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="190">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5162,6 +5225,15 @@
                   <c:v>13.074999999999999</c:v>
                 </c:pt>
                 <c:pt idx="188">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="191">
                   <c:v>13.074999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -5779,6 +5851,15 @@
                 <c:pt idx="189">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="190">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6353,6 +6434,15 @@
                   <c:v>32.479999999999997</c:v>
                 </c:pt>
                 <c:pt idx="188">
+                  <c:v>32.479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>32.479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>32.479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="191">
                   <c:v>32.479999999999997</c:v>
                 </c:pt>
               </c:numCache>
@@ -6986,6 +7076,15 @@
                 <c:pt idx="189">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="190">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7561,6 +7660,15 @@
                 </c:pt>
                 <c:pt idx="188">
                   <c:v>5.9</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>5.9</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>5.9</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>5.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8179,6 +8287,15 @@
                 <c:pt idx="189">
                   <c:v>46141</c:v>
                 </c:pt>
+                <c:pt idx="190">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>46142</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8754,6 +8871,15 @@
                 </c:pt>
                 <c:pt idx="188">
                   <c:v>8.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>8.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>8.375</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>8.375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12264,7 +12390,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y192"/>
+  <dimension ref="A1:Y195"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -26985,6 +27111,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D192" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E192" s="11">
+        <v>51</v>
+      </c>
+      <c r="F192" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G192" s="11">
+        <v>38.866999999999997</v>
+      </c>
+      <c r="H192" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I192" s="11">
+        <v>21</v>
+      </c>
+      <c r="J192" s="11">
+        <v>22</v>
+      </c>
+      <c r="K192" s="11">
+        <v>75</v>
+      </c>
+      <c r="L192" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="M192" s="11">
+        <v>61.783000000000001</v>
+      </c>
+      <c r="N192" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O192" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P192" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q192" s="11">
+        <v>51</v>
+      </c>
+      <c r="R192" s="11">
+        <v>15.3</v>
+      </c>
+      <c r="S192" s="11">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="T192" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U192" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="V192" s="11">
+        <v>5.9</v>
+      </c>
+      <c r="W192" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X192" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y192" s="11">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A193" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B193" s="12">
+        <v>46142</v>
+      </c>
+      <c r="C193" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E193" s="11">
+        <v>51</v>
+      </c>
+      <c r="F193" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G193" s="11">
+        <v>39</v>
+      </c>
+      <c r="H193" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I193" s="11">
+        <v>21</v>
+      </c>
+      <c r="J193" s="11">
+        <v>22</v>
+      </c>
+      <c r="K193" s="11">
+        <v>75</v>
+      </c>
+      <c r="L193" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="M193" s="11">
+        <v>61.152000000000001</v>
+      </c>
+      <c r="N193" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O193" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P193" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q193" s="11">
+        <v>51</v>
+      </c>
+      <c r="R193" s="11">
+        <v>15.3</v>
+      </c>
+      <c r="S193" s="11">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="T193" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U193" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="V193" s="11">
+        <v>5.9</v>
+      </c>
+      <c r="W193" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X193" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y193" s="11">
+        <v>8.375</v>
+      </c>
+    </row>
+    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A194" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B194" s="12">
+        <v>46142</v>
+      </c>
+      <c r="C194" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E194" s="11">
+        <v>51</v>
+      </c>
+      <c r="F194" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="G194" s="11">
+        <v>39</v>
+      </c>
+      <c r="H194" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I194" s="11">
+        <v>21</v>
+      </c>
+      <c r="J194" s="11">
+        <v>22</v>
+      </c>
+      <c r="K194" s="11">
+        <v>75</v>
+      </c>
+      <c r="L194" s="11">
+        <v>30.5</v>
+      </c>
+      <c r="M194" s="11">
+        <v>61.152000000000001</v>
+      </c>
+      <c r="N194" s="11">
+        <v>14.3</v>
+      </c>
+      <c r="O194" s="11">
+        <v>11.8</v>
+      </c>
+      <c r="P194" s="11">
+        <v>13.074999999999999</v>
+      </c>
+      <c r="Q194" s="11">
+        <v>51</v>
+      </c>
+      <c r="R194" s="11">
+        <v>15.3</v>
+      </c>
+      <c r="S194" s="11">
+        <v>32.479999999999997</v>
+      </c>
+      <c r="T194" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="U194" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="V194" s="11">
+        <v>5.82</v>
+      </c>
+      <c r="W194" s="11">
+        <v>10.5</v>
+      </c>
+      <c r="X194" s="11">
+        <v>5.15</v>
+      </c>
+      <c r="Y194" s="11">
+        <v>8.375</v>
+      </c>
+    </row>
+    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A195" s="12">
+        <v>46142</v>
+      </c>
+      <c r="B195" s="12">
+        <v>46142</v>
+      </c>
+      <c r="C195" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D195" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B605CA-2978-4D4A-A4AF-6A4AF9248C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E0A900-D4C5-4223-B8E9-7CE5A753882E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -253,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1024,6 +1024,15 @@
                 <c:pt idx="192">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="193">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1611,6 +1620,12 @@
                 </c:pt>
                 <c:pt idx="192">
                   <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>38.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2236,6 +2251,15 @@
                 <c:pt idx="192">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="193">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2822,6 +2846,12 @@
                   <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="192">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="194">
                   <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
@@ -3448,6 +3478,15 @@
                 <c:pt idx="192">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="193">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4035,6 +4074,12 @@
                 </c:pt>
                 <c:pt idx="192">
                   <c:v>61.152000000000001</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>60.542999999999999</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>60.542999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4660,6 +4705,15 @@
                 <c:pt idx="192">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="193">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5247,6 +5301,12 @@
                 </c:pt>
                 <c:pt idx="192">
                   <c:v>13.074999999999999</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5872,6 +5932,15 @@
                 <c:pt idx="192">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="193">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6459,6 +6528,12 @@
                 </c:pt>
                 <c:pt idx="192">
                   <c:v>32.479999999999997</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>32.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7100,6 +7175,15 @@
                 <c:pt idx="192">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="193">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7687,6 +7771,12 @@
                 </c:pt>
                 <c:pt idx="192">
                   <c:v>5.82</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>5.76</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>5.76</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8314,6 +8404,15 @@
                 <c:pt idx="192">
                   <c:v>46142</c:v>
                 </c:pt>
+                <c:pt idx="193">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>46146</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8901,6 +9000,12 @@
                 </c:pt>
                 <c:pt idx="192">
                   <c:v>8.375</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>8.4499999999999993</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>8.4499999999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9178,7 +9283,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9269,6 +9374,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9316,6 +9424,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>218.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>216</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9401,6 +9512,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9448,6 +9562,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>148.86799999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>148.83000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9549,6 +9666,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9596,6 +9716,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>960</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9874,7 +9997,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9965,6 +10088,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10012,6 +10138,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>11.864000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11.773</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10097,6 +10226,9 @@
                 <c:pt idx="12">
                   <c:v>46139</c:v>
                 </c:pt>
+                <c:pt idx="13">
+                  <c:v>46146</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10144,6 +10276,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>11.962</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11.829000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12411,18 +12546,18 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y195"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y198"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -12499,7 +12634,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -12568,7 +12703,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -12645,7 +12780,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -12722,7 +12857,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -12799,7 +12934,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -12876,7 +13011,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -12953,7 +13088,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -13030,7 +13165,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -13107,7 +13242,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -13184,7 +13319,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -13261,7 +13396,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -13338,7 +13473,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -13415,7 +13550,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -13492,7 +13627,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -13569,7 +13704,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -13646,7 +13781,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -13723,7 +13858,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -13800,7 +13935,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -13877,7 +14012,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -13954,7 +14089,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -14031,7 +14166,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -14108,7 +14243,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -14185,7 +14320,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -14262,7 +14397,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -14339,7 +14474,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -14416,7 +14551,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -14493,7 +14628,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -14570,7 +14705,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -14647,7 +14782,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -14724,7 +14859,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -14801,7 +14936,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -14878,7 +15013,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -14955,7 +15090,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -15032,7 +15167,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -15109,7 +15244,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -15186,7 +15321,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -15263,7 +15398,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -15340,7 +15475,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -15417,7 +15552,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -15494,7 +15629,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -15571,7 +15706,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -15648,7 +15783,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -15725,7 +15860,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -15802,7 +15937,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -15879,7 +16014,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -15956,7 +16091,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -16033,7 +16168,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -16110,7 +16245,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -16187,7 +16322,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -16264,7 +16399,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -16341,7 +16476,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -16418,7 +16553,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -16495,7 +16630,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -16572,7 +16707,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -16649,7 +16784,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -16726,7 +16861,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -16803,7 +16938,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -16880,7 +17015,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -16957,7 +17092,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -17034,7 +17169,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -17111,7 +17246,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -17188,7 +17323,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -17265,7 +17400,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -17342,7 +17477,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -17419,7 +17554,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -17496,7 +17631,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -17573,7 +17708,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -17650,7 +17785,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -17727,7 +17862,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -17804,7 +17939,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -17881,7 +18016,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -17958,7 +18093,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -18035,7 +18170,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -18112,7 +18247,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -18189,7 +18324,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -18266,7 +18401,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -18343,7 +18478,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -18420,7 +18555,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -18497,7 +18632,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -18574,7 +18709,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -18651,7 +18786,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -18728,7 +18863,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -18805,7 +18940,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -18882,7 +19017,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -18959,7 +19094,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -19036,7 +19171,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -19113,7 +19248,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -19190,7 +19325,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -19267,7 +19402,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -19344,7 +19479,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -19421,7 +19556,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -19498,7 +19633,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -19575,7 +19710,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -19652,7 +19787,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -19729,7 +19864,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -19806,7 +19941,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -19883,7 +20018,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -19960,7 +20095,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -20037,7 +20172,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -20114,7 +20249,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -20191,7 +20326,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -20268,7 +20403,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -20345,7 +20480,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -20422,7 +20557,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -20499,7 +20634,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -20576,7 +20711,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -20653,7 +20788,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -20730,7 +20865,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -20807,7 +20942,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -20884,7 +21019,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -20961,7 +21096,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -21038,7 +21173,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -21115,7 +21250,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -21192,7 +21327,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -21269,7 +21404,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -21346,7 +21481,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -21423,7 +21558,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -21500,7 +21635,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -21577,7 +21712,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -21654,7 +21789,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -21731,7 +21866,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -21808,7 +21943,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -21885,7 +22020,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -21962,7 +22097,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -22039,7 +22174,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -22116,7 +22251,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -22193,7 +22328,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -22270,7 +22405,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -22347,7 +22482,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -22424,7 +22559,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -22501,7 +22636,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -22578,7 +22713,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -22655,7 +22790,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -22732,7 +22867,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -22809,7 +22944,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -22886,7 +23021,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -22963,7 +23098,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -23040,7 +23175,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -23117,7 +23252,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -23194,7 +23329,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -23271,7 +23406,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -23348,7 +23483,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -23425,7 +23560,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -23502,7 +23637,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -23579,7 +23714,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -23656,7 +23791,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -23733,7 +23868,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -23810,7 +23945,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -23887,7 +24022,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -23964,7 +24099,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -24041,7 +24176,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -24118,7 +24253,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -24195,7 +24330,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -24272,7 +24407,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -24349,7 +24484,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -24426,7 +24561,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -24503,7 +24638,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -24580,7 +24715,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -24657,7 +24792,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -24734,7 +24869,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -24811,7 +24946,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -24888,7 +25023,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -24965,7 +25100,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -25042,7 +25177,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -25119,7 +25254,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:25">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A166" s="12">
         <v>46129</v>
       </c>
@@ -25196,7 +25331,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:25">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A167" s="12">
         <v>46129</v>
       </c>
@@ -25273,7 +25408,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="168" spans="1:25">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A168" s="12">
         <v>46129</v>
       </c>
@@ -25350,7 +25485,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:25">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A169" s="12">
         <v>46132</v>
       </c>
@@ -25427,7 +25562,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="170" spans="1:25">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A170" s="12">
         <v>46132</v>
       </c>
@@ -25504,7 +25639,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="171" spans="1:25">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A171" s="12">
         <v>46132</v>
       </c>
@@ -25581,7 +25716,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="172" spans="1:25">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A172" s="12">
         <v>46133</v>
       </c>
@@ -25658,7 +25793,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="173" spans="1:25">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A173" s="12">
         <v>46133</v>
       </c>
@@ -25735,7 +25870,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="174" spans="1:25">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A174" s="12">
         <v>46133</v>
       </c>
@@ -25812,7 +25947,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="175" spans="1:25">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A175" s="12">
         <v>46134</v>
       </c>
@@ -25889,7 +26024,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="176" spans="1:25">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A176" s="12">
         <v>46134</v>
       </c>
@@ -25966,7 +26101,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="177" spans="1:25">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A177" s="12">
         <v>46134</v>
       </c>
@@ -26043,7 +26178,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="178" spans="1:25">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A178" s="12">
         <v>46135</v>
       </c>
@@ -26120,7 +26255,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="179" spans="1:25">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A179" s="12">
         <v>46135</v>
       </c>
@@ -26197,7 +26332,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="180" spans="1:25">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A180" s="12">
         <v>46135</v>
       </c>
@@ -26274,7 +26409,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="181" spans="1:25">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A181" s="12">
         <v>46136</v>
       </c>
@@ -26351,7 +26486,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="182" spans="1:25">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A182" s="12">
         <v>46136</v>
       </c>
@@ -26428,7 +26563,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="183" spans="1:25">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A183" s="12">
         <v>46136</v>
       </c>
@@ -26505,7 +26640,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="184" spans="1:25">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A184" s="12">
         <v>46139</v>
       </c>
@@ -26582,7 +26717,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="185" spans="1:25">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A185" s="12">
         <v>46139</v>
       </c>
@@ -26659,7 +26794,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="186" spans="1:25">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A186" s="12">
         <v>46139</v>
       </c>
@@ -26736,7 +26871,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="187" spans="1:25">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A187" s="12">
         <v>46140</v>
       </c>
@@ -26813,7 +26948,7 @@
         <v>8.2249999999999996</v>
       </c>
     </row>
-    <row r="188" spans="1:25">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A188" s="12">
         <v>46140</v>
       </c>
@@ -26890,7 +27025,7 @@
         <v>8.2249999999999996</v>
       </c>
     </row>
-    <row r="189" spans="1:25">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A189" s="12">
         <v>46140</v>
       </c>
@@ -26967,7 +27102,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="190" spans="1:25">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A190" s="12">
         <v>46141</v>
       </c>
@@ -27044,7 +27179,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="191" spans="1:25">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A191" s="12">
         <v>46141</v>
       </c>
@@ -27121,7 +27256,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="192" spans="1:25">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A192" s="12">
         <v>46141</v>
       </c>
@@ -27198,7 +27333,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="193" spans="1:25">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A193" s="12">
         <v>46142</v>
       </c>
@@ -27275,7 +27410,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="194" spans="1:25">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A194" s="12">
         <v>46142</v>
       </c>
@@ -27352,7 +27487,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="195" spans="1:25">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A195" s="12">
         <v>46142</v>
       </c>
@@ -27427,6 +27562,174 @@
       </c>
       <c r="Y195" s="11">
         <v>8.375</v>
+      </c>
+    </row>
+    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A196" s="12">
+        <v>46146</v>
+      </c>
+      <c r="B196" s="12">
+        <v>46146</v>
+      </c>
+      <c r="C196" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E196" s="11">
+        <v>51</v>
+      </c>
+      <c r="F196" s="11">
+        <v>28</v>
+      </c>
+      <c r="G196" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H196" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I196" s="11">
+        <v>21</v>
+      </c>
+      <c r="J196" s="11">
+        <v>22</v>
+      </c>
+      <c r="K196" s="11">
+        <v>74</v>
+      </c>
+      <c r="L196" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="M196" s="11">
+        <v>60.542999999999999</v>
+      </c>
+      <c r="N196" s="11">
+        <v>14</v>
+      </c>
+      <c r="O196" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="P196" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q196" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R196" s="11">
+        <v>15.4</v>
+      </c>
+      <c r="S196" s="11">
+        <v>32.4</v>
+      </c>
+      <c r="T196" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="U196" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="V196" s="11">
+        <v>5.76</v>
+      </c>
+      <c r="W196" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="X196" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y196" s="11">
+        <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A197" s="12">
+        <v>46146</v>
+      </c>
+      <c r="B197" s="12">
+        <v>46146</v>
+      </c>
+      <c r="C197" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E197" s="11">
+        <v>51</v>
+      </c>
+      <c r="F197" s="11">
+        <v>28</v>
+      </c>
+      <c r="G197" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H197" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I197" s="11">
+        <v>21</v>
+      </c>
+      <c r="J197" s="11">
+        <v>22</v>
+      </c>
+      <c r="K197" s="11">
+        <v>74</v>
+      </c>
+      <c r="L197" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="M197" s="11">
+        <v>60.542999999999999</v>
+      </c>
+      <c r="N197" s="11">
+        <v>14</v>
+      </c>
+      <c r="O197" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="P197" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q197" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R197" s="11">
+        <v>15.4</v>
+      </c>
+      <c r="S197" s="11">
+        <v>32.4</v>
+      </c>
+      <c r="T197" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="U197" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="V197" s="11">
+        <v>5.76</v>
+      </c>
+      <c r="W197" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="X197" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y197" s="11">
+        <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A198" s="12">
+        <v>46146</v>
+      </c>
+      <c r="B198" s="12">
+        <v>46146</v>
+      </c>
+      <c r="C198" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -27445,20 +27748,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AK6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AK7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -27547,7 +27850,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -27628,7 +27931,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -27717,7 +28020,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -27806,7 +28109,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -27838,7 +28141,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -27913,6 +28216,83 @@
       </c>
       <c r="Y6" s="11">
         <v>5.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B7" s="6">
+        <v>46142</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="11">
+        <v>78.5</v>
+      </c>
+      <c r="F7" s="11">
+        <v>72.5</v>
+      </c>
+      <c r="G7" s="11">
+        <v>75</v>
+      </c>
+      <c r="H7" s="11">
+        <v>175</v>
+      </c>
+      <c r="I7" s="11">
+        <v>140</v>
+      </c>
+      <c r="J7" s="11">
+        <v>170</v>
+      </c>
+      <c r="K7" s="11">
+        <v>92</v>
+      </c>
+      <c r="L7" s="11">
+        <v>70.5</v>
+      </c>
+      <c r="M7" s="11">
+        <v>85</v>
+      </c>
+      <c r="N7" s="11">
+        <v>36</v>
+      </c>
+      <c r="O7" s="11">
+        <v>27</v>
+      </c>
+      <c r="P7" s="11">
+        <v>29.5</v>
+      </c>
+      <c r="Q7" s="11">
+        <v>17</v>
+      </c>
+      <c r="R7" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="S7" s="11">
+        <v>13</v>
+      </c>
+      <c r="T7" s="11">
+        <v>10</v>
+      </c>
+      <c r="U7" s="11">
+        <v>5.8</v>
+      </c>
+      <c r="V7" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="W7" s="11">
+        <v>9</v>
+      </c>
+      <c r="X7" s="11">
+        <v>7</v>
+      </c>
+      <c r="Y7" s="11">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -27930,25 +28310,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:Y15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -28001,7 +28381,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -28046,7 +28426,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -28099,7 +28479,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -28152,7 +28532,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -28193,7 +28573,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -28234,7 +28614,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -28275,7 +28655,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -28316,7 +28696,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -28357,7 +28737,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -28398,7 +28778,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -28439,7 +28819,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -28480,7 +28860,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -28521,7 +28901,7 @@
         <v>149.333</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -28562,7 +28942,7 @@
         <v>149.209</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46132</v>
       </c>
@@ -28601,6 +28981,47 @@
       </c>
       <c r="M15" s="11">
         <v>148.86799999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A16" s="12">
+        <v>46139</v>
+      </c>
+      <c r="B16" s="12">
+        <v>46146</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="14">
+        <v>220</v>
+      </c>
+      <c r="F16" s="14">
+        <v>194</v>
+      </c>
+      <c r="G16" s="11">
+        <v>216</v>
+      </c>
+      <c r="H16" s="14">
+        <v>1170</v>
+      </c>
+      <c r="I16" s="14">
+        <v>850</v>
+      </c>
+      <c r="J16" s="11">
+        <v>960</v>
+      </c>
+      <c r="K16" s="14">
+        <v>171</v>
+      </c>
+      <c r="L16" s="14">
+        <v>138</v>
+      </c>
+      <c r="M16" s="11">
+        <v>148.83000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -28619,19 +29040,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:Y15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -28678,7 +29099,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -28717,7 +29138,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -28764,7 +29185,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -28811,7 +29232,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -28843,7 +29264,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -28875,7 +29296,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -28907,7 +29328,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -28939,7 +29360,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -28971,7 +29392,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -29003,7 +29424,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -29035,7 +29456,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -29067,7 +29488,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -29099,7 +29520,7 @@
         <v>12.412000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -29131,7 +29552,7 @@
         <v>12.335000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46132</v>
       </c>
@@ -29161,6 +29582,38 @@
       </c>
       <c r="J15" s="11">
         <v>11.962</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A16" s="12">
+        <v>46139</v>
+      </c>
+      <c r="B16" s="12">
+        <v>46146</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="11">
+        <v>18</v>
+      </c>
+      <c r="F16" s="11">
+        <v>9.5</v>
+      </c>
+      <c r="G16" s="11">
+        <v>11.773</v>
+      </c>
+      <c r="H16" s="11">
+        <v>17.8</v>
+      </c>
+      <c r="I16" s="11">
+        <v>9</v>
+      </c>
+      <c r="J16" s="11">
+        <v>11.829000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -29179,7 +29632,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -29194,15 +29647,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -29213,7 +29666,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -29227,7 +29680,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -29236,7 +29689,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -29245,7 +29698,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -29254,7 +29707,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -29263,7 +29716,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -29272,7 +29725,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -29281,7 +29734,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -29290,49 +29743,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -29343,7 +29796,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -29352,7 +29805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -29361,7 +29814,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -29372,7 +29825,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -29381,7 +29834,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -29390,42 +29843,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -29434,35 +29887,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E0A900-D4C5-4223-B8E9-7CE5A753882E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6007B0F0-3402-4F41-87F1-B21019228A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -253,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1627,6 +1627,9 @@
                 <c:pt idx="194">
                   <c:v>38.832999999999998</c:v>
                 </c:pt>
+                <c:pt idx="195">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2854,6 +2857,9 @@
                 <c:pt idx="194">
                   <c:v>22</c:v>
                 </c:pt>
+                <c:pt idx="195">
+                  <c:v>22</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4081,6 +4087,9 @@
                 <c:pt idx="194">
                   <c:v>60.542999999999999</c:v>
                 </c:pt>
+                <c:pt idx="195">
+                  <c:v>60.542999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5308,6 +5317,9 @@
                 <c:pt idx="194">
                   <c:v>13</c:v>
                 </c:pt>
+                <c:pt idx="195">
+                  <c:v>13</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6533,6 +6545,9 @@
                   <c:v>32.4</c:v>
                 </c:pt>
                 <c:pt idx="194">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="195">
                   <c:v>32.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -7778,6 +7793,9 @@
                 <c:pt idx="194">
                   <c:v>5.76</c:v>
                 </c:pt>
+                <c:pt idx="195">
+                  <c:v>5.76</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9005,6 +9023,9 @@
                   <c:v>8.4499999999999993</c:v>
                 </c:pt>
                 <c:pt idx="194">
+                  <c:v>8.4499999999999993</c:v>
+                </c:pt>
+                <c:pt idx="195">
                   <c:v>8.4499999999999993</c:v>
                 </c:pt>
               </c:numCache>
@@ -9283,7 +9304,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9997,7 +10018,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12547,17 +12568,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y198"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -12634,7 +12655,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -12703,7 +12724,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -12780,7 +12801,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -12857,7 +12878,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -12934,7 +12955,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -13011,7 +13032,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -13088,7 +13109,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -13165,7 +13186,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -13242,7 +13263,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -13319,7 +13340,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -13396,7 +13417,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -13473,7 +13494,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -13550,7 +13571,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -13627,7 +13648,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -13704,7 +13725,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -13781,7 +13802,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -13858,7 +13879,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -13935,7 +13956,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -14012,7 +14033,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -14089,7 +14110,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -14166,7 +14187,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -14243,7 +14264,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -14320,7 +14341,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -14397,7 +14418,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -14474,7 +14495,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -14551,7 +14572,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -14628,7 +14649,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -14705,7 +14726,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -14782,7 +14803,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -14859,7 +14880,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -14936,7 +14957,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -15013,7 +15034,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -15090,7 +15111,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -15167,7 +15188,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -15244,7 +15265,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -15321,7 +15342,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -15398,7 +15419,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -15475,7 +15496,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -15552,7 +15573,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -15629,7 +15650,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -15706,7 +15727,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -15783,7 +15804,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -15860,7 +15881,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -15937,7 +15958,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -16014,7 +16035,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -16091,7 +16112,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -16168,7 +16189,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -16245,7 +16266,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -16322,7 +16343,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -16399,7 +16420,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -16476,7 +16497,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -16553,7 +16574,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -16630,7 +16651,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -16707,7 +16728,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -16784,7 +16805,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -16861,7 +16882,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -16938,7 +16959,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -17015,7 +17036,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -17092,7 +17113,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -17169,7 +17190,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -17246,7 +17267,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -17323,7 +17344,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -17400,7 +17421,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -17477,7 +17498,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -17554,7 +17575,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -17631,7 +17652,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -17708,7 +17729,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -17785,7 +17806,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -17862,7 +17883,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -17939,7 +17960,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -18016,7 +18037,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -18093,7 +18114,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -18170,7 +18191,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -18247,7 +18268,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -18324,7 +18345,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -18401,7 +18422,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -18478,7 +18499,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -18555,7 +18576,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -18632,7 +18653,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -18709,7 +18730,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -18786,7 +18807,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -18863,7 +18884,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -18940,7 +18961,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -19017,7 +19038,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -19094,7 +19115,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -19171,7 +19192,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -19248,7 +19269,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -19325,7 +19346,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -19402,7 +19423,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -19479,7 +19500,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -19556,7 +19577,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -19633,7 +19654,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -19710,7 +19731,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -19787,7 +19808,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -19864,7 +19885,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -19941,7 +19962,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -20018,7 +20039,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -20095,7 +20116,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -20172,7 +20193,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -20249,7 +20270,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -20326,7 +20347,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -20403,7 +20424,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -20480,7 +20501,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -20557,7 +20578,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -20634,7 +20655,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -20711,7 +20732,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -20788,7 +20809,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -20865,7 +20886,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -20942,7 +20963,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -21019,7 +21040,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -21096,7 +21117,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -21173,7 +21194,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -21250,7 +21271,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -21327,7 +21348,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -21404,7 +21425,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -21481,7 +21502,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -21558,7 +21579,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -21635,7 +21656,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -21712,7 +21733,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -21789,7 +21810,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -21866,7 +21887,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -21943,7 +21964,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -22020,7 +22041,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -22097,7 +22118,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -22174,7 +22195,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -22251,7 +22272,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -22328,7 +22349,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -22405,7 +22426,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -22482,7 +22503,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -22559,7 +22580,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -22636,7 +22657,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -22713,7 +22734,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -22790,7 +22811,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -22867,7 +22888,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -22944,7 +22965,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -23021,7 +23042,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -23098,7 +23119,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -23175,7 +23196,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -23252,7 +23273,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -23329,7 +23350,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -23406,7 +23427,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -23483,7 +23504,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -23560,7 +23581,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -23637,7 +23658,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -23714,7 +23735,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -23791,7 +23812,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -23868,7 +23889,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -23945,7 +23966,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -24022,7 +24043,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -24099,7 +24120,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -24176,7 +24197,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -24253,7 +24274,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -24330,7 +24351,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -24407,7 +24428,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -24484,7 +24505,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -24561,7 +24582,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -24638,7 +24659,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -24715,7 +24736,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -24792,7 +24813,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -24869,7 +24890,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -24946,7 +24967,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -25023,7 +25044,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -25100,7 +25121,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -25177,7 +25198,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -25254,7 +25275,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25">
       <c r="A166" s="12">
         <v>46129</v>
       </c>
@@ -25331,7 +25352,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25">
       <c r="A167" s="12">
         <v>46129</v>
       </c>
@@ -25408,7 +25429,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25">
       <c r="A168" s="12">
         <v>46129</v>
       </c>
@@ -25485,7 +25506,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25">
       <c r="A169" s="12">
         <v>46132</v>
       </c>
@@ -25562,7 +25583,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25">
       <c r="A170" s="12">
         <v>46132</v>
       </c>
@@ -25639,7 +25660,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25">
       <c r="A171" s="12">
         <v>46132</v>
       </c>
@@ -25716,7 +25737,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25">
       <c r="A172" s="12">
         <v>46133</v>
       </c>
@@ -25793,7 +25814,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25">
       <c r="A173" s="12">
         <v>46133</v>
       </c>
@@ -25870,7 +25891,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25">
       <c r="A174" s="12">
         <v>46133</v>
       </c>
@@ -25947,7 +25968,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25">
       <c r="A175" s="12">
         <v>46134</v>
       </c>
@@ -26024,7 +26045,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25">
       <c r="A176" s="12">
         <v>46134</v>
       </c>
@@ -26101,7 +26122,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25">
       <c r="A177" s="12">
         <v>46134</v>
       </c>
@@ -26178,7 +26199,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25">
       <c r="A178" s="12">
         <v>46135</v>
       </c>
@@ -26255,7 +26276,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25">
       <c r="A179" s="12">
         <v>46135</v>
       </c>
@@ -26332,7 +26353,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25">
       <c r="A180" s="12">
         <v>46135</v>
       </c>
@@ -26409,7 +26430,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25">
       <c r="A181" s="12">
         <v>46136</v>
       </c>
@@ -26486,7 +26507,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25">
       <c r="A182" s="12">
         <v>46136</v>
       </c>
@@ -26563,7 +26584,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25">
       <c r="A183" s="12">
         <v>46136</v>
       </c>
@@ -26640,7 +26661,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25">
       <c r="A184" s="12">
         <v>46139</v>
       </c>
@@ -26717,7 +26738,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25">
       <c r="A185" s="12">
         <v>46139</v>
       </c>
@@ -26794,7 +26815,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25">
       <c r="A186" s="12">
         <v>46139</v>
       </c>
@@ -26871,7 +26892,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25">
       <c r="A187" s="12">
         <v>46140</v>
       </c>
@@ -26948,7 +26969,7 @@
         <v>8.2249999999999996</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25">
       <c r="A188" s="12">
         <v>46140</v>
       </c>
@@ -27025,7 +27046,7 @@
         <v>8.2249999999999996</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25">
       <c r="A189" s="12">
         <v>46140</v>
       </c>
@@ -27102,7 +27123,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25">
       <c r="A190" s="12">
         <v>46141</v>
       </c>
@@ -27179,7 +27200,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25">
       <c r="A191" s="12">
         <v>46141</v>
       </c>
@@ -27256,7 +27277,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25">
       <c r="A192" s="12">
         <v>46141</v>
       </c>
@@ -27333,7 +27354,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25">
       <c r="A193" s="12">
         <v>46142</v>
       </c>
@@ -27410,7 +27431,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25">
       <c r="A194" s="12">
         <v>46142</v>
       </c>
@@ -27487,7 +27508,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25">
       <c r="A195" s="12">
         <v>46142</v>
       </c>
@@ -27564,7 +27585,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25">
       <c r="A196" s="12">
         <v>46146</v>
       </c>
@@ -27641,7 +27662,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25">
       <c r="A197" s="12">
         <v>46146</v>
       </c>
@@ -27718,7 +27739,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25">
       <c r="A198" s="12">
         <v>46146</v>
       </c>
@@ -27730,6 +27751,69 @@
       </c>
       <c r="D198" s="7" t="s">
         <v>53</v>
+      </c>
+      <c r="E198" s="11">
+        <v>51</v>
+      </c>
+      <c r="F198" s="11">
+        <v>28</v>
+      </c>
+      <c r="G198" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H198" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I198" s="11">
+        <v>21</v>
+      </c>
+      <c r="J198" s="11">
+        <v>22</v>
+      </c>
+      <c r="K198" s="11">
+        <v>74</v>
+      </c>
+      <c r="L198" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="M198" s="11">
+        <v>60.542999999999999</v>
+      </c>
+      <c r="N198" s="11">
+        <v>14</v>
+      </c>
+      <c r="O198" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="P198" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q198" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R198" s="11">
+        <v>15.4</v>
+      </c>
+      <c r="S198" s="11">
+        <v>32.4</v>
+      </c>
+      <c r="T198" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="U198" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="V198" s="11">
+        <v>5.76</v>
+      </c>
+      <c r="W198" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="X198" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y198" s="11">
+        <v>8.4499999999999993</v>
       </c>
     </row>
   </sheetData>
@@ -27749,19 +27833,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -27850,7 +27934,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -27931,7 +28015,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -28020,7 +28104,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -28109,7 +28193,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -28141,7 +28225,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -28218,7 +28302,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37">
       <c r="A7" s="6">
         <v>46082</v>
       </c>
@@ -28311,24 +28395,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -28381,7 +28465,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -28426,7 +28510,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -28479,7 +28563,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -28532,7 +28616,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -28573,7 +28657,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -28614,7 +28698,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -28655,7 +28739,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -28696,7 +28780,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -28737,7 +28821,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -28778,7 +28862,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -28819,7 +28903,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -28860,7 +28944,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -28901,7 +28985,7 @@
         <v>149.333</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -28942,7 +29026,7 @@
         <v>149.209</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46132</v>
       </c>
@@ -28983,7 +29067,7 @@
         <v>148.86799999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46139</v>
       </c>
@@ -29041,18 +29125,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" s="5" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -29099,7 +29183,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -29138,7 +29222,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -29185,7 +29269,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -29232,7 +29316,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -29264,7 +29348,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -29296,7 +29380,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -29328,7 +29412,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -29360,7 +29444,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -29392,7 +29476,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -29424,7 +29508,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -29456,7 +29540,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -29488,7 +29572,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -29520,7 +29604,7 @@
         <v>12.412000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -29552,7 +29636,7 @@
         <v>12.335000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25">
       <c r="A15" s="12">
         <v>46132</v>
       </c>
@@ -29584,7 +29668,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25">
       <c r="A16" s="12">
         <v>46139</v>
       </c>
@@ -29632,7 +29716,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -29647,15 +29731,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -29666,7 +29750,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -29680,7 +29764,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -29689,7 +29773,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -29698,7 +29782,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -29707,7 +29791,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -29716,7 +29800,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -29725,7 +29809,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -29734,7 +29818,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -29743,49 +29827,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -29796,7 +29880,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -29805,7 +29889,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -29814,7 +29898,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -29825,7 +29909,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -29834,7 +29918,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -29843,42 +29927,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -29887,35 +29971,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6007B0F0-3402-4F41-87F1-B21019228A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F4AC34-15F9-4CCC-984D-951250F050A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -253,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1033,6 +1033,15 @@
                 <c:pt idx="195">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="196">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1628,6 +1637,12 @@
                   <c:v>38.832999999999998</c:v>
                 </c:pt>
                 <c:pt idx="195">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="197">
                   <c:v>38.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -2263,6 +2278,15 @@
                 <c:pt idx="195">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="196">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2858,6 +2882,12 @@
                   <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="195">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="197">
                   <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
@@ -3493,6 +3523,15 @@
                 <c:pt idx="195">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="196">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4089,6 +4128,12 @@
                 </c:pt>
                 <c:pt idx="195">
                   <c:v>60.542999999999999</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>60.087000000000003</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>60.09</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4723,6 +4768,15 @@
                 <c:pt idx="195">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="196">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5318,6 +5372,12 @@
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="195">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="197">
                   <c:v>13</c:v>
                 </c:pt>
               </c:numCache>
@@ -5953,6 +6013,15 @@
                 <c:pt idx="195">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="196">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6548,6 +6617,12 @@
                   <c:v>32.4</c:v>
                 </c:pt>
                 <c:pt idx="195">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="197">
                   <c:v>32.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -7199,6 +7274,15 @@
                 <c:pt idx="195">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="196">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7795,6 +7879,12 @@
                 </c:pt>
                 <c:pt idx="195">
                   <c:v>5.76</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>5.71</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>5.71</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8431,6 +8521,15 @@
                 <c:pt idx="195">
                   <c:v>46146</c:v>
                 </c:pt>
+                <c:pt idx="196">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>46147</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>46147</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9027,6 +9126,12 @@
                 </c:pt>
                 <c:pt idx="195">
                   <c:v>8.4499999999999993</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>8.4749999999999996</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>8.4749999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9304,7 +9409,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10018,7 +10123,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12567,18 +12672,18 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y198"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Y201"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -12655,7 +12760,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -12724,7 +12829,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46044</v>
       </c>
@@ -12801,7 +12906,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46045</v>
       </c>
@@ -12878,7 +12983,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46045</v>
       </c>
@@ -12955,7 +13060,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46045</v>
       </c>
@@ -13032,7 +13137,7 @@
         <v>5.0250000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46048</v>
       </c>
@@ -13109,7 +13214,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46048</v>
       </c>
@@ -13186,7 +13291,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46048</v>
       </c>
@@ -13263,7 +13368,7 @@
         <v>5.1479999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46049</v>
       </c>
@@ -13340,7 +13445,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46049</v>
       </c>
@@ -13417,7 +13522,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46049</v>
       </c>
@@ -13494,7 +13599,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46050</v>
       </c>
@@ -13571,7 +13676,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46050</v>
       </c>
@@ -13648,7 +13753,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46050</v>
       </c>
@@ -13725,7 +13830,7 @@
         <v>5.2089999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46051</v>
       </c>
@@ -13802,7 +13907,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="12">
         <v>46051</v>
       </c>
@@ -13879,7 +13984,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="12">
         <v>46051</v>
       </c>
@@ -13956,7 +14061,7 @@
         <v>5.3319999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="12">
         <v>46052</v>
       </c>
@@ -14033,7 +14138,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="12">
         <v>46052</v>
       </c>
@@ -14110,7 +14215,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="12">
         <v>46052</v>
       </c>
@@ -14187,7 +14292,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="12">
         <v>46055</v>
       </c>
@@ -14264,7 +14369,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="12">
         <v>46055</v>
       </c>
@@ -14341,7 +14446,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="12">
         <v>46055</v>
       </c>
@@ -14418,7 +14523,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="12">
         <v>46056</v>
       </c>
@@ -14495,7 +14600,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="12">
         <v>46056</v>
       </c>
@@ -14572,7 +14677,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="12">
         <v>46056</v>
       </c>
@@ -14649,7 +14754,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="12">
         <v>46057</v>
       </c>
@@ -14726,7 +14831,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="12">
         <v>46057</v>
       </c>
@@ -14803,7 +14908,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="12">
         <v>46057</v>
       </c>
@@ -14880,7 +14985,7 @@
         <v>5.468</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="12">
         <v>46058</v>
       </c>
@@ -14957,7 +15062,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="12">
         <v>46058</v>
       </c>
@@ -15034,7 +15139,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="12">
         <v>46058</v>
       </c>
@@ -15111,7 +15216,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="12">
         <v>46059</v>
       </c>
@@ -15188,7 +15293,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="12">
         <v>46059</v>
       </c>
@@ -15265,7 +15370,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="12">
         <v>46059</v>
       </c>
@@ -15342,7 +15447,7 @@
         <v>5.4950000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="12">
         <v>46062</v>
       </c>
@@ -15419,7 +15524,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="12">
         <v>46062</v>
       </c>
@@ -15496,7 +15601,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="39" spans="1:25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="12">
         <v>46062</v>
       </c>
@@ -15573,7 +15678,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="12">
         <v>46063</v>
       </c>
@@ -15650,7 +15755,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="12">
         <v>46063</v>
       </c>
@@ -15727,7 +15832,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="12">
         <v>46063</v>
       </c>
@@ -15804,7 +15909,7 @@
         <v>5.5069999999999997</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="12">
         <v>46064</v>
       </c>
@@ -15881,7 +15986,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="12">
         <v>46064</v>
       </c>
@@ -15958,7 +16063,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="12">
         <v>46064</v>
       </c>
@@ -16035,7 +16140,7 @@
         <v>5.5229999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="12">
         <v>46065</v>
       </c>
@@ -16112,7 +16217,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="12">
         <v>46065</v>
       </c>
@@ -16189,7 +16294,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="12">
         <v>46065</v>
       </c>
@@ -16266,7 +16371,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="12">
         <v>46066</v>
       </c>
@@ -16343,7 +16448,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="12">
         <v>46066</v>
       </c>
@@ -16420,7 +16525,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="12">
         <v>46066</v>
       </c>
@@ -16497,7 +16602,7 @@
         <v>5.5449999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="12">
         <v>46076</v>
       </c>
@@ -16574,7 +16679,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="12">
         <v>46076</v>
       </c>
@@ -16651,7 +16756,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="12">
         <v>46076</v>
       </c>
@@ -16728,7 +16833,7 @@
         <v>5.5609999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="12">
         <v>46077</v>
       </c>
@@ -16805,7 +16910,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="12">
         <v>46077</v>
       </c>
@@ -16882,7 +16987,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="12">
         <v>46077</v>
       </c>
@@ -16959,7 +17064,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="12">
         <v>46078</v>
       </c>
@@ -17036,7 +17141,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="12">
         <v>46078</v>
       </c>
@@ -17113,7 +17218,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="12">
         <v>46078</v>
       </c>
@@ -17190,7 +17295,7 @@
         <v>5.5730000000000004</v>
       </c>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="12">
         <v>46079</v>
       </c>
@@ -17267,7 +17372,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="12">
         <v>46079</v>
       </c>
@@ -17344,7 +17449,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="12">
         <v>46079</v>
       </c>
@@ -17421,7 +17526,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="64" spans="1:25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="12">
         <v>46080</v>
       </c>
@@ -17498,7 +17603,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="65" spans="1:25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="12">
         <v>46080</v>
       </c>
@@ -17575,7 +17680,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" s="12">
         <v>46080</v>
       </c>
@@ -17652,7 +17757,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" s="12">
         <v>46083</v>
       </c>
@@ -17729,7 +17834,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>46083</v>
       </c>
@@ -17806,7 +17911,7 @@
         <v>5.5890000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>46083</v>
       </c>
@@ -17883,7 +17988,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>46084</v>
       </c>
@@ -17960,7 +18065,7 @@
         <v>5.7590000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>46084</v>
       </c>
@@ -18037,7 +18142,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>46084</v>
       </c>
@@ -18114,7 +18219,7 @@
         <v>5.7889999999999997</v>
       </c>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>46085</v>
       </c>
@@ -18191,7 +18296,7 @@
         <v>5.8390000000000004</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>46085</v>
       </c>
@@ -18268,7 +18373,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>46085</v>
       </c>
@@ -18345,7 +18450,7 @@
         <v>5.8620000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>46086</v>
       </c>
@@ -18422,7 +18527,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" s="12">
         <v>46086</v>
       </c>
@@ -18499,7 +18604,7 @@
         <v>5.8979999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" s="12">
         <v>46086</v>
       </c>
@@ -18576,7 +18681,7 @@
         <v>5.9210000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" s="12">
         <v>46087</v>
       </c>
@@ -18653,7 +18758,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="80" spans="1:25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" s="12">
         <v>46087</v>
       </c>
@@ -18730,7 +18835,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" s="12">
         <v>46087</v>
       </c>
@@ -18807,7 +18912,7 @@
         <v>6.0380000000000003</v>
       </c>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" s="12">
         <v>46090</v>
       </c>
@@ -18884,7 +18989,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="83" spans="1:25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" s="12">
         <v>46090</v>
       </c>
@@ -18961,7 +19066,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" s="12">
         <v>46090</v>
       </c>
@@ -19038,7 +19143,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="85" spans="1:25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" s="12">
         <v>46091</v>
       </c>
@@ -19115,7 +19220,7 @@
         <v>6.157</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" s="12">
         <v>46091</v>
       </c>
@@ -19192,7 +19297,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" s="12">
         <v>46091</v>
       </c>
@@ -19269,7 +19374,7 @@
         <v>6.181</v>
       </c>
     </row>
-    <row r="88" spans="1:25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" s="12">
         <v>46092</v>
       </c>
@@ -19346,7 +19451,7 @@
         <v>6.2430000000000003</v>
       </c>
     </row>
-    <row r="89" spans="1:25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" s="12">
         <v>46092</v>
       </c>
@@ -19423,7 +19528,7 @@
         <v>6.29</v>
       </c>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" s="12">
         <v>46092</v>
       </c>
@@ -19500,7 +19605,7 @@
         <v>6.3049999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" s="12">
         <v>46093</v>
       </c>
@@ -19577,7 +19682,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" s="12">
         <v>46093</v>
       </c>
@@ -19654,7 +19759,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" s="12">
         <v>46093</v>
       </c>
@@ -19731,7 +19836,7 @@
         <v>6.3810000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" s="12">
         <v>46094</v>
       </c>
@@ -19808,7 +19913,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" s="12">
         <v>46094</v>
       </c>
@@ -19885,7 +19990,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" s="12">
         <v>46094</v>
       </c>
@@ -19962,7 +20067,7 @@
         <v>6.4379999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A97" s="12">
         <v>46097</v>
       </c>
@@ -20039,7 +20144,7 @@
         <v>6.5330000000000004</v>
       </c>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A98" s="12">
         <v>46097</v>
       </c>
@@ -20116,7 +20221,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A99" s="12">
         <v>46097</v>
       </c>
@@ -20193,7 +20298,7 @@
         <v>6.5119999999999996</v>
       </c>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A100" s="12">
         <v>46098</v>
       </c>
@@ -20270,7 +20375,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A101" s="12">
         <v>46098</v>
       </c>
@@ -20347,7 +20452,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A102" s="12">
         <v>46098</v>
       </c>
@@ -20424,7 +20529,7 @@
         <v>6.6189999999999998</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A103" s="12">
         <v>46099</v>
       </c>
@@ -20501,7 +20606,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A104" s="12">
         <v>46099</v>
       </c>
@@ -20578,7 +20683,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A105" s="12">
         <v>46099</v>
       </c>
@@ -20655,7 +20760,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A106" s="12">
         <v>46100</v>
       </c>
@@ -20732,7 +20837,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A107" s="12">
         <v>46100</v>
       </c>
@@ -20809,7 +20914,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A108" s="12">
         <v>46100</v>
       </c>
@@ -20886,7 +20991,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="109" spans="1:25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A109" s="12">
         <v>46101</v>
       </c>
@@ -20963,7 +21068,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="110" spans="1:25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A110" s="12">
         <v>46101</v>
       </c>
@@ -21040,7 +21145,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A111" s="12">
         <v>46101</v>
       </c>
@@ -21117,7 +21222,7 @@
         <v>6.8879999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A112" s="12">
         <v>46104</v>
       </c>
@@ -21194,7 +21299,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="113" spans="1:25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A113" s="12">
         <v>46104</v>
       </c>
@@ -21271,7 +21376,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A114" s="12">
         <v>46104</v>
       </c>
@@ -21348,7 +21453,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A115" s="12">
         <v>46105</v>
       </c>
@@ -21425,7 +21530,7 @@
         <v>7.0250000000000004</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A116" s="12">
         <v>46105</v>
       </c>
@@ -21502,7 +21607,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="117" spans="1:25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A117" s="12">
         <v>46105</v>
       </c>
@@ -21579,7 +21684,7 @@
         <v>7.125</v>
       </c>
     </row>
-    <row r="118" spans="1:25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A118" s="12">
         <v>46106</v>
       </c>
@@ -21656,7 +21761,7 @@
         <v>7.15</v>
       </c>
     </row>
-    <row r="119" spans="1:25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A119" s="12">
         <v>46106</v>
       </c>
@@ -21733,7 +21838,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A120" s="12">
         <v>46106</v>
       </c>
@@ -21810,7 +21915,7 @@
         <v>7.2249999999999996</v>
       </c>
     </row>
-    <row r="121" spans="1:25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A121" s="12">
         <v>46107</v>
       </c>
@@ -21887,7 +21992,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A122" s="12">
         <v>46107</v>
       </c>
@@ -21964,7 +22069,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="123" spans="1:25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A123" s="12">
         <v>46107</v>
       </c>
@@ -22041,7 +22146,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A124" s="12">
         <v>46108</v>
       </c>
@@ -22118,7 +22223,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="125" spans="1:25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A125" s="12">
         <v>46108</v>
       </c>
@@ -22195,7 +22300,7 @@
         <v>7.3250000000000002</v>
       </c>
     </row>
-    <row r="126" spans="1:25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A126" s="12">
         <v>46108</v>
       </c>
@@ -22272,7 +22377,7 @@
         <v>7.375</v>
       </c>
     </row>
-    <row r="127" spans="1:25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A127" s="12">
         <v>46111</v>
       </c>
@@ -22349,7 +22454,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A128" s="12">
         <v>46111</v>
       </c>
@@ -22426,7 +22531,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A129" s="12">
         <v>46111</v>
       </c>
@@ -22503,7 +22608,7 @@
         <v>7.4249999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A130" s="12">
         <v>46112</v>
       </c>
@@ -22580,7 +22685,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="131" spans="1:25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A131" s="12">
         <v>46112</v>
       </c>
@@ -22657,7 +22762,7 @@
         <v>7.5250000000000004</v>
       </c>
     </row>
-    <row r="132" spans="1:25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A132" s="12">
         <v>46112</v>
       </c>
@@ -22734,7 +22839,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="133" spans="1:25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A133" s="12">
         <v>46113</v>
       </c>
@@ -22811,7 +22916,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="134" spans="1:25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A134" s="12">
         <v>46113</v>
       </c>
@@ -22888,7 +22993,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="135" spans="1:25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A135" s="12">
         <v>46113</v>
       </c>
@@ -22965,7 +23070,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="136" spans="1:25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A136" s="12">
         <v>46114</v>
       </c>
@@ -23042,7 +23147,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="137" spans="1:25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A137" s="12">
         <v>46114</v>
       </c>
@@ -23119,7 +23224,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="138" spans="1:25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A138" s="12">
         <v>46114</v>
       </c>
@@ -23196,7 +23301,7 @@
         <v>7.625</v>
       </c>
     </row>
-    <row r="139" spans="1:25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A139" s="12">
         <v>46115</v>
       </c>
@@ -23273,7 +23378,7 @@
         <v>7.6749999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A140" s="12">
         <v>46115</v>
       </c>
@@ -23350,7 +23455,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="141" spans="1:25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A141" s="12">
         <v>46115</v>
       </c>
@@ -23427,7 +23532,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="142" spans="1:25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A142" s="12">
         <v>46119</v>
       </c>
@@ -23504,7 +23609,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="143" spans="1:25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A143" s="12">
         <v>46119</v>
       </c>
@@ -23581,7 +23686,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="144" spans="1:25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A144" s="12">
         <v>46119</v>
       </c>
@@ -23658,7 +23763,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="145" spans="1:25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A145" s="12">
         <v>46120</v>
       </c>
@@ -23735,7 +23840,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="146" spans="1:25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A146" s="12">
         <v>46120</v>
       </c>
@@ -23812,7 +23917,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="147" spans="1:25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A147" s="12">
         <v>46120</v>
       </c>
@@ -23889,7 +23994,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="148" spans="1:25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A148" s="12">
         <v>46121</v>
       </c>
@@ -23966,7 +24071,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="149" spans="1:25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A149" s="12">
         <v>46121</v>
       </c>
@@ -24043,7 +24148,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="150" spans="1:25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A150" s="12">
         <v>46121</v>
       </c>
@@ -24120,7 +24225,7 @@
         <v>7.7249999999999996</v>
       </c>
     </row>
-    <row r="151" spans="1:25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A151" s="12">
         <v>46122</v>
       </c>
@@ -24197,7 +24302,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="152" spans="1:25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A152" s="12">
         <v>46122</v>
       </c>
@@ -24274,7 +24379,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="153" spans="1:25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A153" s="12">
         <v>46122</v>
       </c>
@@ -24351,7 +24456,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="154" spans="1:25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A154" s="12">
         <v>46125</v>
       </c>
@@ -24428,7 +24533,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="155" spans="1:25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A155" s="12">
         <v>46125</v>
       </c>
@@ -24505,7 +24610,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="156" spans="1:25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A156" s="12">
         <v>46125</v>
       </c>
@@ -24582,7 +24687,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="157" spans="1:25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A157" s="12">
         <v>46126</v>
       </c>
@@ -24659,7 +24764,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="158" spans="1:25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A158" s="12">
         <v>46126</v>
       </c>
@@ -24736,7 +24841,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="159" spans="1:25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A159" s="12">
         <v>46126</v>
       </c>
@@ -24813,7 +24918,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="160" spans="1:25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A160" s="12">
         <v>46127</v>
       </c>
@@ -24890,7 +24995,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="161" spans="1:25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" s="12">
         <v>46127</v>
       </c>
@@ -24967,7 +25072,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="162" spans="1:25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" s="12">
         <v>46127</v>
       </c>
@@ -25044,7 +25149,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="163" spans="1:25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A163" s="12">
         <v>46128</v>
       </c>
@@ -25121,7 +25226,7 @@
         <v>7.8630000000000004</v>
       </c>
     </row>
-    <row r="164" spans="1:25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A164" s="12">
         <v>46128</v>
       </c>
@@ -25198,7 +25303,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="165" spans="1:25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A165" s="12">
         <v>46128</v>
       </c>
@@ -25275,7 +25380,7 @@
         <v>7.9749999999999996</v>
       </c>
     </row>
-    <row r="166" spans="1:25">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A166" s="12">
         <v>46129</v>
       </c>
@@ -25352,7 +25457,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="167" spans="1:25">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A167" s="12">
         <v>46129</v>
       </c>
@@ -25429,7 +25534,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="168" spans="1:25">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A168" s="12">
         <v>46129</v>
       </c>
@@ -25506,7 +25611,7 @@
         <v>8.0250000000000004</v>
       </c>
     </row>
-    <row r="169" spans="1:25">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A169" s="12">
         <v>46132</v>
       </c>
@@ -25583,7 +25688,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="170" spans="1:25">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A170" s="12">
         <v>46132</v>
       </c>
@@ -25660,7 +25765,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="171" spans="1:25">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A171" s="12">
         <v>46132</v>
       </c>
@@ -25737,7 +25842,7 @@
         <v>8.0749999999999993</v>
       </c>
     </row>
-    <row r="172" spans="1:25">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A172" s="12">
         <v>46133</v>
       </c>
@@ -25814,7 +25919,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="173" spans="1:25">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A173" s="12">
         <v>46133</v>
       </c>
@@ -25891,7 +25996,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="174" spans="1:25">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A174" s="12">
         <v>46133</v>
       </c>
@@ -25968,7 +26073,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="175" spans="1:25">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A175" s="12">
         <v>46134</v>
       </c>
@@ -26045,7 +26150,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="176" spans="1:25">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A176" s="12">
         <v>46134</v>
       </c>
@@ -26122,7 +26227,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="177" spans="1:25">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A177" s="12">
         <v>46134</v>
       </c>
@@ -26199,7 +26304,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="178" spans="1:25">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A178" s="12">
         <v>46135</v>
       </c>
@@ -26276,7 +26381,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="179" spans="1:25">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A179" s="12">
         <v>46135</v>
       </c>
@@ -26353,7 +26458,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="180" spans="1:25">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A180" s="12">
         <v>46135</v>
       </c>
@@ -26430,7 +26535,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="181" spans="1:25">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A181" s="12">
         <v>46136</v>
       </c>
@@ -26507,7 +26612,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="182" spans="1:25">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A182" s="12">
         <v>46136</v>
       </c>
@@ -26584,7 +26689,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="183" spans="1:25">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A183" s="12">
         <v>46136</v>
       </c>
@@ -26661,7 +26766,7 @@
         <v>8.125</v>
       </c>
     </row>
-    <row r="184" spans="1:25">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A184" s="12">
         <v>46139</v>
       </c>
@@ -26738,7 +26843,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="185" spans="1:25">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A185" s="12">
         <v>46139</v>
       </c>
@@ -26815,7 +26920,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="186" spans="1:25">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A186" s="12">
         <v>46139</v>
       </c>
@@ -26892,7 +26997,7 @@
         <v>8.1750000000000007</v>
       </c>
     </row>
-    <row r="187" spans="1:25">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A187" s="12">
         <v>46140</v>
       </c>
@@ -26969,7 +27074,7 @@
         <v>8.2249999999999996</v>
       </c>
     </row>
-    <row r="188" spans="1:25">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A188" s="12">
         <v>46140</v>
       </c>
@@ -27046,7 +27151,7 @@
         <v>8.2249999999999996</v>
       </c>
     </row>
-    <row r="189" spans="1:25">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A189" s="12">
         <v>46140</v>
       </c>
@@ -27123,7 +27228,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="190" spans="1:25">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A190" s="12">
         <v>46141</v>
       </c>
@@ -27200,7 +27305,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="191" spans="1:25">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A191" s="12">
         <v>46141</v>
       </c>
@@ -27277,7 +27382,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="192" spans="1:25">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A192" s="12">
         <v>46141</v>
       </c>
@@ -27354,7 +27459,7 @@
         <v>8.3000000000000007</v>
       </c>
     </row>
-    <row r="193" spans="1:25">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A193" s="12">
         <v>46142</v>
       </c>
@@ -27431,7 +27536,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="194" spans="1:25">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A194" s="12">
         <v>46142</v>
       </c>
@@ -27508,7 +27613,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="195" spans="1:25">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A195" s="12">
         <v>46142</v>
       </c>
@@ -27585,7 +27690,7 @@
         <v>8.375</v>
       </c>
     </row>
-    <row r="196" spans="1:25">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A196" s="12">
         <v>46146</v>
       </c>
@@ -27662,7 +27767,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="197" spans="1:25">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A197" s="12">
         <v>46146</v>
       </c>
@@ -27739,7 +27844,7 @@
         <v>8.4499999999999993</v>
       </c>
     </row>
-    <row r="198" spans="1:25">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A198" s="12">
         <v>46146</v>
       </c>
@@ -27814,6 +27919,174 @@
       </c>
       <c r="Y198" s="11">
         <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="199" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A199" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B199" s="12">
+        <v>46147</v>
+      </c>
+      <c r="C199" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E199" s="11">
+        <v>51</v>
+      </c>
+      <c r="F199" s="11">
+        <v>28</v>
+      </c>
+      <c r="G199" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H199" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I199" s="11">
+        <v>21</v>
+      </c>
+      <c r="J199" s="11">
+        <v>22</v>
+      </c>
+      <c r="K199" s="11">
+        <v>74</v>
+      </c>
+      <c r="L199" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="M199" s="11">
+        <v>60.087000000000003</v>
+      </c>
+      <c r="N199" s="11">
+        <v>14</v>
+      </c>
+      <c r="O199" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="P199" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q199" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R199" s="11">
+        <v>15.4</v>
+      </c>
+      <c r="S199" s="11">
+        <v>32.4</v>
+      </c>
+      <c r="T199" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="U199" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V199" s="11">
+        <v>5.71</v>
+      </c>
+      <c r="W199" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="X199" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y199" s="11">
+        <v>8.4749999999999996</v>
+      </c>
+    </row>
+    <row r="200" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A200" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B200" s="12">
+        <v>46147</v>
+      </c>
+      <c r="C200" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E200" s="11">
+        <v>51</v>
+      </c>
+      <c r="F200" s="11">
+        <v>28</v>
+      </c>
+      <c r="G200" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H200" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I200" s="11">
+        <v>21</v>
+      </c>
+      <c r="J200" s="11">
+        <v>22</v>
+      </c>
+      <c r="K200" s="11">
+        <v>74</v>
+      </c>
+      <c r="L200" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="M200" s="11">
+        <v>60.09</v>
+      </c>
+      <c r="N200" s="11">
+        <v>14</v>
+      </c>
+      <c r="O200" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="P200" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q200" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R200" s="11">
+        <v>15.4</v>
+      </c>
+      <c r="S200" s="11">
+        <v>32.4</v>
+      </c>
+      <c r="T200" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="U200" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V200" s="11">
+        <v>5.71</v>
+      </c>
+      <c r="W200" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="X200" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y200" s="11">
+        <v>8.4749999999999996</v>
+      </c>
+    </row>
+    <row r="201" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A201" s="12">
+        <v>46147</v>
+      </c>
+      <c r="B201" s="12">
+        <v>46147</v>
+      </c>
+      <c r="C201" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -27833,19 +28106,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="9" style="11"/>
-    <col min="8" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="5" customFormat="1">
+    <row r="1" spans="1:37" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -27934,7 +28207,7 @@
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -28015,7 +28288,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
     </row>
-    <row r="3" spans="1:37">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45962</v>
       </c>
@@ -28104,7 +28377,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
     </row>
-    <row r="4" spans="1:37">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45992</v>
       </c>
@@ -28193,7 +28466,7 @@
       <c r="AJ4" s="2"/>
       <c r="AK4" s="2"/>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>46023</v>
       </c>
@@ -28225,7 +28498,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>46054</v>
       </c>
@@ -28302,7 +28575,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>46082</v>
       </c>
@@ -28395,24 +28668,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Y16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="9.08984375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.09765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="9" style="14"/>
-    <col min="13" max="13" width="13.26953125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.296875" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>49</v>
       </c>
@@ -28465,7 +28738,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="15"/>
       <c r="B2" s="15"/>
       <c r="C2" s="16"/>
@@ -28510,7 +28783,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -28563,7 +28836,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -28616,7 +28889,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -28657,7 +28930,7 @@
         <v>118.333</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -28698,7 +28971,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -28739,7 +29012,7 @@
         <v>122.667</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -28780,7 +29053,7 @@
         <v>123.333</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -28821,7 +29094,7 @@
         <v>126.667</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -28862,7 +29135,7 @@
         <v>132.333</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -28903,7 +29176,7 @@
         <v>143.333</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -28944,7 +29217,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -28985,7 +29258,7 @@
         <v>149.333</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -29026,7 +29299,7 @@
         <v>149.209</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46132</v>
       </c>
@@ -29067,7 +29340,7 @@
         <v>148.86799999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46139</v>
       </c>
@@ -29125,18 +29398,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:Y16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="10.6328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.09765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="10.59765625" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="25" width="9" style="11"/>
     <col min="26" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
+    <row r="1" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>49</v>
       </c>
@@ -29183,7 +29456,7 @@
       <c r="X1" s="9"/>
       <c r="Y1" s="9"/>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="16"/>
@@ -29222,7 +29495,7 @@
       <c r="X2" s="10"/>
       <c r="Y2" s="10"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>46034</v>
       </c>
@@ -29269,7 +29542,7 @@
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>46048</v>
       </c>
@@ -29316,7 +29589,7 @@
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="12">
         <v>46055</v>
       </c>
@@ -29348,7 +29621,7 @@
         <v>9.6539999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="12">
         <v>46062</v>
       </c>
@@ -29380,7 +29653,7 @@
         <v>9.8650000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>46076</v>
       </c>
@@ -29412,7 +29685,7 @@
         <v>10.221</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>46083</v>
       </c>
@@ -29444,7 +29717,7 @@
         <v>10.721</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>46090</v>
       </c>
@@ -29476,7 +29749,7 @@
         <v>11.462</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="12">
         <v>46097</v>
       </c>
@@ -29508,7 +29781,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="12">
         <v>46104</v>
       </c>
@@ -29540,7 +29813,7 @@
         <v>12.865</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="12">
         <v>46111</v>
       </c>
@@ -29572,7 +29845,7 @@
         <v>12.71</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="12">
         <v>46118</v>
       </c>
@@ -29604,7 +29877,7 @@
         <v>12.412000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="12">
         <v>46125</v>
       </c>
@@ -29636,7 +29909,7 @@
         <v>12.335000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="12">
         <v>46132</v>
       </c>
@@ -29668,7 +29941,7 @@
         <v>11.962</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="12">
         <v>46139</v>
       </c>
@@ -29716,7 +29989,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -29731,15 +30004,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.8984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.59765625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -29750,7 +30023,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -29764,7 +30037,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -29773,7 +30046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2" t="s">
         <v>31</v>
@@ -29782,7 +30055,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2" t="s">
         <v>33</v>
@@ -29791,7 +30064,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2" t="s">
         <v>35</v>
@@ -29800,7 +30073,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2" t="s">
         <v>37</v>
@@ -29809,7 +30082,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
@@ -29818,7 +30091,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -29827,49 +30100,49 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
@@ -29880,7 +30153,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="2" t="s">
         <v>8</v>
@@ -29889,7 +30162,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>9</v>
@@ -29898,7 +30171,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
@@ -29909,7 +30182,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="2" t="s">
         <v>11</v>
@@ -29918,7 +30191,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>45</v>
       </c>
@@ -29927,42 +30200,42 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -29971,35 +30244,35 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="2" t="s">
         <v>23</v>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F4AC34-15F9-4CCC-984D-951250F050A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77969603-A577-43E2-B0EC-F74D9F2A6F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="58">
   <si>
     <t>DDR5 8GB SO-DIMM</t>
   </si>
@@ -1042,6 +1042,15 @@
                 <c:pt idx="198">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="199">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1643,6 +1652,15 @@
                   <c:v>38.832999999999998</c:v>
                 </c:pt>
                 <c:pt idx="197">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>38.832999999999998</c:v>
+                </c:pt>
+                <c:pt idx="200">
                   <c:v>38.832999999999998</c:v>
                 </c:pt>
               </c:numCache>
@@ -2287,6 +2305,15 @@
                 <c:pt idx="198">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="199">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2888,6 +2915,15 @@
                   <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="197">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="200">
                   <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
@@ -3532,6 +3568,15 @@
                 <c:pt idx="198">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="199">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4134,6 +4179,15 @@
                 </c:pt>
                 <c:pt idx="197">
                   <c:v>60.09</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>60.087000000000003</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>59.652000000000001</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>59.113999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4777,6 +4831,15 @@
                 <c:pt idx="198">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="199">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5379,6 +5442,15 @@
                 </c:pt>
                 <c:pt idx="197">
                   <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>12.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6022,6 +6094,15 @@
                 <c:pt idx="198">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="199">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6624,6 +6705,15 @@
                 </c:pt>
                 <c:pt idx="197">
                   <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7283,6 +7373,15 @@
                 <c:pt idx="198">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="199">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7885,6 +7984,15 @@
                 </c:pt>
                 <c:pt idx="197">
                   <c:v>5.71</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>5.7</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>5.62</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>5.58</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8530,6 +8638,15 @@
                 <c:pt idx="198">
                   <c:v>46147</c:v>
                 </c:pt>
+                <c:pt idx="199">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>46148</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>46148</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9132,6 +9249,15 @@
                 </c:pt>
                 <c:pt idx="197">
                   <c:v>8.4749999999999996</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>8.4749999999999996</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>8.5250000000000004</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>8.5250000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12672,7 +12798,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Y201"/>
+  <dimension ref="A1:Y204"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="12" bestFit="1" customWidth="1"/>
@@ -28086,6 +28212,237 @@
         <v>0.75694444444444453</v>
       </c>
       <c r="D201" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E201" s="11">
+        <v>51</v>
+      </c>
+      <c r="F201" s="11">
+        <v>28</v>
+      </c>
+      <c r="G201" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H201" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I201" s="11">
+        <v>21</v>
+      </c>
+      <c r="J201" s="11">
+        <v>22</v>
+      </c>
+      <c r="K201" s="11">
+        <v>74</v>
+      </c>
+      <c r="L201" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="M201" s="11">
+        <v>60.087000000000003</v>
+      </c>
+      <c r="N201" s="11">
+        <v>14</v>
+      </c>
+      <c r="O201" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="P201" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q201" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R201" s="11">
+        <v>15.4</v>
+      </c>
+      <c r="S201" s="11">
+        <v>32.4</v>
+      </c>
+      <c r="T201" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="U201" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V201" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="W201" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="X201" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y201" s="11">
+        <v>8.4749999999999996</v>
+      </c>
+    </row>
+    <row r="202" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A202" s="12">
+        <v>46148</v>
+      </c>
+      <c r="B202" s="12">
+        <v>46148</v>
+      </c>
+      <c r="C202" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E202" s="11">
+        <v>51</v>
+      </c>
+      <c r="F202" s="11">
+        <v>28</v>
+      </c>
+      <c r="G202" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H202" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I202" s="11">
+        <v>21</v>
+      </c>
+      <c r="J202" s="11">
+        <v>22</v>
+      </c>
+      <c r="K202" s="11">
+        <v>74</v>
+      </c>
+      <c r="L202" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="M202" s="11">
+        <v>59.652000000000001</v>
+      </c>
+      <c r="N202" s="11">
+        <v>14</v>
+      </c>
+      <c r="O202" s="11">
+        <v>11.7</v>
+      </c>
+      <c r="P202" s="11">
+        <v>13</v>
+      </c>
+      <c r="Q202" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R202" s="11">
+        <v>15.4</v>
+      </c>
+      <c r="S202" s="11">
+        <v>32</v>
+      </c>
+      <c r="T202" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="U202" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="V202" s="11">
+        <v>5.62</v>
+      </c>
+      <c r="W202" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="X202" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="Y202" s="11">
+        <v>8.5250000000000004</v>
+      </c>
+    </row>
+    <row r="203" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A203" s="12">
+        <v>46148</v>
+      </c>
+      <c r="B203" s="12">
+        <v>46148</v>
+      </c>
+      <c r="C203" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E203" s="11">
+        <v>51</v>
+      </c>
+      <c r="F203" s="11">
+        <v>28</v>
+      </c>
+      <c r="G203" s="11">
+        <v>38.832999999999998</v>
+      </c>
+      <c r="H203" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="I203" s="11">
+        <v>21</v>
+      </c>
+      <c r="J203" s="11">
+        <v>22</v>
+      </c>
+      <c r="K203" s="11">
+        <v>74</v>
+      </c>
+      <c r="L203" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="M203" s="11">
+        <v>59.113999999999997</v>
+      </c>
+      <c r="N203" s="11">
+        <v>14</v>
+      </c>
+      <c r="O203" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="P203" s="11">
+        <v>12.875</v>
+      </c>
+      <c r="Q203" s="11">
+        <v>51.5</v>
+      </c>
+      <c r="R203" s="11">
+        <v>15.4</v>
+      </c>
+      <c r="S203" s="11">
+        <v>32</v>
+      </c>
+      <c r="T203" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="U203" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="V203" s="11">
+        <v>5.58</v>
+      </c>
+      <c r="W203" s="11">
+        <v>10.6</v>
+      </c>
+      <c r="X203" s="11">
+        <v>5.25</v>
+      </c>
+      <c r="Y203" s="11">
+        <v>8.5250000000000004</v>
+      </c>
+    </row>
+    <row r="204" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A204" s="12">
+        <v>46148</v>
+      </c>
+      <c r="B204" s="12">
+        <v>46148</v>
+      </c>
+      <c r="C204" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D204" s="7" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/industry/TrendForce/DRAM.xlsx
+++ b/data/industry/TrendForce/DRAM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45339E6-B198-4716-8976-715EFD0A2311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F682CC-D05E-45AB-9F79-9F4986B641C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DRAM" sheetId="2" r:id="rId1"/>
@@ -253,23 +253,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -282,7 +282,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -325,7 +325,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -346,27 +346,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -374,8 +374,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,7 +393,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1681,6 +1681,9 @@
                 <c:pt idx="203">
                   <c:v>39</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>39</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2962,6 +2965,9 @@
                 <c:pt idx="203">
                   <c:v>22.1</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>22.1</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4243,6 +4249,9 @@
                 <c:pt idx="203">
                   <c:v>58.567999999999998</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>58.567999999999998</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5524,6 +5533,9 @@
                 <c:pt idx="203">
                   <c:v>12.75</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>12.75</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -6803,6 +6815,9 @@
                   <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="203">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="204">
                   <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
@@ -8102,6 +8117,9 @@
                 <c:pt idx="203">
                   <c:v>5.48</c:v>
                 </c:pt>
+                <c:pt idx="204">
+                  <c:v>5.48</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -9383,6 +9401,9 @@
                   <c:v>8.5749999999999993</c:v>
                 </c:pt>
                 <c:pt idx="203">
+                  <c:v>8.625</c:v>
+                </c:pt>
+                <c:pt idx="204">
                   <c:v>8.625</c:v>
                 </c:pt>
               </c:numCache>
@@ -9661,7 +9682,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10375,7 +10396,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12925,17 +12946,17 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:Y207"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6